--- a/Data/examples.xlsx
+++ b/Data/examples.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7209" uniqueCount="6205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7207" uniqueCount="6202">
   <si>
     <t xml:space="preserve">BackgroundLipids</t>
   </si>
@@ -4165,7 +4165,7 @@
     <t xml:space="preserve">PC O-18:0/18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P26807</t>
+    <t xml:space="preserve">P00920</t>
   </si>
   <si>
     <t xml:space="preserve">P36423</t>
@@ -4174,15 +4174,12 @@
     <t xml:space="preserve">PC O-18:0/20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P00920</t>
+    <t xml:space="preserve">P49935</t>
   </si>
   <si>
     <t xml:space="preserve">Q9D7X3</t>
   </si>
   <si>
-    <t xml:space="preserve">P49935</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q60715</t>
   </si>
   <si>
@@ -4195,52 +4192,55 @@
     <t xml:space="preserve">Q91ZE0</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8K394</t>
+  </si>
+  <si>
     <t xml:space="preserve">P07724</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8K394</t>
+    <t xml:space="preserve">Q9WV85</t>
   </si>
   <si>
     <t xml:space="preserve">P15105</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WV85</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q61878</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8CI59</t>
+  </si>
+  <si>
     <t xml:space="preserve">O54824</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8CI59</t>
+    <t xml:space="preserve">Q793I8</t>
   </si>
   <si>
     <t xml:space="preserve">Q61646</t>
   </si>
   <si>
-    <t xml:space="preserve">Q793I8</t>
+    <t xml:space="preserve">Q78PG9</t>
   </si>
   <si>
     <t xml:space="preserve">P06801</t>
   </si>
   <si>
-    <t xml:space="preserve">Q78PG9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8BZQ2</t>
   </si>
   <si>
+    <t xml:space="preserve">Q80SW1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9CR67</t>
   </si>
   <si>
-    <t xml:space="preserve">Q80SW1</t>
+    <t xml:space="preserve">P15864</t>
   </si>
   <si>
     <t xml:space="preserve">P24452</t>
   </si>
   <si>
-    <t xml:space="preserve">P15864</t>
+    <t xml:space="preserve">O70309</t>
   </si>
   <si>
     <t xml:space="preserve">P16627</t>
@@ -4249,7 +4249,7 @@
     <t xml:space="preserve">TG 46:0</t>
   </si>
   <si>
-    <t xml:space="preserve">O70309</t>
+    <t xml:space="preserve">P62305</t>
   </si>
   <si>
     <t xml:space="preserve">Q00651</t>
@@ -4258,13 +4258,13 @@
     <t xml:space="preserve">TG 48:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P62305</t>
+    <t xml:space="preserve">Q9QXK7</t>
   </si>
   <si>
     <t xml:space="preserve">P16045</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QXK7</t>
+    <t xml:space="preserve">Q9CQI6</t>
   </si>
   <si>
     <t xml:space="preserve">P97801</t>
@@ -4276,19 +4276,19 @@
     <t xml:space="preserve">PC 18:2_22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQI6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8BV49</t>
   </si>
   <si>
     <t xml:space="preserve">TG 50:0</t>
   </si>
   <si>
+    <t xml:space="preserve">Q3U0V2</t>
+  </si>
+  <si>
     <t xml:space="preserve">P11672</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3U0V2</t>
+    <t xml:space="preserve">Q61171</t>
   </si>
   <si>
     <t xml:space="preserve">Q7TSE6</t>
@@ -4297,7 +4297,7 @@
     <t xml:space="preserve">TG 50:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61171</t>
+    <t xml:space="preserve">Q9D2G2</t>
   </si>
   <si>
     <t xml:space="preserve">Q8R1G6</t>
@@ -4309,7 +4309,7 @@
     <t xml:space="preserve">PG 16:1_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D2G2</t>
+    <t xml:space="preserve">P42208</t>
   </si>
   <si>
     <t xml:space="preserve">P30681</t>
@@ -4318,7 +4318,7 @@
     <t xml:space="preserve">TG 52:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P42208</t>
+    <t xml:space="preserve">Q8R2Y8</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BHX3</t>
@@ -4327,22 +4327,22 @@
     <t xml:space="preserve">TG 52:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8R2Y8</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6P549</t>
   </si>
   <si>
     <t xml:space="preserve">PG 18:1_18:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8BH95</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8CJ53</t>
   </si>
   <si>
     <t xml:space="preserve">TG 52:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BH95</t>
+    <t xml:space="preserve">P17710</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BWW9</t>
@@ -4351,7 +4351,7 @@
     <t xml:space="preserve">TG 52:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P17710</t>
+    <t xml:space="preserve">Q9WUM5</t>
   </si>
   <si>
     <t xml:space="preserve">Q9Z268</t>
@@ -4363,22 +4363,22 @@
     <t xml:space="preserve">PG 18:2_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WUM5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9QXH4</t>
   </si>
   <si>
     <t xml:space="preserve">PA 16:0_16:1</t>
   </si>
   <si>
+    <t xml:space="preserve">P68510</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9D154</t>
   </si>
   <si>
     <t xml:space="preserve">TG 54:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P68510</t>
+    <t xml:space="preserve">P24270</t>
   </si>
   <si>
     <t xml:space="preserve">Q9D176</t>
@@ -4390,7 +4390,7 @@
     <t xml:space="preserve">PA 16:0_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P24270</t>
+    <t xml:space="preserve">Q9D1G1</t>
   </si>
   <si>
     <t xml:space="preserve">Q689Z5</t>
@@ -4402,7 +4402,7 @@
     <t xml:space="preserve">PA 18:0_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D1G1</t>
+    <t xml:space="preserve">O35658</t>
   </si>
   <si>
     <t xml:space="preserve">Q9JMH6</t>
@@ -4411,7 +4411,7 @@
     <t xml:space="preserve">TG 54:6</t>
   </si>
   <si>
-    <t xml:space="preserve">O35658</t>
+    <t xml:space="preserve">Q8BYU6</t>
   </si>
   <si>
     <t xml:space="preserve">Q8C156</t>
@@ -4423,7 +4423,7 @@
     <t xml:space="preserve">PA 18:1_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BYU6</t>
+    <t xml:space="preserve">O55222</t>
   </si>
   <si>
     <t xml:space="preserve">P11835</t>
@@ -4432,7 +4432,7 @@
     <t xml:space="preserve">TG 56:5</t>
   </si>
   <si>
-    <t xml:space="preserve">O55222</t>
+    <t xml:space="preserve">Q9CQ92</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BJS4</t>
@@ -4444,7 +4444,7 @@
     <t xml:space="preserve">LPG 18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQ92</t>
+    <t xml:space="preserve">P31324</t>
   </si>
   <si>
     <t xml:space="preserve">Q80W04</t>
@@ -4453,7 +4453,7 @@
     <t xml:space="preserve">TG 58:6</t>
   </si>
   <si>
-    <t xml:space="preserve">P31324</t>
+    <t xml:space="preserve">Q8R404</t>
   </si>
   <si>
     <t xml:space="preserve">Q60854</t>
@@ -4462,7 +4462,7 @@
     <t xml:space="preserve">TG 58:7</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8R404</t>
+    <t xml:space="preserve">P56391</t>
   </si>
   <si>
     <t xml:space="preserve">Q05144</t>
@@ -4474,7 +4474,7 @@
     <t xml:space="preserve">LPG 20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P56391</t>
+    <t xml:space="preserve">Q9CQW9</t>
   </si>
   <si>
     <t xml:space="preserve">Q3UZA1</t>
@@ -4486,7 +4486,7 @@
     <t xml:space="preserve">LPG 20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQW9</t>
+    <t xml:space="preserve">B2RPV6</t>
   </si>
   <si>
     <t xml:space="preserve">P04117</t>
@@ -4495,7 +4495,7 @@
     <t xml:space="preserve">LPG 22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">B2RPV6</t>
+    <t xml:space="preserve">Q9D892</t>
   </si>
   <si>
     <t xml:space="preserve">O88536</t>
@@ -4504,7 +4504,7 @@
     <t xml:space="preserve">DG 16:0_16:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D892</t>
+    <t xml:space="preserve">P46460</t>
   </si>
   <si>
     <t xml:space="preserve">Q64105</t>
@@ -4513,7 +4513,7 @@
     <t xml:space="preserve">DG 16:0_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P46460</t>
+    <t xml:space="preserve">Q99M04</t>
   </si>
   <si>
     <t xml:space="preserve">P70335</t>
@@ -4522,7 +4522,7 @@
     <t xml:space="preserve">CL 72:7</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99M04</t>
+    <t xml:space="preserve">Q8BMJ3</t>
   </si>
   <si>
     <t xml:space="preserve">F7BJB9</t>
@@ -4531,19 +4531,19 @@
     <t xml:space="preserve">DG 16:0_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BMJ3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6PZD9</t>
   </si>
   <si>
+    <t xml:space="preserve">P70158</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9D6N1</t>
   </si>
   <si>
     <t xml:space="preserve">DG 16:0_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P70158</t>
+    <t xml:space="preserve">Q9DCX2</t>
   </si>
   <si>
     <t xml:space="preserve">P35601</t>
@@ -4552,19 +4552,19 @@
     <t xml:space="preserve">DG 16:0_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9DCX2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9QZ08</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9CQX8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9D6Y7</t>
   </si>
   <si>
     <t xml:space="preserve">DG 16:1_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQX8</t>
+    <t xml:space="preserve">Q8QZT1</t>
   </si>
   <si>
     <t xml:space="preserve">Q921M7</t>
@@ -4573,7 +4573,7 @@
     <t xml:space="preserve">DG 16:2_16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8QZT1</t>
+    <t xml:space="preserve">Q9ES28</t>
   </si>
   <si>
     <t xml:space="preserve">P28293</t>
@@ -4582,37 +4582,37 @@
     <t xml:space="preserve">DG 18:0_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9ES28</t>
+    <t xml:space="preserve">P57759</t>
   </si>
   <si>
     <t xml:space="preserve">P19973</t>
   </si>
   <si>
-    <t xml:space="preserve">P57759</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9JKY5</t>
   </si>
   <si>
+    <t xml:space="preserve">Q6ZPZ3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q99MK8</t>
   </si>
   <si>
     <t xml:space="preserve">DG 18:0_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6ZPZ3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9CXS4</t>
   </si>
   <si>
     <t xml:space="preserve">DG 18:0_20:4</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9WTP7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q61550</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WTP7</t>
+    <t xml:space="preserve">Q6ZPJ0</t>
   </si>
   <si>
     <t xml:space="preserve">Q91V01</t>
@@ -4621,7 +4621,7 @@
     <t xml:space="preserve">DG 18:1_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6ZPJ0</t>
+    <t xml:space="preserve">O08848</t>
   </si>
   <si>
     <t xml:space="preserve">Q62315</t>
@@ -4630,7 +4630,7 @@
     <t xml:space="preserve">DG 18:1_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">O08848</t>
+    <t xml:space="preserve">P23188</t>
   </si>
   <si>
     <t xml:space="preserve">Q8K3G9</t>
@@ -4639,7 +4639,7 @@
     <t xml:space="preserve">DG 18:2_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P23188</t>
+    <t xml:space="preserve">O54774</t>
   </si>
   <si>
     <t xml:space="preserve">Q99JW1</t>
@@ -4648,7 +4648,7 @@
     <t xml:space="preserve">DG 20:2_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">O54774</t>
+    <t xml:space="preserve">Q8VCX5</t>
   </si>
   <si>
     <t xml:space="preserve">P40142</t>
@@ -4657,7 +4657,7 @@
     <t xml:space="preserve">DG 20:4_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8VCX5</t>
+    <t xml:space="preserve">D3Z7P3</t>
   </si>
   <si>
     <t xml:space="preserve">Q91XL9</t>
@@ -4666,7 +4666,7 @@
     <t xml:space="preserve">PS 14:0_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">D3Z7P3</t>
+    <t xml:space="preserve">P37040</t>
   </si>
   <si>
     <t xml:space="preserve">Q9QY73</t>
@@ -4675,7 +4675,7 @@
     <t xml:space="preserve">PS 14:0_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P37040</t>
+    <t xml:space="preserve">P35441</t>
   </si>
   <si>
     <t xml:space="preserve">Q7TN75</t>
@@ -4684,7 +4684,7 @@
     <t xml:space="preserve">PS 14:1_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P35441</t>
+    <t xml:space="preserve">Q64433</t>
   </si>
   <si>
     <t xml:space="preserve">Q64701</t>
@@ -4693,13 +4693,13 @@
     <t xml:space="preserve">PS 16:0_16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q64433</t>
+    <t xml:space="preserve">E9Q6P5</t>
   </si>
   <si>
     <t xml:space="preserve">Q9D2V7</t>
   </si>
   <si>
-    <t xml:space="preserve">E9Q6P5</t>
+    <t xml:space="preserve">O89001</t>
   </si>
   <si>
     <t xml:space="preserve">Q3TGF2</t>
@@ -4708,7 +4708,7 @@
     <t xml:space="preserve">PS 16:0_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">O89001</t>
+    <t xml:space="preserve">Q6P5E6</t>
   </si>
   <si>
     <t xml:space="preserve">Q9QYC0</t>
@@ -4717,7 +4717,7 @@
     <t xml:space="preserve">PS 16:0_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6P5E6</t>
+    <t xml:space="preserve">Q99104</t>
   </si>
   <si>
     <t xml:space="preserve">Q8R3V6</t>
@@ -4726,34 +4726,34 @@
     <t xml:space="preserve">PS 16:0_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99104</t>
-  </si>
-  <si>
     <t xml:space="preserve">B1AXH1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9JJF9</t>
+  </si>
+  <si>
     <t xml:space="preserve">P25206</t>
   </si>
   <si>
     <t xml:space="preserve">PS 16:0_22:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JJF9</t>
+    <t xml:space="preserve">Q01237</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BXA5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q01237</t>
-  </si>
-  <si>
     <t xml:space="preserve">P15626</t>
   </si>
   <si>
+    <t xml:space="preserve">P11688</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9D7B7</t>
   </si>
   <si>
-    <t xml:space="preserve">P11688</t>
+    <t xml:space="preserve">P42859</t>
   </si>
   <si>
     <t xml:space="preserve">Q09200</t>
@@ -4762,7 +4762,7 @@
     <t xml:space="preserve">PS 16:1_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P42859</t>
+    <t xml:space="preserve">P56812</t>
   </si>
   <si>
     <t xml:space="preserve">O70293</t>
@@ -4771,7 +4771,7 @@
     <t xml:space="preserve">PS 16:1_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P56812</t>
+    <t xml:space="preserve">Q9CQA5</t>
   </si>
   <si>
     <t xml:space="preserve">Q78IQ7</t>
@@ -4780,13 +4780,13 @@
     <t xml:space="preserve">PS 16:1_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQA5</t>
+    <t xml:space="preserve">Q9CYH2</t>
   </si>
   <si>
     <t xml:space="preserve">Q9R0N3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CYH2</t>
+    <t xml:space="preserve">Q62219</t>
   </si>
   <si>
     <t xml:space="preserve">Q61335</t>
@@ -4795,7 +4795,7 @@
     <t xml:space="preserve">PS 16:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q62219</t>
+    <t xml:space="preserve">Q5I012</t>
   </si>
   <si>
     <t xml:space="preserve">P10107</t>
@@ -4804,7 +4804,7 @@
     <t xml:space="preserve">PS 16:1_22:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q5I012</t>
+    <t xml:space="preserve">Q8R0G7</t>
   </si>
   <si>
     <t xml:space="preserve">P58137</t>
@@ -4813,22 +4813,22 @@
     <t xml:space="preserve">PS 16:1_22:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8R0G7</t>
-  </si>
-  <si>
     <t xml:space="preserve">P70460</t>
   </si>
   <si>
     <t xml:space="preserve">PS 16:1_22:3</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9R0M6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q99J56</t>
   </si>
   <si>
     <t xml:space="preserve">PS 16:1_24:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9R0M6</t>
+    <t xml:space="preserve">Q3TC72</t>
   </si>
   <si>
     <t xml:space="preserve">P97814</t>
@@ -4837,49 +4837,49 @@
     <t xml:space="preserve">PS 16:2_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3TC72</t>
+    <t xml:space="preserve">Q9WTP6</t>
   </si>
   <si>
     <t xml:space="preserve">O89053</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WTP6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8VIB3</t>
   </si>
   <si>
     <t xml:space="preserve">PS 17:1_17:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9JIG8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9JL95</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JIG8</t>
+    <t xml:space="preserve">Q91WQ3</t>
   </si>
   <si>
     <t xml:space="preserve">Q9R0P5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q91WQ3</t>
+    <t xml:space="preserve">O88186</t>
   </si>
   <si>
     <t xml:space="preserve">P11247</t>
   </si>
   <si>
-    <t xml:space="preserve">O88186</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8VD75</t>
   </si>
   <si>
+    <t xml:space="preserve">Q80ZJ1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8K354</t>
   </si>
   <si>
     <t xml:space="preserve">PS 18:0_24:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q80ZJ1</t>
+    <t xml:space="preserve">O70370</t>
   </si>
   <si>
     <t xml:space="preserve">Q8CHP8</t>
@@ -4888,31 +4888,31 @@
     <t xml:space="preserve">PS 18:1_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">O70370</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6SJQ7</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8CIZ8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8R550</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8CIZ8</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q61599</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9DCT1</t>
+  </si>
+  <si>
     <t xml:space="preserve">P35969</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9DCT1</t>
+    <t xml:space="preserve">Q8K558</t>
   </si>
   <si>
     <t xml:space="preserve">Q811M1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8K558</t>
+    <t xml:space="preserve">P10852</t>
   </si>
   <si>
     <t xml:space="preserve">Q9WVJ3</t>
@@ -4921,46 +4921,46 @@
     <t xml:space="preserve">PS 18:1_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P10852</t>
+    <t xml:space="preserve">P62900</t>
   </si>
   <si>
     <t xml:space="preserve">P68433</t>
   </si>
   <si>
-    <t xml:space="preserve">P62900</t>
+    <t xml:space="preserve">Q920Q6</t>
   </si>
   <si>
     <t xml:space="preserve">Q4PJX1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q920Q6</t>
+    <t xml:space="preserve">Q9JL99</t>
   </si>
   <si>
     <t xml:space="preserve">Q7TMQ7</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JL99</t>
+    <t xml:space="preserve">Q99P58</t>
   </si>
   <si>
     <t xml:space="preserve">P97447</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99P58</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q3V300</t>
   </si>
   <si>
     <t xml:space="preserve">PS 18:2_18:0</t>
   </si>
   <si>
+    <t xml:space="preserve">O89103</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9Z2W0</t>
   </si>
   <si>
     <t xml:space="preserve">PS 18:2_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">O89103</t>
+    <t xml:space="preserve">Q62469</t>
   </si>
   <si>
     <t xml:space="preserve">Q99J62</t>
@@ -4969,22 +4969,22 @@
     <t xml:space="preserve">PS 18:2_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q62469</t>
-  </si>
-  <si>
     <t xml:space="preserve">P59108</t>
   </si>
   <si>
     <t xml:space="preserve">PS 18:2_20:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9CY27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9ERG0</t>
   </si>
   <si>
     <t xml:space="preserve">PS 18:2_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CY27</t>
+    <t xml:space="preserve">Q9R0A0</t>
   </si>
   <si>
     <t xml:space="preserve">P16110</t>
@@ -4993,9 +4993,6 @@
     <t xml:space="preserve">PS 18:2_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9R0A0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9ERL7</t>
   </si>
   <si>
@@ -5008,25 +5005,28 @@
     <t xml:space="preserve">PS 18:2_22:5</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9QUM0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q62393</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QUM0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8K078</t>
   </si>
   <si>
     <t xml:space="preserve">PS 18:3_22:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q6PDL0</t>
+  </si>
+  <si>
     <t xml:space="preserve">O08579</t>
   </si>
   <si>
     <t xml:space="preserve">PS 20:2_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6PDL0</t>
+    <t xml:space="preserve">Q61490</t>
   </si>
   <si>
     <t xml:space="preserve">Q8K0B2</t>
@@ -5035,19 +5035,19 @@
     <t xml:space="preserve">PS 20:3_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61490</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9DCT5</t>
   </si>
   <si>
+    <t xml:space="preserve">P97287</t>
+  </si>
+  <si>
     <t xml:space="preserve">P43277</t>
   </si>
   <si>
     <t xml:space="preserve">PS 20:4_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P97287</t>
+    <t xml:space="preserve">Q9QYR9</t>
   </si>
   <si>
     <t xml:space="preserve">Q920L1</t>
@@ -5056,7 +5056,7 @@
     <t xml:space="preserve">PS 20:4_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QYR9</t>
+    <t xml:space="preserve">Q7TN98</t>
   </si>
   <si>
     <t xml:space="preserve">Q3TRM4</t>
@@ -5065,16 +5065,16 @@
     <t xml:space="preserve">PS 20:4_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q7TN98</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9QZM0</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9ESW8</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q91VI7</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9ESW8</t>
+    <t xml:space="preserve">Q9D3X9</t>
   </si>
   <si>
     <t xml:space="preserve">Q91Z96</t>
@@ -5083,25 +5083,25 @@
     <t xml:space="preserve">PI 16:0_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D3X9</t>
+    <t xml:space="preserve">Q8JZK9</t>
   </si>
   <si>
     <t xml:space="preserve">Q80X41</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8JZK9</t>
+    <t xml:space="preserve">Q3T9M1</t>
   </si>
   <si>
     <t xml:space="preserve">Q9WUT3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3T9M1</t>
+    <t xml:space="preserve">Q02111</t>
   </si>
   <si>
     <t xml:space="preserve">O08663</t>
   </si>
   <si>
-    <t xml:space="preserve">Q02111</t>
+    <t xml:space="preserve">O88792</t>
   </si>
   <si>
     <t xml:space="preserve">Q8R0W6</t>
@@ -5110,7 +5110,7 @@
     <t xml:space="preserve">PI 16:0_22:5</t>
   </si>
   <si>
-    <t xml:space="preserve">O88792</t>
+    <t xml:space="preserve">Q61009</t>
   </si>
   <si>
     <t xml:space="preserve">Q68FH4</t>
@@ -5119,13 +5119,13 @@
     <t xml:space="preserve">PI 17:0_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61009</t>
+    <t xml:space="preserve">Q64131</t>
   </si>
   <si>
     <t xml:space="preserve">P56477</t>
   </si>
   <si>
-    <t xml:space="preserve">Q64131</t>
+    <t xml:space="preserve">Q61391</t>
   </si>
   <si>
     <t xml:space="preserve">P28660</t>
@@ -5134,7 +5134,7 @@
     <t xml:space="preserve">PI 18:0_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61391</t>
+    <t xml:space="preserve">Q9DCS3</t>
   </si>
   <si>
     <t xml:space="preserve">O89017</t>
@@ -5143,7 +5143,7 @@
     <t xml:space="preserve">PI 18:0_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9DCS3</t>
+    <t xml:space="preserve">Q3TSG4</t>
   </si>
   <si>
     <t xml:space="preserve">O88986</t>
@@ -5152,25 +5152,25 @@
     <t xml:space="preserve">PI 18:0_18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3TSG4</t>
+    <t xml:space="preserve">P11152</t>
   </si>
   <si>
     <t xml:space="preserve">Q8QZZ8</t>
   </si>
   <si>
-    <t xml:space="preserve">P11152</t>
+    <t xml:space="preserve">Q9D1H6</t>
   </si>
   <si>
     <t xml:space="preserve">O55023</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D1H6</t>
+    <t xml:space="preserve">Q148V7</t>
   </si>
   <si>
     <t xml:space="preserve">P48036</t>
   </si>
   <si>
-    <t xml:space="preserve">Q148V7</t>
+    <t xml:space="preserve">Q9DCZ1</t>
   </si>
   <si>
     <t xml:space="preserve">O35604</t>
@@ -5179,7 +5179,7 @@
     <t xml:space="preserve">PI 18:0_20:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9DCZ1</t>
+    <t xml:space="preserve">Q61321</t>
   </si>
   <si>
     <t xml:space="preserve">P54276</t>
@@ -5188,15 +5188,12 @@
     <t xml:space="preserve">PI 18:0_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61321</t>
+    <t xml:space="preserve">Q9CQR4</t>
   </si>
   <si>
     <t xml:space="preserve">P28271</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQR4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q61033</t>
   </si>
   <si>
@@ -5206,13 +5203,16 @@
     <t xml:space="preserve">Q64669</t>
   </si>
   <si>
+    <t xml:space="preserve">P40240</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9CY64</t>
   </si>
   <si>
     <t xml:space="preserve">PI 18:1_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P40240</t>
+    <t xml:space="preserve">Q99LG4</t>
   </si>
   <si>
     <t xml:space="preserve">P98156</t>
@@ -5221,13 +5221,13 @@
     <t xml:space="preserve">PI 18:1_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99LG4</t>
+    <t xml:space="preserve">Q6PGL7</t>
   </si>
   <si>
     <t xml:space="preserve">P35700</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6PGL7</t>
+    <t xml:space="preserve">O54890</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BYY9</t>
@@ -5236,7 +5236,7 @@
     <t xml:space="preserve">PI 18:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">O54890</t>
+    <t xml:space="preserve">Q9D4H1</t>
   </si>
   <si>
     <t xml:space="preserve">Q9DCN2</t>
@@ -5245,19 +5245,19 @@
     <t xml:space="preserve">PI 18:1_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D4H1</t>
+    <t xml:space="preserve">P60603</t>
   </si>
   <si>
     <t xml:space="preserve">P51830</t>
   </si>
   <si>
-    <t xml:space="preserve">P60603</t>
+    <t xml:space="preserve">P11881</t>
   </si>
   <si>
     <t xml:space="preserve">P05063</t>
   </si>
   <si>
-    <t xml:space="preserve">P11881</t>
+    <t xml:space="preserve">Q6PB93</t>
   </si>
   <si>
     <t xml:space="preserve">Q61686</t>
@@ -5266,7 +5266,7 @@
     <t xml:space="preserve">PI 18:2_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6PB93</t>
+    <t xml:space="preserve">Q99P65</t>
   </si>
   <si>
     <t xml:space="preserve">P58064</t>
@@ -5275,22 +5275,22 @@
     <t xml:space="preserve">PI 19:1_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99P65</t>
-  </si>
-  <si>
     <t xml:space="preserve">P16125</t>
   </si>
   <si>
     <t xml:space="preserve">PI 20:0_20:3</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8K021</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q61576</t>
   </si>
   <si>
     <t xml:space="preserve">PI 20:1_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8K021</t>
+    <t xml:space="preserve">P51125</t>
   </si>
   <si>
     <t xml:space="preserve">Q9R1S3</t>
@@ -5299,7 +5299,7 @@
     <t xml:space="preserve">PI 20:1_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P51125</t>
+    <t xml:space="preserve">P70302</t>
   </si>
   <si>
     <t xml:space="preserve">P33609</t>
@@ -5308,43 +5308,43 @@
     <t xml:space="preserve">PI 20:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P70302</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q64455</t>
   </si>
   <si>
     <t xml:space="preserve">PI 20:2_20:2</t>
   </si>
   <si>
+    <t xml:space="preserve">P31786</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9JJ00</t>
   </si>
   <si>
     <t xml:space="preserve">PI 20:2_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P31786</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6YGZ1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q99P72</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q6DIA2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99P72</t>
+    <t xml:space="preserve">Q810V0</t>
   </si>
   <si>
     <t xml:space="preserve">Q8CAA7</t>
   </si>
   <si>
-    <t xml:space="preserve">Q810V0</t>
+    <t xml:space="preserve">P06797</t>
   </si>
   <si>
     <t xml:space="preserve">Q99KC8</t>
   </si>
   <si>
-    <t xml:space="preserve">P06797</t>
+    <t xml:space="preserve">Q8C0P5</t>
   </si>
   <si>
     <t xml:space="preserve">Q8R0Y6</t>
@@ -5353,7 +5353,7 @@
     <t xml:space="preserve">PE O-18:0/18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8C0P5</t>
+    <t xml:space="preserve">Q60790</t>
   </si>
   <si>
     <t xml:space="preserve">Q60780</t>
@@ -5362,7 +5362,7 @@
     <t xml:space="preserve">PE O-18:0/20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q60790</t>
+    <t xml:space="preserve">Q80X85</t>
   </si>
   <si>
     <t xml:space="preserve">Q9JHF7</t>
@@ -5371,7 +5371,7 @@
     <t xml:space="preserve">PE O-18:0/20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q80X85</t>
+    <t xml:space="preserve">Q9WUX5</t>
   </si>
   <si>
     <t xml:space="preserve">Q9Z1G4</t>
@@ -5380,69 +5380,66 @@
     <t xml:space="preserve">PE O-18:0/20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WUX5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8BJU2</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-18:0/22:4</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9D8V0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q6PFQ7</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-18:0/22:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D8V0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8K0Q5</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-18:1/16:1</t>
   </si>
   <si>
+    <t xml:space="preserve">P35951</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q9R0B9</t>
   </si>
   <si>
-    <t xml:space="preserve">P35951</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q64521</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-18:1/22:2</t>
   </si>
   <si>
+    <t xml:space="preserve">Q62086</t>
+  </si>
+  <si>
     <t xml:space="preserve">P34884</t>
   </si>
   <si>
-    <t xml:space="preserve">Q62086</t>
+    <t xml:space="preserve">A2CG49</t>
   </si>
   <si>
     <t xml:space="preserve">Q8C0E3</t>
   </si>
   <si>
-    <t xml:space="preserve">A2CG49</t>
-  </si>
-  <si>
     <t xml:space="preserve">P39876</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-18:2/19:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q99LM2</t>
+  </si>
+  <si>
     <t xml:space="preserve">P19258</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-18:2/20:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99LM2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9Z183</t>
   </si>
   <si>
@@ -5455,25 +5452,28 @@
     <t xml:space="preserve">PE O-18:2/22:2</t>
   </si>
   <si>
+    <t xml:space="preserve">Q3UI43</t>
+  </si>
+  <si>
     <t xml:space="preserve">O54865</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3UI43</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9EQP2</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-20:0/22:5</t>
   </si>
   <si>
+    <t xml:space="preserve">Q6P9Q4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q80XU3</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-20:1/18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6P9Q4</t>
+    <t xml:space="preserve">Q9CPR5</t>
   </si>
   <si>
     <t xml:space="preserve">Q9QZB7</t>
@@ -5482,7 +5482,7 @@
     <t xml:space="preserve">PE O-20:1/20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CPR5</t>
+    <t xml:space="preserve">Q7M759</t>
   </si>
   <si>
     <t xml:space="preserve">Q9JKK1</t>
@@ -5491,7 +5491,7 @@
     <t xml:space="preserve">PE O-20:1/20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q7M759</t>
+    <t xml:space="preserve">Q8BTI8</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BRU6</t>
@@ -5500,31 +5500,31 @@
     <t xml:space="preserve">PE O-20:1/22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BTI8</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8CE50</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8BYP3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q91YJ2</t>
   </si>
   <si>
     <t xml:space="preserve">PE O-20:1/22:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BYP3</t>
+    <t xml:space="preserve">E9Q137</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BTY2</t>
   </si>
   <si>
-    <t xml:space="preserve">E9Q137</t>
+    <t xml:space="preserve">P58044</t>
   </si>
   <si>
     <t xml:space="preserve">Q3V384</t>
   </si>
   <si>
-    <t xml:space="preserve">P58044</t>
+    <t xml:space="preserve">P21836</t>
   </si>
   <si>
     <t xml:space="preserve">Q3UZ39</t>
@@ -5533,7 +5533,7 @@
     <t xml:space="preserve">PE 14:0_14:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P21836</t>
+    <t xml:space="preserve">Q63918</t>
   </si>
   <si>
     <t xml:space="preserve">Q6NZQ4</t>
@@ -5542,15 +5542,12 @@
     <t xml:space="preserve">PE 14:0_16:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q63918</t>
+    <t xml:space="preserve">Q06890</t>
   </si>
   <si>
     <t xml:space="preserve">Q9R0P3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q06890</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8BH02</t>
   </si>
   <si>
@@ -5575,31 +5572,34 @@
     <t xml:space="preserve">PE 14:1_18:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Q6PGH2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8K0E8</t>
   </si>
   <si>
     <t xml:space="preserve">PE 14:1_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6PGH2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8CFE2</t>
   </si>
   <si>
     <t xml:space="preserve">PE 14:1_22:4</t>
   </si>
   <si>
+    <t xml:space="preserve">Q99LP6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8BZ03</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99LP6</t>
+    <t xml:space="preserve">Q8CG19</t>
   </si>
   <si>
     <t xml:space="preserve">Q99N69</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8CG19</t>
+    <t xml:space="preserve">A1L314</t>
   </si>
   <si>
     <t xml:space="preserve">Q9D1A2</t>
@@ -5608,67 +5608,67 @@
     <t xml:space="preserve">PE 16:0_16:2</t>
   </si>
   <si>
-    <t xml:space="preserve">A1L314</t>
+    <t xml:space="preserve">Q9R0H0</t>
   </si>
   <si>
     <t xml:space="preserve">Q04447</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9R0H0</t>
-  </si>
-  <si>
     <t xml:space="preserve">P53690</t>
   </si>
   <si>
     <t xml:space="preserve">Q9ER00</t>
   </si>
   <si>
+    <t xml:space="preserve">Q61263</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q01341</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61263</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6A065</t>
   </si>
   <si>
+    <t xml:space="preserve">Q60604</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8BRH0</t>
   </si>
   <si>
     <t xml:space="preserve">PE 16:0_22:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q60604</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8C708</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9QY76</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q62159</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QY76</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q64261</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9QX15</t>
+  </si>
+  <si>
     <t xml:space="preserve">P21956</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QX15</t>
+    <t xml:space="preserve">P39655</t>
   </si>
   <si>
     <t xml:space="preserve">P16675</t>
   </si>
   <si>
-    <t xml:space="preserve">P39655</t>
+    <t xml:space="preserve">Q6P5D4</t>
   </si>
   <si>
     <t xml:space="preserve">A2AAY5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6P5D4</t>
+    <t xml:space="preserve">P14753</t>
   </si>
   <si>
     <t xml:space="preserve">Q61147</t>
@@ -5677,13 +5677,13 @@
     <t xml:space="preserve">PE 16:1_18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P14753</t>
+    <t xml:space="preserve">Q64337</t>
   </si>
   <si>
     <t xml:space="preserve">Q8K183</t>
   </si>
   <si>
-    <t xml:space="preserve">Q64337</t>
+    <t xml:space="preserve">P51912</t>
   </si>
   <si>
     <t xml:space="preserve">Q9CWF2</t>
@@ -5692,7 +5692,7 @@
     <t xml:space="preserve">PE 16:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P51912</t>
+    <t xml:space="preserve">Q9QXY6</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BU33</t>
@@ -5701,19 +5701,19 @@
     <t xml:space="preserve">PE 16:1_22:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QXY6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8K297</t>
   </si>
   <si>
+    <t xml:space="preserve">Q924T2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q60634</t>
   </si>
   <si>
     <t xml:space="preserve">PE 16:2_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q924T2</t>
+    <t xml:space="preserve">A2AQ07</t>
   </si>
   <si>
     <t xml:space="preserve">Q3V1T4</t>
@@ -5722,7 +5722,7 @@
     <t xml:space="preserve">PE 16:2_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">A2AQ07</t>
+    <t xml:space="preserve">Q9JLC8</t>
   </si>
   <si>
     <t xml:space="preserve">Q9EP71</t>
@@ -5731,7 +5731,7 @@
     <t xml:space="preserve">PE 16:2_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JLC8</t>
+    <t xml:space="preserve">P19467</t>
   </si>
   <si>
     <t xml:space="preserve">Q4PZA2</t>
@@ -5740,7 +5740,7 @@
     <t xml:space="preserve">PE 16:3_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P19467</t>
+    <t xml:space="preserve">Q0GNC1</t>
   </si>
   <si>
     <t xml:space="preserve">Q9D020</t>
@@ -5749,85 +5749,85 @@
     <t xml:space="preserve">PE 16:3_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q0GNC1</t>
+    <t xml:space="preserve">Q8VHL0</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BHS6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8VHL0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9WTS2</t>
   </si>
   <si>
     <t xml:space="preserve">PE 18:0_18:2</t>
   </si>
   <si>
+    <t xml:space="preserve">P39061</t>
+  </si>
+  <si>
     <t xml:space="preserve">P53798</t>
   </si>
   <si>
-    <t xml:space="preserve">P39061</t>
+    <t xml:space="preserve">Q8VC57</t>
   </si>
   <si>
     <t xml:space="preserve">Q9R0E2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8VC57</t>
+    <t xml:space="preserve">Q99P91</t>
   </si>
   <si>
     <t xml:space="preserve">E9Q634</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99P91</t>
+    <t xml:space="preserve">Q9QZ47</t>
   </si>
   <si>
     <t xml:space="preserve">Q6BCL1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9QZ47</t>
+    <t xml:space="preserve">P97457</t>
   </si>
   <si>
     <t xml:space="preserve">P43406</t>
   </si>
   <si>
-    <t xml:space="preserve">P97457</t>
+    <t xml:space="preserve">Q91Z98</t>
   </si>
   <si>
     <t xml:space="preserve">O08605</t>
   </si>
   <si>
-    <t xml:space="preserve">Q91Z98</t>
+    <t xml:space="preserve">Q69ZU6</t>
   </si>
   <si>
     <t xml:space="preserve">Q9JII6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q69ZU6</t>
+    <t xml:space="preserve">P58774</t>
   </si>
   <si>
     <t xml:space="preserve">Q5SRX1</t>
   </si>
   <si>
-    <t xml:space="preserve">P58774</t>
+    <t xml:space="preserve">P62322</t>
   </si>
   <si>
     <t xml:space="preserve">Q05816</t>
   </si>
   <si>
-    <t xml:space="preserve">P62322</t>
+    <t xml:space="preserve">P13412</t>
   </si>
   <si>
     <t xml:space="preserve">Q8VDC0</t>
   </si>
   <si>
-    <t xml:space="preserve">P13412</t>
+    <t xml:space="preserve">Q9CZ69</t>
   </si>
   <si>
     <t xml:space="preserve">Q64331</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CZ69</t>
+    <t xml:space="preserve">P01631</t>
   </si>
   <si>
     <t xml:space="preserve">Q69ZA1</t>
@@ -5836,37 +5836,37 @@
     <t xml:space="preserve">PE 18:1_18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P01631</t>
+    <t xml:space="preserve">Q9DBV3</t>
   </si>
   <si>
     <t xml:space="preserve">P10833</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9DBV3</t>
+    <t xml:space="preserve">O88990</t>
   </si>
   <si>
     <t xml:space="preserve">Q9Z0R9</t>
   </si>
   <si>
-    <t xml:space="preserve">O88990</t>
+    <t xml:space="preserve">Q8C8U0</t>
   </si>
   <si>
     <t xml:space="preserve">P97429</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8C8U0</t>
+    <t xml:space="preserve">Q9D8I1</t>
   </si>
   <si>
     <t xml:space="preserve">Q9QYI4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D8I1</t>
+    <t xml:space="preserve">Q9Z222</t>
   </si>
   <si>
     <t xml:space="preserve">Q2TBE6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9Z222</t>
+    <t xml:space="preserve">P14429</t>
   </si>
   <si>
     <t xml:space="preserve">Q64373</t>
@@ -5875,19 +5875,19 @@
     <t xml:space="preserve">PE 18:2_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P14429</t>
+    <t xml:space="preserve">Q5XKE0</t>
   </si>
   <si>
     <t xml:space="preserve">Q91XL3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q5XKE0</t>
+    <t xml:space="preserve">P01639</t>
   </si>
   <si>
     <t xml:space="preserve">Q91YR1</t>
   </si>
   <si>
-    <t xml:space="preserve">P01639</t>
+    <t xml:space="preserve">Q01149</t>
   </si>
   <si>
     <t xml:space="preserve">Q80VA0</t>
@@ -5896,7 +5896,7 @@
     <t xml:space="preserve">PE 20:0_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q01149</t>
+    <t xml:space="preserve">Q9JLN5</t>
   </si>
   <si>
     <t xml:space="preserve">P21300</t>
@@ -5905,7 +5905,7 @@
     <t xml:space="preserve">PE 20:1_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JLN5</t>
+    <t xml:space="preserve">E9Q2M9</t>
   </si>
   <si>
     <t xml:space="preserve">P97449</t>
@@ -5914,7 +5914,7 @@
     <t xml:space="preserve">PE 20:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">E9Q2M9</t>
+    <t xml:space="preserve">Q80WS3</t>
   </si>
   <si>
     <t xml:space="preserve">P70704</t>
@@ -5923,7 +5923,7 @@
     <t xml:space="preserve">PE 20:1_22:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q80WS3</t>
+    <t xml:space="preserve">P06330</t>
   </si>
   <si>
     <t xml:space="preserve">Q07235</t>
@@ -5932,7 +5932,7 @@
     <t xml:space="preserve">PE 20:2_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P06330</t>
+    <t xml:space="preserve">P17679</t>
   </si>
   <si>
     <t xml:space="preserve">Q8BRK9</t>
@@ -5941,7 +5941,7 @@
     <t xml:space="preserve">PE 20:2_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P17679</t>
+    <t xml:space="preserve">P97930</t>
   </si>
   <si>
     <t xml:space="preserve">Q8R059</t>
@@ -5950,7 +5950,7 @@
     <t xml:space="preserve">PE 20:2_22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P97930</t>
+    <t xml:space="preserve">P35329</t>
   </si>
   <si>
     <t xml:space="preserve">Q69ZN7</t>
@@ -5959,7 +5959,7 @@
     <t xml:space="preserve">PE 20:3_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P35329</t>
+    <t xml:space="preserve">P05977</t>
   </si>
   <si>
     <t xml:space="preserve">O35930</t>
@@ -5968,7 +5968,7 @@
     <t xml:space="preserve">PE 20:4_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P05977</t>
+    <t xml:space="preserve">Q9CVD2</t>
   </si>
   <si>
     <t xml:space="preserve">Q80YR4</t>
@@ -5977,19 +5977,19 @@
     <t xml:space="preserve">PC O-14:0/16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CVD2</t>
+    <t xml:space="preserve">Q5XG71</t>
   </si>
   <si>
     <t xml:space="preserve">P30999</t>
   </si>
   <si>
-    <t xml:space="preserve">Q5XG71</t>
+    <t xml:space="preserve">Q9D0M2</t>
   </si>
   <si>
     <t xml:space="preserve">P39688</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D0M2</t>
+    <t xml:space="preserve">P59328</t>
   </si>
   <si>
     <t xml:space="preserve">P30412</t>
@@ -5998,7 +5998,7 @@
     <t xml:space="preserve">PC O-16:0/20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P59328</t>
+    <t xml:space="preserve">Q99KP3</t>
   </si>
   <si>
     <t xml:space="preserve">Q3V0K9</t>
@@ -6007,7 +6007,7 @@
     <t xml:space="preserve">PC O-16:0/22:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99KP3</t>
+    <t xml:space="preserve">Q3UP87</t>
   </si>
   <si>
     <t xml:space="preserve">P63141</t>
@@ -6016,22 +6016,22 @@
     <t xml:space="preserve">PC O-16:1/16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3UP87</t>
-  </si>
-  <si>
     <t xml:space="preserve">P61226</t>
   </si>
   <si>
     <t xml:space="preserve">PC O-16:1/16:1</t>
   </si>
   <si>
+    <t xml:space="preserve">P31809</t>
+  </si>
+  <si>
     <t xml:space="preserve">Q8R1F1</t>
   </si>
   <si>
     <t xml:space="preserve">PC O-16:1/18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">P31809</t>
+    <t xml:space="preserve">Q9CPU4</t>
   </si>
   <si>
     <t xml:space="preserve">P20444</t>
@@ -6040,15 +6040,12 @@
     <t xml:space="preserve">PC O-16:2/16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CPU4</t>
+    <t xml:space="preserve">P0DP28</t>
   </si>
   <si>
     <t xml:space="preserve">P12388</t>
   </si>
   <si>
-    <t xml:space="preserve">P0DP28</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8CHG3</t>
   </si>
   <si>
@@ -6061,30 +6058,30 @@
     <t xml:space="preserve">Q91X96</t>
   </si>
   <si>
+    <t xml:space="preserve">P39654</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC O-18:2/18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P39654</t>
-  </si>
-  <si>
     <t xml:space="preserve">O70497</t>
   </si>
   <si>
     <t xml:space="preserve">Q3UL36</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9Z280</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC 14:0_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9Z280</t>
+    <t xml:space="preserve">P52431</t>
   </si>
   <si>
     <t xml:space="preserve">PC 14:0_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P52431</t>
-  </si>
-  <si>
     <t xml:space="preserve">P70255</t>
   </si>
   <si>
@@ -6100,9 +6097,6 @@
     <t xml:space="preserve">P35456</t>
   </si>
   <si>
-    <t xml:space="preserve">P23090</t>
-  </si>
-  <si>
     <t xml:space="preserve">P58771</t>
   </si>
   <si>
@@ -6136,60 +6130,60 @@
     <t xml:space="preserve">P21460</t>
   </si>
   <si>
+    <t xml:space="preserve">P48453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q91V08</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC 16:1_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P48453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q91V08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9DAA6</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8R242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9JME7</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC 16:1_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8R242</t>
+    <t xml:space="preserve">Q9WTX5</t>
   </si>
   <si>
     <t xml:space="preserve">PC 16:1_22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JME7</t>
+    <t xml:space="preserve">P63321</t>
   </si>
   <si>
     <t xml:space="preserve">PC 16:1_22:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WTX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P63321</t>
+    <t xml:space="preserve">P04184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q91VY6</t>
   </si>
   <si>
     <t xml:space="preserve">PC 16:2_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P04184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q91VY6</t>
-  </si>
-  <si>
     <t xml:space="preserve">O35892</t>
   </si>
   <si>
+    <t xml:space="preserve">Q920Q8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O88593</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC 18:0_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q920Q8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O88593</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8CCI5</t>
   </si>
   <si>
@@ -6202,15 +6196,15 @@
     <t xml:space="preserve">Q9EPL4</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8VE19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P01645</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC 18:1_22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8VE19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P01645</t>
-  </si>
-  <si>
     <t xml:space="preserve">O35648</t>
   </si>
   <si>
@@ -6241,27 +6235,27 @@
     <t xml:space="preserve">Q6ZWV7</t>
   </si>
   <si>
+    <t xml:space="preserve">A6PWY4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q8CF89</t>
+  </si>
+  <si>
     <t xml:space="preserve">PG 14:0_16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">A6PWY4</t>
+    <t xml:space="preserve">P15508</t>
   </si>
   <si>
     <t xml:space="preserve">PG 14:0_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8CF89</t>
+    <t xml:space="preserve">Q9D1H7</t>
   </si>
   <si>
     <t xml:space="preserve">PG 15:0_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P15508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9D1H7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9QZF2</t>
   </si>
   <si>
@@ -6277,42 +6271,42 @@
     <t xml:space="preserve">Q99J87</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9DCB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q8R429</t>
+  </si>
+  <si>
     <t xml:space="preserve">PG 16:1_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9DCB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8R429</t>
-  </si>
-  <si>
     <t xml:space="preserve">P56213</t>
   </si>
   <si>
     <t xml:space="preserve">Q8CJG0</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9WTU0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q64133</t>
+  </si>
+  <si>
     <t xml:space="preserve">PG 18:1_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WTU0</t>
+    <t xml:space="preserve">Q00898</t>
   </si>
   <si>
     <t xml:space="preserve">PG 18:1_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q64133</t>
+    <t xml:space="preserve">Q8C2K1</t>
   </si>
   <si>
     <t xml:space="preserve">PG 18:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q00898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8C2K1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8K4I3</t>
   </si>
   <si>
@@ -6328,84 +6322,84 @@
     <t xml:space="preserve">Q07802</t>
   </si>
   <si>
+    <t xml:space="preserve">P70429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q61189</t>
+  </si>
+  <si>
     <t xml:space="preserve">PG 18:3_18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">P70429</t>
+    <t xml:space="preserve">O08997</t>
   </si>
   <si>
     <t xml:space="preserve">PG 18:3_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61189</t>
+    <t xml:space="preserve">Q9CQA1</t>
   </si>
   <si>
     <t xml:space="preserve">PG 18:3_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">O08997</t>
+    <t xml:space="preserve">P63166</t>
   </si>
   <si>
     <t xml:space="preserve">PG 20:1_22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CQA1</t>
+    <t xml:space="preserve">P43276</t>
   </si>
   <si>
     <t xml:space="preserve">PG 20:2_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P63166</t>
+    <t xml:space="preserve">P58058</t>
   </si>
   <si>
     <t xml:space="preserve">PG 20:2_22:5</t>
   </si>
   <si>
-    <t xml:space="preserve">P43276</t>
+    <t xml:space="preserve">P22315</t>
   </si>
   <si>
     <t xml:space="preserve">PG 20:3_20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P58058</t>
+    <t xml:space="preserve">Q9R1X4</t>
   </si>
   <si>
     <t xml:space="preserve">PG 20:3_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P22315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9R1X4</t>
+    <t xml:space="preserve">Q8BHL5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9EST4</t>
   </si>
   <si>
     <t xml:space="preserve">PG 20:3_22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BHL5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9EST4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q64705</t>
   </si>
   <si>
+    <t xml:space="preserve">Q91WM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q6ZWM4</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA 14:0_16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q91WM1</t>
+    <t xml:space="preserve">Q91WB4</t>
   </si>
   <si>
     <t xml:space="preserve">PA 14:0_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6ZWM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q91WB4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q91YX0</t>
   </si>
   <si>
@@ -6415,39 +6409,39 @@
     <t xml:space="preserve">P51437</t>
   </si>
   <si>
+    <t xml:space="preserve">P29533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E9PVX6</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA 16:0_20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P29533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E9PVX6</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q8BNU0</t>
   </si>
   <si>
+    <t xml:space="preserve">P11276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9JJD0</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA 16:0_22:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P11276</t>
+    <t xml:space="preserve">Q9Z2X8</t>
   </si>
   <si>
     <t xml:space="preserve">PA 16:1_16:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9JJD0</t>
+    <t xml:space="preserve">P58059</t>
   </si>
   <si>
     <t xml:space="preserve">PA 16:1_18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9Z2X8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P58059</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q61069</t>
   </si>
   <si>
@@ -6457,120 +6451,120 @@
     <t xml:space="preserve">Q60953</t>
   </si>
   <si>
+    <t xml:space="preserve">Q921E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9WTQ5</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA 18:1_20:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q921E6</t>
+    <t xml:space="preserve">Q9D0W5</t>
   </si>
   <si>
     <t xml:space="preserve">PA 18:1_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WTQ5</t>
+    <t xml:space="preserve">Q8VC85</t>
   </si>
   <si>
     <t xml:space="preserve">PA 18:2_18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9D0W5</t>
+    <t xml:space="preserve">Q99K95</t>
   </si>
   <si>
     <t xml:space="preserve">PA 18:2_20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8VC85</t>
+    <t xml:space="preserve">Q8K1A6</t>
   </si>
   <si>
     <t xml:space="preserve">LPA 16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99K95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8K1A6</t>
+    <t xml:space="preserve">A2A690</t>
   </si>
   <si>
     <t xml:space="preserve">LPI 16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">A2A690</t>
+    <t xml:space="preserve">P97484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P35330</t>
   </si>
   <si>
     <t xml:space="preserve">LPI 18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">P97484</t>
+    <t xml:space="preserve">Q99J72</t>
   </si>
   <si>
     <t xml:space="preserve">LPI 18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P35330</t>
+    <t xml:space="preserve">O35943</t>
   </si>
   <si>
     <t xml:space="preserve">LPI 20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99J72</t>
+    <t xml:space="preserve">Q8BHG2</t>
   </si>
   <si>
     <t xml:space="preserve">LPI 20:2</t>
   </si>
   <si>
-    <t xml:space="preserve">O35943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8BHG2</t>
+    <t xml:space="preserve">Q80U16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3UQA7</t>
   </si>
   <si>
     <t xml:space="preserve">LPG 16:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q80U16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3UQA7</t>
-  </si>
-  <si>
     <t xml:space="preserve">P13542</t>
   </si>
   <si>
     <t xml:space="preserve">Q9JKE1</t>
   </si>
   <si>
+    <t xml:space="preserve">O08664</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPG 20:1</t>
   </si>
   <si>
-    <t xml:space="preserve">O08664</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9D659</t>
   </si>
   <si>
     <t xml:space="preserve">Q9ERZ0</t>
   </si>
   <si>
+    <t xml:space="preserve">P61079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O88968</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPG 22:2</t>
   </si>
   <si>
-    <t xml:space="preserve">P61079</t>
-  </si>
-  <si>
     <t xml:space="preserve">LPG 22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">O88968</t>
+    <t xml:space="preserve">Q6DFV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q08288</t>
   </si>
   <si>
     <t xml:space="preserve">LPG 22:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6DFV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q08288</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q921K9</t>
   </si>
   <si>
@@ -6586,21 +6580,21 @@
     <t xml:space="preserve">Q00519</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9CY21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O88597</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPE 18:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CY21</t>
+    <t xml:space="preserve">Q5DW34</t>
   </si>
   <si>
     <t xml:space="preserve">LPE 20:0</t>
   </si>
   <si>
-    <t xml:space="preserve">O88597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q5DW34</t>
-  </si>
-  <si>
     <t xml:space="preserve">O08692</t>
   </si>
   <si>
@@ -6610,15 +6604,15 @@
     <t xml:space="preserve">O88559</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8BHC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2AL36</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPE 22:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BHC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2AL36</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6ZQF0</t>
   </si>
   <si>
@@ -6631,192 +6625,192 @@
     <t xml:space="preserve">E9Q557</t>
   </si>
   <si>
+    <t xml:space="preserve">Q8VDF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0DOV1</t>
+  </si>
+  <si>
     <t xml:space="preserve">CL 66:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8VDF2</t>
+    <t xml:space="preserve">Q91WV0</t>
   </si>
   <si>
     <t xml:space="preserve">CL 66:5</t>
   </si>
   <si>
-    <t xml:space="preserve">P0DOV1</t>
-  </si>
-  <si>
     <t xml:space="preserve">CL 68:3</t>
   </si>
   <si>
-    <t xml:space="preserve">Q91WV0</t>
-  </si>
-  <si>
     <t xml:space="preserve">CL 68:4</t>
   </si>
   <si>
+    <t xml:space="preserve">A2ASS6</t>
+  </si>
+  <si>
     <t xml:space="preserve">CL 68:5</t>
   </si>
   <si>
+    <t xml:space="preserve">P43274</t>
+  </si>
+  <si>
     <t xml:space="preserve">CL 68:6</t>
   </si>
   <si>
-    <t xml:space="preserve">A2ASS6</t>
+    <t xml:space="preserve">O09012</t>
   </si>
   <si>
     <t xml:space="preserve">CL 69:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P43274</t>
+    <t xml:space="preserve">Q8BYI6</t>
   </si>
   <si>
     <t xml:space="preserve">CL 69:5</t>
   </si>
   <si>
-    <t xml:space="preserve">O09012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8BYI6</t>
+    <t xml:space="preserve">C0HKD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q6P5D3</t>
   </si>
   <si>
     <t xml:space="preserve">CL 70:5</t>
   </si>
   <si>
-    <t xml:space="preserve">C0HKD9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q6P5D3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q6PGG2</t>
   </si>
   <si>
+    <t xml:space="preserve">P62254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q640N3</t>
+  </si>
+  <si>
     <t xml:space="preserve">CL 72:4</t>
   </si>
   <si>
-    <t xml:space="preserve">P62254</t>
+    <t xml:space="preserve">Q9CPT3</t>
   </si>
   <si>
     <t xml:space="preserve">CL 72:5</t>
   </si>
   <si>
-    <t xml:space="preserve">Q640N3</t>
+    <t xml:space="preserve">Q8BGF3</t>
   </si>
   <si>
     <t xml:space="preserve">CL 72:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9CPT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8BGF3</t>
+    <t xml:space="preserve">Q9Z2D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q9CPQ3</t>
   </si>
   <si>
     <t xml:space="preserve">CL 72:9</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9Z2D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9CPQ3</t>
+    <t xml:space="preserve">P70279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P01027</t>
   </si>
   <si>
     <t xml:space="preserve">CL 74:6</t>
   </si>
   <si>
-    <t xml:space="preserve">P70279</t>
+    <t xml:space="preserve">Q8BQZ5</t>
   </si>
   <si>
     <t xml:space="preserve">CL 74:7</t>
   </si>
   <si>
-    <t xml:space="preserve">P01027</t>
+    <t xml:space="preserve">Q9JI48</t>
   </si>
   <si>
     <t xml:space="preserve">CL 74:8</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BQZ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9JI48</t>
-  </si>
-  <si>
     <t xml:space="preserve">Q9Z2C5</t>
   </si>
   <si>
+    <t xml:space="preserve">Q9WVH4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q8R4Y8</t>
+  </si>
+  <si>
     <t xml:space="preserve">CL 76:11</t>
   </si>
   <si>
-    <t xml:space="preserve">Q9WVH4</t>
+    <t xml:space="preserve">Q7TNV0</t>
   </si>
   <si>
     <t xml:space="preserve">CL 76:9</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8R4Y8</t>
+    <t xml:space="preserve">Q61830</t>
   </si>
   <si>
     <t xml:space="preserve">CL 92:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q7TNV0</t>
+    <t xml:space="preserve">O35075</t>
   </si>
   <si>
     <t xml:space="preserve">CL 94:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q61830</t>
+    <t xml:space="preserve">Q91WG0</t>
   </si>
   <si>
     <t xml:space="preserve">ST 27:1;1</t>
   </si>
   <si>
-    <t xml:space="preserve">O35075</t>
+    <t xml:space="preserve">Q99KN2</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/16:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q91WG0</t>
+    <t xml:space="preserve">Q6PCN7</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/16:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q99KN2</t>
+    <t xml:space="preserve">Q8K1E6</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/18:0</t>
   </si>
   <si>
-    <t xml:space="preserve">Q6PCN7</t>
+    <t xml:space="preserve">Q91YE5</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8K1E6</t>
+    <t xml:space="preserve">Q8BY87</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/18:2</t>
   </si>
   <si>
-    <t xml:space="preserve">Q91YE5</t>
+    <t xml:space="preserve">Q78JE5</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/20:4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q8BY87</t>
+    <t xml:space="preserve">Q6ZQ03</t>
   </si>
   <si>
     <t xml:space="preserve">SE 27:1/22:6</t>
   </si>
   <si>
-    <t xml:space="preserve">Q78JE5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q6ZQ03</t>
-  </si>
-  <si>
     <t xml:space="preserve">P28659</t>
   </si>
   <si>
@@ -15974,9 +15968,6 @@
   </si>
   <si>
     <t xml:space="preserve">Q8QZY9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P12894</t>
   </si>
   <si>
     <t xml:space="preserve">Q6PGF3</t>
@@ -26265,7 +26256,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4691"/>
+  <dimension ref="A1:I4688"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26293,6 +26284,9 @@
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -26319,6 +26313,9 @@
       <c r="H2" s="5" t="s">
         <v>1223</v>
       </c>
+      <c r="I2" s="0" t="n">
+        <v>10090</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
@@ -27154,10 +27151,10 @@
         <v>313</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>1385</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27165,13 +27162,13 @@
         <v>108</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>1387</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27182,10 +27179,10 @@
         <v>247</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27196,7 +27193,7 @@
         <v>254</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1266</v>
+        <v>1389</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>1390</v>
@@ -27224,10 +27221,10 @@
         <v>262</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>1393</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27238,7 +27235,7 @@
         <v>263</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1270</v>
+        <v>1394</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>1395</v>
@@ -27280,10 +27277,10 @@
         <v>275</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>1400</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27294,7 +27291,7 @@
         <v>281</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1274</v>
+        <v>1401</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>1402</v>
@@ -27378,21 +27375,21 @@
         <v>1416</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>1417</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1278</v>
+        <v>1419</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>1420</v>
@@ -27462,10 +27459,10 @@
         <v>422</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>1434</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27473,10 +27470,10 @@
         <v>1256</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>1436</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>1282</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>1437</v>
@@ -27518,10 +27515,10 @@
         <v>1445</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>1446</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27529,10 +27526,10 @@
         <v>1260</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>1448</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>1286</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>1449</v>
@@ -27753,10 +27750,10 @@
         <v>1501</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>1502</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27764,7 +27761,7 @@
         <v>1272</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1290</v>
+        <v>1503</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>1504</v>
@@ -27786,10 +27783,10 @@
         <v>1508</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>1509</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27797,7 +27794,7 @@
         <v>1276</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1293</v>
+        <v>1510</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>1511</v>
@@ -27841,10 +27838,10 @@
         <v>1280</v>
       </c>
       <c r="C113" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27852,7 +27849,7 @@
         <v>1284</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1295</v>
+        <v>1522</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>1523</v>
@@ -27863,18 +27860,18 @@
         <v>1524</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>1525</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>1527</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>1298</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>1528</v>
@@ -28028,10 +28025,10 @@
         <v>1566</v>
       </c>
       <c r="C130" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D130" s="2" t="s">
         <v>1567</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28039,7 +28036,7 @@
         <v>458</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>1301</v>
+        <v>1568</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>1569</v>
@@ -28061,10 +28058,10 @@
         <v>1291</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>1573</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28072,7 +28069,7 @@
         <v>459</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>1304</v>
+        <v>1574</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>1575</v>
@@ -28160,18 +28157,18 @@
         <v>1595</v>
       </c>
       <c r="C142" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>1596</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>1597</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>1598</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>1306</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>1599</v>
@@ -28204,18 +28201,18 @@
         <v>1302</v>
       </c>
       <c r="C146" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D146" s="2" t="s">
         <v>1606</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>1608</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>1308</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>1609</v>
@@ -28248,10 +28245,10 @@
         <v>468</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>1614</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28259,7 +28256,7 @@
         <v>469</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1309</v>
+        <v>1615</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>1616</v>
@@ -28281,10 +28278,10 @@
         <v>1620</v>
       </c>
       <c r="C153" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>1621</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28292,7 +28289,7 @@
         <v>471</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1312</v>
+        <v>1622</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>1623</v>
@@ -28303,10 +28300,10 @@
         <v>75</v>
       </c>
       <c r="C155" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>1624</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28314,7 +28311,7 @@
         <v>475</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1315</v>
+        <v>1625</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>1626</v>
@@ -28391,18 +28388,18 @@
         <v>486</v>
       </c>
       <c r="C163" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D163" s="2" t="s">
         <v>1640</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>1642</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>1318</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>1643</v>
@@ -28424,18 +28421,18 @@
         <v>1647</v>
       </c>
       <c r="C166" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>1648</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>1650</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>1321</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>1651</v>
@@ -28457,29 +28454,29 @@
         <v>1655</v>
       </c>
       <c r="C169" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D169" s="2" t="s">
         <v>1656</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>1658</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>1660</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>1324</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>1661</v>
@@ -28490,18 +28487,18 @@
         <v>1313</v>
       </c>
       <c r="C172" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>1662</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>1664</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>1327</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>1665</v>
@@ -28523,10 +28520,10 @@
         <v>1669</v>
       </c>
       <c r="C175" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D175" s="2" t="s">
         <v>1670</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28534,7 +28531,7 @@
         <v>1316</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1329</v>
+        <v>1671</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>1672</v>
@@ -28567,10 +28564,10 @@
         <v>1679</v>
       </c>
       <c r="C179" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D179" s="2" t="s">
         <v>1680</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28578,7 +28575,7 @@
         <v>438</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>1331</v>
+        <v>1681</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>1682</v>
@@ -28765,10 +28762,10 @@
         <v>447</v>
       </c>
       <c r="C197" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D197" s="2" t="s">
         <v>1723</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28776,10 +28773,10 @@
         <v>448</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28787,10 +28784,10 @@
         <v>450</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28798,7 +28795,7 @@
         <v>1325</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>1339</v>
+        <v>1726</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>1727</v>
@@ -28897,18 +28894,18 @@
         <v>1749</v>
       </c>
       <c r="C209" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D209" s="2" t="s">
         <v>1750</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C210" s="1" t="s">
         <v>1752</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>1341</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>1753</v>
@@ -28941,18 +28938,18 @@
         <v>1760</v>
       </c>
       <c r="C213" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D213" s="2" t="s">
         <v>1761</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>1763</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>1344</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>1764</v>
@@ -28963,10 +28960,10 @@
         <v>1765</v>
       </c>
       <c r="C215" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D215" s="2" t="s">
         <v>1766</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28974,7 +28971,7 @@
         <v>371</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1346</v>
+        <v>1767</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>1768</v>
@@ -29051,18 +29048,18 @@
         <v>1784</v>
       </c>
       <c r="C223" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>1785</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C224" s="1" t="s">
         <v>1787</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>1348</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>1788</v>
@@ -29073,18 +29070,18 @@
         <v>1789</v>
       </c>
       <c r="C225" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>1790</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C226" s="1" t="s">
         <v>1792</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>1351</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>1793</v>
@@ -29095,18 +29092,18 @@
         <v>395</v>
       </c>
       <c r="C227" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>1794</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C228" s="1" t="s">
         <v>1796</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>1352</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>1797</v>
@@ -29128,18 +29125,18 @@
         <v>399</v>
       </c>
       <c r="C230" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>1800</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>1802</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>1803</v>
@@ -29150,29 +29147,29 @@
         <v>1804</v>
       </c>
       <c r="C232" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D232" s="2" t="s">
         <v>1805</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>1807</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>1356</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>1809</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>1358</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>1810</v>
@@ -29183,18 +29180,18 @@
         <v>1334</v>
       </c>
       <c r="C235" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>1811</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>1813</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>1361</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>1814</v>
@@ -29238,10 +29235,10 @@
         <v>1824</v>
       </c>
       <c r="C240" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D240" s="2" t="s">
         <v>1825</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29249,7 +29246,7 @@
         <v>408</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1362</v>
+        <v>1826</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>1827</v>
@@ -29315,51 +29312,51 @@
         <v>317</v>
       </c>
       <c r="C247" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>1841</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>1843</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>1845</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D250" s="2" t="s">
         <v>1847</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C251" s="1" t="s">
         <v>1849</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>1371</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>1850</v>
@@ -29370,18 +29367,18 @@
         <v>1851</v>
       </c>
       <c r="C252" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D252" s="2" t="s">
         <v>1852</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C253" s="1" t="s">
         <v>1854</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>1373</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>1855</v>
@@ -29425,10 +29422,10 @@
         <v>322</v>
       </c>
       <c r="C257" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>1863</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29436,10 +29433,10 @@
         <v>323</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29447,7 +29444,7 @@
         <v>1347</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1376</v>
+        <v>1865</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>1866</v>
@@ -29458,10 +29455,10 @@
         <v>326</v>
       </c>
       <c r="C260" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D260" s="2" t="s">
         <v>1867</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29469,7 +29466,7 @@
         <v>327</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1378</v>
+        <v>1868</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>1869</v>
@@ -29480,10 +29477,10 @@
         <v>1870</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D262" s="2" t="s">
         <v>1871</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29491,7 +29488,7 @@
         <v>328</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1381</v>
+        <v>1872</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>1873</v>
@@ -29502,10 +29499,10 @@
         <v>329</v>
       </c>
       <c r="C264" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D264" s="2" t="s">
         <v>1874</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29513,7 +29510,7 @@
         <v>1349</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1384</v>
+        <v>1875</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>1876</v>
@@ -29590,10 +29587,10 @@
         <v>1891</v>
       </c>
       <c r="C272" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D272" s="2" t="s">
         <v>1892</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29601,7 +29598,7 @@
         <v>1359</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1386</v>
+        <v>1893</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>1894</v>
@@ -29667,18 +29664,18 @@
         <v>339</v>
       </c>
       <c r="C279" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D279" s="2" t="s">
         <v>1910</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C280" s="1" t="s">
         <v>1912</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>1388</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>1913</v>
@@ -30063,18 +30060,18 @@
         <v>1996</v>
       </c>
       <c r="C315" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D315" s="2" t="s">
         <v>1997</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>1998</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C316" s="1" t="s">
         <v>1999</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>1389</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>2000</v>
@@ -30123,15 +30120,15 @@
         <v>312</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>2009</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C322" s="1" t="s">
         <v>2010</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30152,7 +30149,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>2014</v>
@@ -30427,7 +30424,7 @@
         <v>281</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>2056</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30435,7 +30432,7 @@
         <v>282</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30443,7 +30440,7 @@
         <v>283</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>1392</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30648,7 +30645,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>2088</v>
@@ -30848,7 +30845,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>2127</v>
@@ -30987,7 +30984,7 @@
         <v>2152</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>2153</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30995,15 +30992,15 @@
         <v>51</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C431" s="1" t="s">
         <v>2155</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31075,7 +31072,7 @@
         <v>218</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>2169</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31083,15 +31080,15 @@
         <v>219</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C442" s="1" t="s">
         <v>2171</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31123,15 +31120,15 @@
         <v>2175</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>2176</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C447" s="1" t="s">
         <v>2177</v>
-      </c>
-      <c r="C447" s="1" t="s">
-        <v>2178</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31139,7 +31136,7 @@
         <v>1489</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>1397</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31275,7 +31272,7 @@
         <v>216</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>2199</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31283,7 +31280,7 @@
         <v>53</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31291,7 +31288,7 @@
         <v>56</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>1399</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31315,31 +31312,31 @@
         <v>2204</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>2205</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>2207</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>1401</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C473" s="1" t="s">
         <v>2209</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31419,7 +31416,7 @@
         <v>2225</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>2226</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31427,7 +31424,7 @@
         <v>1498</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31435,7 +31432,7 @@
         <v>27</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>1404</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31652,17 +31649,17 @@
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C517" s="1" t="s">
-        <v>2275</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C518" s="1" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C519" s="1" t="s">
-        <v>1406</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31697,22 +31694,22 @@
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C526" s="1" t="s">
-        <v>2283</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C527" s="1" t="s">
-        <v>2284</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C528" s="1" t="s">
-        <v>1409</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C529" s="1" t="s">
-        <v>1412</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31747,17 +31744,17 @@
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C536" s="1" t="s">
-        <v>2291</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C537" s="1" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C538" s="1" t="s">
-        <v>1414</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31822,17 +31819,17 @@
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C551" s="1" t="s">
-        <v>2305</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C552" s="1" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C553" s="1" t="s">
-        <v>1418</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32242,17 +32239,17 @@
     </row>
     <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C635" s="1" t="s">
-        <v>2388</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C636" s="1" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C637" s="1" t="s">
-        <v>1420</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32297,17 +32294,17 @@
     </row>
     <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C646" s="1" t="s">
-        <v>2398</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C647" s="1" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C648" s="1" t="s">
-        <v>1422</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32547,17 +32544,17 @@
     </row>
     <row r="696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C696" s="1" t="s">
-        <v>2447</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C697" s="1" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C698" s="1" t="s">
-        <v>1425</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32612,17 +32609,17 @@
     </row>
     <row r="709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C709" s="1" t="s">
-        <v>2459</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C710" s="1" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C711" s="1" t="s">
-        <v>1429</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32707,17 +32704,17 @@
     </row>
     <row r="728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C728" s="1" t="s">
-        <v>2477</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C729" s="1" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C730" s="1" t="s">
-        <v>1432</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32762,42 +32759,42 @@
     </row>
     <row r="739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C739" s="1" t="s">
-        <v>2487</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C740" s="1" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C741" s="1" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C742" s="1" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C743" s="1" t="s">
-        <v>1437</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C744" s="1" t="s">
-        <v>2490</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C745" s="1" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C746" s="1" t="s">
-        <v>1440</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32822,17 +32819,17 @@
     </row>
     <row r="751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C751" s="1" t="s">
-        <v>2496</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C752" s="1" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C753" s="1" t="s">
-        <v>1443</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32947,17 +32944,17 @@
     </row>
     <row r="776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C776" s="1" t="s">
-        <v>2520</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C777" s="1" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C778" s="1" t="s">
-        <v>1447</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33112,17 +33109,17 @@
     </row>
     <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C809" s="1" t="s">
-        <v>2552</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C810" s="1" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C811" s="1" t="s">
-        <v>1449</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33337,17 +33334,17 @@
     </row>
     <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C854" s="1" t="s">
-        <v>2596</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C855" s="1" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C856" s="1" t="s">
-        <v>1452</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33387,37 +33384,37 @@
     </row>
     <row r="864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C864" s="1" t="s">
-        <v>2605</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C865" s="1" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C866" s="1" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C867" s="1" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C868" s="1" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C869" s="1" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C870" s="1" t="s">
-        <v>1463</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33522,22 +33519,22 @@
     </row>
     <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C891" s="1" t="s">
-        <v>2629</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C892" s="1" t="s">
-        <v>2630</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C893" s="1" t="s">
-        <v>1467</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C894" s="1" t="s">
-        <v>1470</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33767,17 +33764,17 @@
     </row>
     <row r="940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C940" s="1" t="s">
-        <v>2676</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C941" s="1" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C942" s="1" t="s">
-        <v>1474</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33922,17 +33919,17 @@
     </row>
     <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C971" s="1" t="s">
-        <v>2706</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C972" s="1" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C973" s="1" t="s">
-        <v>1477</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33992,17 +33989,17 @@
     </row>
     <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C985" s="1" t="s">
-        <v>2719</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C986" s="1" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C987" s="1" t="s">
-        <v>1480</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34217,17 +34214,17 @@
     </row>
     <row r="1030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1030" s="1" t="s">
-        <v>2763</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1031" s="1" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="1032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1032" s="1" t="s">
-        <v>1484</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="1033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34237,17 +34234,17 @@
     </row>
     <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1034" s="1" t="s">
-        <v>2766</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1035" s="1" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="1036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1036" s="1" t="s">
-        <v>1488</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="1037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34322,32 +34319,32 @@
     </row>
     <row r="1051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1051" s="1" t="s">
-        <v>2782</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1052" s="1" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1053" s="1" t="s">
-        <v>1491</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="1054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1054" s="1" t="s">
-        <v>2784</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1055" s="1" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="1056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1056" s="1" t="s">
-        <v>1494</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="1057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34362,32 +34359,32 @@
     </row>
     <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1059" s="1" t="s">
-        <v>2788</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1060" s="1" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1061" s="1" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1062" s="1" t="s">
-        <v>2790</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1063" s="1" t="s">
-        <v>1500</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1064" s="1" t="s">
-        <v>1503</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="1065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34502,17 +34499,17 @@
     </row>
     <row r="1087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1087" s="1" t="s">
-        <v>2813</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1088" s="1" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="1089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1089" s="1" t="s">
-        <v>1504</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="1090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34597,17 +34594,17 @@
     </row>
     <row r="1106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1106" s="1" t="s">
-        <v>2831</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1107" s="1" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="1108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1108" s="1" t="s">
-        <v>1507</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="1109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34617,17 +34614,17 @@
     </row>
     <row r="1110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1110" s="1" t="s">
-        <v>2834</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1111" s="1" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1112" s="1" t="s">
-        <v>1510</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="1113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34637,32 +34634,32 @@
     </row>
     <row r="1114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1114" s="1" t="s">
-        <v>2837</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1115" s="1" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1116" s="1" t="s">
-        <v>1511</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="1117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1117" s="1" t="s">
-        <v>2839</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="1118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1118" s="1" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="1119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1119" s="1" t="s">
-        <v>1514</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34702,17 +34699,17 @@
     </row>
     <row r="1127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1127" s="1" t="s">
-        <v>2848</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1128" s="1" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="1129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1129" s="1" t="s">
-        <v>1517</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="1130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34782,17 +34779,17 @@
     </row>
     <row r="1143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1143" s="1" t="s">
-        <v>2863</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1144" s="1" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="1145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1145" s="1" t="s">
-        <v>1520</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="1146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34857,17 +34854,17 @@
     </row>
     <row r="1158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1158" s="1" t="s">
-        <v>2877</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1159" s="1" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="1160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1160" s="1" t="s">
-        <v>1522</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="1161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34957,17 +34954,17 @@
     </row>
     <row r="1178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1178" s="1" t="s">
-        <v>2896</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1179" s="1" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="1180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1180" s="1" t="s">
-        <v>1523</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="1181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34987,17 +34984,17 @@
     </row>
     <row r="1184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1184" s="1" t="s">
-        <v>2901</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1185" s="1" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1186" s="1" t="s">
-        <v>1526</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="1187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35022,17 +35019,17 @@
     </row>
     <row r="1191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1191" s="1" t="s">
-        <v>2907</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1192" s="1" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="1193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1193" s="1" t="s">
-        <v>1528</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="1194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35252,22 +35249,22 @@
     </row>
     <row r="1237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1237" s="1" t="s">
-        <v>2952</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1238" s="1" t="s">
-        <v>2953</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1239" s="1" t="s">
-        <v>1530</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="1240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1240" s="1" t="s">
-        <v>1533</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="1241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35337,17 +35334,17 @@
     </row>
     <row r="1254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1254" s="1" t="s">
-        <v>2967</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1255" s="1" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="1256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1256" s="1" t="s">
-        <v>1536</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="1257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35472,17 +35469,17 @@
     </row>
     <row r="1281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1281" s="1" t="s">
-        <v>2993</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1282" s="1" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="1283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1283" s="1" t="s">
-        <v>1539</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="1284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35527,17 +35524,17 @@
     </row>
     <row r="1292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1292" s="1" t="s">
-        <v>3003</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1293" s="1" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="1294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1294" s="1" t="s">
-        <v>1542</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="1295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35562,17 +35559,17 @@
     </row>
     <row r="1299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1299" s="1" t="s">
-        <v>3009</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1300" s="1" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="1301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1301" s="1" t="s">
-        <v>1545</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="1302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35677,17 +35674,17 @@
     </row>
     <row r="1322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1322" s="1" t="s">
-        <v>3031</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1323" s="1" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="1324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1324" s="1" t="s">
-        <v>1548</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35707,17 +35704,17 @@
     </row>
     <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1328" s="1" t="s">
-        <v>3036</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1329" s="1" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1330" s="1" t="s">
-        <v>1551</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35857,17 +35854,17 @@
     </row>
     <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1358" s="1" t="s">
-        <v>3065</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1359" s="1" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1360" s="1" t="s">
-        <v>1554</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35937,17 +35934,17 @@
     </row>
     <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1374" s="1" t="s">
-        <v>3080</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1375" s="1" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1376" s="1" t="s">
-        <v>1557</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36227,17 +36224,17 @@
     </row>
     <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1432" s="1" t="s">
-        <v>3137</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1433" s="1" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1434" s="1" t="s">
-        <v>1559</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36512,17 +36509,17 @@
     </row>
     <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1489" s="1" t="s">
-        <v>3193</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1490" s="1" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1491" s="1" t="s">
-        <v>1562</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="1492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36612,17 +36609,17 @@
     </row>
     <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1509" s="1" t="s">
-        <v>3212</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1510" s="1" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1511" s="1" t="s">
-        <v>1565</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="1512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36657,17 +36654,17 @@
     </row>
     <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1518" s="1" t="s">
-        <v>3220</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1519" s="1" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1520" s="1" t="s">
-        <v>1568</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36727,17 +36724,17 @@
     </row>
     <row r="1532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1532" s="1" t="s">
-        <v>3233</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1533" s="1" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1534" s="1" t="s">
-        <v>1569</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36777,17 +36774,17 @@
     </row>
     <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1542" s="1" t="s">
-        <v>3242</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1543" s="1" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1544" s="1" t="s">
-        <v>1572</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36827,17 +36824,17 @@
     </row>
     <row r="1552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1552" s="1" t="s">
-        <v>3251</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1553" s="1" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1554" s="1" t="s">
-        <v>1574</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36857,17 +36854,17 @@
     </row>
     <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1558" s="1" t="s">
-        <v>3256</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1559" s="1" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1560" s="1" t="s">
-        <v>1575</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36887,17 +36884,17 @@
     </row>
     <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1564" s="1" t="s">
-        <v>3261</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1565" s="1" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="1566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1566" s="1" t="s">
-        <v>1577</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="1567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36917,17 +36914,17 @@
     </row>
     <row r="1570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1570" s="1" t="s">
-        <v>3266</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1571" s="1" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="1572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1572" s="1" t="s">
-        <v>1580</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="1573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37127,17 +37124,17 @@
     </row>
     <row r="1612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1612" s="1" t="s">
-        <v>3307</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1613" s="1" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="1614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1614" s="1" t="s">
-        <v>1583</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="1615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37222,17 +37219,17 @@
     </row>
     <row r="1631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1631" s="1" t="s">
-        <v>3325</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1632" s="1" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="1633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1633" s="1" t="s">
-        <v>1586</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="1634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37387,17 +37384,17 @@
     </row>
     <row r="1664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1664" s="1" t="s">
-        <v>3357</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1665" s="1" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="1666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1666" s="1" t="s">
-        <v>1588</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="1667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37707,17 +37704,17 @@
     </row>
     <row r="1728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1728" s="1" t="s">
-        <v>3420</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1729" s="1" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="1730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1730" s="1" t="s">
-        <v>1591</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="1731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37732,17 +37729,17 @@
     </row>
     <row r="1733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1733" s="1" t="s">
-        <v>3424</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1734" s="1" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="1735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1735" s="1" t="s">
-        <v>1594</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="1736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37842,17 +37839,17 @@
     </row>
     <row r="1755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1755" s="1" t="s">
-        <v>3445</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1756" s="1" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="1757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1757" s="1" t="s">
-        <v>1597</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="1758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37872,17 +37869,17 @@
     </row>
     <row r="1761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1761" s="1" t="s">
-        <v>3450</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1762" s="1" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="1763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1763" s="1" t="s">
-        <v>1599</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="1764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38192,17 +38189,17 @@
     </row>
     <row r="1825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1825" s="1" t="s">
-        <v>3513</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1826" s="1" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="1827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1827" s="1" t="s">
-        <v>1602</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="1828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38212,17 +38209,17 @@
     </row>
     <row r="1829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1829" s="1" t="s">
-        <v>3516</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1830" s="1" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="1831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1831" s="1" t="s">
-        <v>1605</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="1832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38242,17 +38239,17 @@
     </row>
     <row r="1835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1835" s="1" t="s">
-        <v>3521</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1836" s="1" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="1837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1837" s="1" t="s">
-        <v>1607</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="1838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38397,17 +38394,17 @@
     </row>
     <row r="1866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1866" s="1" t="s">
-        <v>3551</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1867" s="1" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="1868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1868" s="1" t="s">
-        <v>1609</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="1869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38477,17 +38474,17 @@
     </row>
     <row r="1882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1882" s="1" t="s">
-        <v>3566</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1883" s="1" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="1884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1884" s="1" t="s">
-        <v>1611</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="1885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38677,17 +38674,17 @@
     </row>
     <row r="1922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1922" s="1" t="s">
-        <v>3605</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1923" s="1" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="1924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1924" s="1" t="s">
-        <v>1613</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="1925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38707,17 +38704,17 @@
     </row>
     <row r="1928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1928" s="1" t="s">
-        <v>3610</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1929" s="1" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="1930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1930" s="1" t="s">
-        <v>1615</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="1931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38732,22 +38729,22 @@
     </row>
     <row r="1933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1933" s="1" t="s">
-        <v>3614</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1934" s="1" t="s">
-        <v>3615</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1935" s="1" t="s">
-        <v>1616</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="1936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1936" s="1" t="s">
-        <v>1619</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="1937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38782,17 +38779,17 @@
     </row>
     <row r="1943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1943" s="1" t="s">
-        <v>3622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1944" s="1" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="1945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1945" s="1" t="s">
-        <v>1622</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="1946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38807,17 +38804,17 @@
     </row>
     <row r="1948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1948" s="1" t="s">
-        <v>3626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1949" s="1" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="1950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1950" s="1" t="s">
-        <v>1623</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="1951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39037,32 +39034,32 @@
     </row>
     <row r="1994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1994" s="1" t="s">
-        <v>3671</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1995" s="1" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="1996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1996" s="1" t="s">
-        <v>1625</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="1997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1997" s="1" t="s">
-        <v>3673</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1998" s="1" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="1999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1999" s="1" t="s">
-        <v>1626</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="2000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39307,17 +39304,17 @@
     </row>
     <row r="2048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2048" s="1" t="s">
-        <v>3723</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="2049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2049" s="1" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="2050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2050" s="1" t="s">
-        <v>1628</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="2051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39427,17 +39424,17 @@
     </row>
     <row r="2072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2072" s="1" t="s">
-        <v>3746</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="2073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2073" s="1" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="2074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2074" s="1" t="s">
-        <v>1630</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="2075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39457,17 +39454,17 @@
     </row>
     <row r="2078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2078" s="1" t="s">
-        <v>3751</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="2079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2079" s="1" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="2080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2080" s="1" t="s">
-        <v>1633</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="2081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39502,17 +39499,17 @@
     </row>
     <row r="2087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2087" s="1" t="s">
-        <v>3759</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="2088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2088" s="1" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="2089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2089" s="1" t="s">
-        <v>1635</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="2090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39922,17 +39919,17 @@
     </row>
     <row r="2171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2171" s="1" t="s">
-        <v>3842</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="2172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2172" s="1" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="2173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2173" s="1" t="s">
-        <v>1637</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="2174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39972,17 +39969,17 @@
     </row>
     <row r="2181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2181" s="1" t="s">
-        <v>3851</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="2182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2182" s="1" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="2183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2183" s="1" t="s">
-        <v>1639</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="2184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40097,17 +40094,17 @@
     </row>
     <row r="2206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2206" s="1" t="s">
-        <v>3875</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="2207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2207" s="1" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="2208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2208" s="1" t="s">
-        <v>1641</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="2209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40147,17 +40144,17 @@
     </row>
     <row r="2216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2216" s="1" t="s">
-        <v>3884</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="2217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2217" s="1" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="2218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2218" s="1" t="s">
-        <v>1643</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="2219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40182,17 +40179,17 @@
     </row>
     <row r="2223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2223" s="1" t="s">
-        <v>3890</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="2224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2224" s="1" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="2225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2225" s="1" t="s">
-        <v>1646</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="2226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40262,32 +40259,32 @@
     </row>
     <row r="2239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2239" s="1" t="s">
-        <v>3905</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="2240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2240" s="1" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="2241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2241" s="1" t="s">
-        <v>1649</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="2242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2242" s="1" t="s">
-        <v>3907</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="2243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2243" s="1" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="2244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2244" s="1" t="s">
-        <v>1651</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="2245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40427,17 +40424,17 @@
     </row>
     <row r="2272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2272" s="1" t="s">
-        <v>3936</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="2273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2273" s="1" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="2274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2274" s="1" t="s">
-        <v>1654</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="2275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40487,17 +40484,17 @@
     </row>
     <row r="2284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2284" s="1" t="s">
-        <v>3947</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="2285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2285" s="1" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="2286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2286" s="1" t="s">
-        <v>1657</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="2287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40612,17 +40609,17 @@
     </row>
     <row r="2309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2309" s="1" t="s">
-        <v>3971</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="2310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2310" s="1" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="2311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2311" s="1" t="s">
-        <v>1659</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="2312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40757,22 +40754,22 @@
     </row>
     <row r="2338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2338" s="1" t="s">
-        <v>3999</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="2339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2339" s="1" t="s">
-        <v>4000</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="2340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2340" s="1" t="s">
-        <v>1661</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="2341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2341" s="1" t="s">
-        <v>1663</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="2342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40877,17 +40874,17 @@
     </row>
     <row r="2362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2362" s="1" t="s">
-        <v>4021</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="2363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2363" s="1" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="2364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2364" s="1" t="s">
-        <v>1665</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="2365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40997,17 +40994,17 @@
     </row>
     <row r="2386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2386" s="1" t="s">
-        <v>4044</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="2387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2387" s="1" t="s">
-        <v>4045</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="2388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2388" s="1" t="s">
-        <v>1668</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="2389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41027,17 +41024,17 @@
     </row>
     <row r="2392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2392" s="1" t="s">
-        <v>4049</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="2393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2393" s="1" t="s">
-        <v>4050</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="2394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2394" s="1" t="s">
-        <v>1671</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="2395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41102,17 +41099,17 @@
     </row>
     <row r="2407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2407" s="1" t="s">
-        <v>4063</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="2408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2408" s="1" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="2409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2409" s="1" t="s">
-        <v>1672</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="2410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41177,17 +41174,17 @@
     </row>
     <row r="2422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2422" s="1" t="s">
-        <v>4077</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="2423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2423" s="1" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="2424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2424" s="1" t="s">
-        <v>1675</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="2425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41282,17 +41279,17 @@
     </row>
     <row r="2443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2443" s="1" t="s">
-        <v>4097</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="2444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2444" s="1" t="s">
-        <v>4098</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="2445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2445" s="1" t="s">
-        <v>1678</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="2446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41347,37 +41344,37 @@
     </row>
     <row r="2456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2456" s="1" t="s">
-        <v>4109</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="2457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2457" s="1" t="s">
-        <v>4110</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="2458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2458" s="1" t="s">
-        <v>1681</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="2459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2459" s="1" t="s">
-        <v>4111</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="2460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2460" s="1" t="s">
-        <v>4112</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="2461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2461" s="1" t="s">
-        <v>1682</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="2462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2462" s="1" t="s">
-        <v>1684</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="2463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41717,17 +41714,17 @@
     </row>
     <row r="2530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2530" s="1" t="s">
-        <v>4180</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="2531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2531" s="1" t="s">
-        <v>4181</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="2532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2532" s="1" t="s">
-        <v>1687</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="2533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41737,17 +41734,17 @@
     </row>
     <row r="2534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2534" s="1" t="s">
-        <v>4183</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="2535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2535" s="1" t="s">
-        <v>4184</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="2536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2536" s="1" t="s">
-        <v>1689</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="2537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41852,22 +41849,22 @@
     </row>
     <row r="2557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2557" s="1" t="s">
-        <v>4205</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="2558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2558" s="1" t="s">
-        <v>4206</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="2559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2559" s="1" t="s">
-        <v>1691</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="2560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2560" s="1" t="s">
-        <v>1693</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="2561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41932,17 +41929,17 @@
     </row>
     <row r="2573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2573" s="1" t="s">
-        <v>4219</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="2574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2574" s="1" t="s">
-        <v>4220</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="2575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2575" s="1" t="s">
-        <v>1696</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="2576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42277,17 +42274,17 @@
     </row>
     <row r="2642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2642" s="1" t="s">
-        <v>4287</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="2643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2643" s="1" t="s">
-        <v>4288</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="2644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2644" s="1" t="s">
-        <v>1699</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="2645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42397,17 +42394,17 @@
     </row>
     <row r="2666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2666" s="1" t="s">
-        <v>4310</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="2667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2667" s="1" t="s">
-        <v>4311</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="2668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2668" s="1" t="s">
-        <v>1701</v>
+        <v>4311</v>
       </c>
     </row>
     <row r="2669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42522,17 +42519,17 @@
     </row>
     <row r="2691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2691" s="1" t="s">
-        <v>4334</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="2692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2692" s="1" t="s">
-        <v>4335</v>
+        <v>4334</v>
       </c>
     </row>
     <row r="2693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2693" s="1" t="s">
-        <v>1704</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="2694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42602,22 +42599,22 @@
     </row>
     <row r="2707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2707" s="1" t="s">
-        <v>4349</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="2708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2708" s="1" t="s">
-        <v>4350</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="2709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2709" s="1" t="s">
-        <v>1707</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="2710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2710" s="1" t="s">
-        <v>1710</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="2711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42737,17 +42734,17 @@
     </row>
     <row r="2734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2734" s="1" t="s">
-        <v>4374</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="2735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2735" s="1" t="s">
-        <v>4375</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="2736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2736" s="1" t="s">
-        <v>1712</v>
+        <v>4375</v>
       </c>
     </row>
     <row r="2737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42982,17 +42979,17 @@
     </row>
     <row r="2783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2783" s="1" t="s">
-        <v>4422</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="2784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2784" s="1" t="s">
-        <v>4423</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="2785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2785" s="1" t="s">
-        <v>1714</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="2786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43227,17 +43224,17 @@
     </row>
     <row r="2832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2832" s="1" t="s">
-        <v>4470</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="2833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2833" s="1" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="2834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2834" s="1" t="s">
-        <v>1716</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="2835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43302,32 +43299,32 @@
     </row>
     <row r="2847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2847" s="1" t="s">
-        <v>4484</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="2848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2848" s="1" t="s">
-        <v>4485</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="2849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2849" s="1" t="s">
-        <v>1719</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="2850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2850" s="1" t="s">
-        <v>4486</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="2851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2851" s="1" t="s">
-        <v>4487</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="2852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2852" s="1" t="s">
-        <v>1722</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="2853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43477,17 +43474,17 @@
     </row>
     <row r="2882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2882" s="1" t="s">
-        <v>4517</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="2883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2883" s="1" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="2884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2884" s="1" t="s">
-        <v>1724</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="2885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43612,12 +43609,12 @@
     </row>
     <row r="2909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2909" s="1" t="s">
-        <v>4543</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="2910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2910" s="1" t="s">
-        <v>4544</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="2911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43627,22 +43624,22 @@
     </row>
     <row r="2912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2912" s="1" t="s">
-        <v>4545</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="2913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2913" s="1" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="2914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2914" s="1" t="s">
-        <v>4546</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="2915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2915" s="1" t="s">
-        <v>1727</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="2916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43677,17 +43674,17 @@
     </row>
     <row r="2922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2922" s="1" t="s">
-        <v>4553</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="2923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2923" s="1" t="s">
-        <v>4554</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="2924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2924" s="1" t="s">
-        <v>1730</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="2925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43812,32 +43809,32 @@
     </row>
     <row r="2949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2949" s="1" t="s">
-        <v>4579</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="2950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2950" s="1" t="s">
-        <v>4580</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="2951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2951" s="1" t="s">
-        <v>1733</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="2952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2952" s="1" t="s">
-        <v>4581</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="2953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2953" s="1" t="s">
-        <v>4582</v>
+        <v>4581</v>
       </c>
     </row>
     <row r="2954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2954" s="1" t="s">
-        <v>1735</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="2955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44102,17 +44099,17 @@
     </row>
     <row r="3007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3007" s="1" t="s">
-        <v>4635</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="3008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3008" s="1" t="s">
-        <v>4636</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="3009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3009" s="1" t="s">
-        <v>1738</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="3010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44212,17 +44209,17 @@
     </row>
     <row r="3029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3029" s="1" t="s">
-        <v>4656</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="3030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3030" s="1" t="s">
-        <v>4657</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="3031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3031" s="1" t="s">
-        <v>1741</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="3032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44272,17 +44269,17 @@
     </row>
     <row r="3041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3041" s="1" t="s">
-        <v>4667</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="3042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3042" s="1" t="s">
-        <v>4668</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="3043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3043" s="1" t="s">
-        <v>1743</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="3044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44732,17 +44729,17 @@
     </row>
     <row r="3133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3133" s="1" t="s">
-        <v>4758</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="3134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3134" s="1" t="s">
-        <v>4759</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="3135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3135" s="1" t="s">
-        <v>1745</v>
+        <v>4759</v>
       </c>
     </row>
     <row r="3136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44767,17 +44764,17 @@
     </row>
     <row r="3140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3140" s="1" t="s">
-        <v>4764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="3141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3141" s="1" t="s">
-        <v>4765</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="3142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3142" s="1" t="s">
-        <v>1748</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="3143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44862,17 +44859,17 @@
     </row>
     <row r="3159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3159" s="1" t="s">
-        <v>4782</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="3160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3160" s="1" t="s">
-        <v>4783</v>
+        <v>4782</v>
       </c>
     </row>
     <row r="3161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3161" s="1" t="s">
-        <v>1751</v>
+        <v>4783</v>
       </c>
     </row>
     <row r="3162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44897,17 +44894,17 @@
     </row>
     <row r="3166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3166" s="1" t="s">
-        <v>4788</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="3167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3167" s="1" t="s">
-        <v>4789</v>
+        <v>4788</v>
       </c>
     </row>
     <row r="3168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3168" s="1" t="s">
-        <v>1753</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="3169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45082,17 +45079,17 @@
     </row>
     <row r="3203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3203" s="1" t="s">
-        <v>4824</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="3204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3204" s="1" t="s">
-        <v>4825</v>
+        <v>4824</v>
       </c>
     </row>
     <row r="3205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3205" s="1" t="s">
-        <v>1756</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="3206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45172,17 +45169,17 @@
     </row>
     <row r="3221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3221" s="1" t="s">
-        <v>4841</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="3222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3222" s="1" t="s">
-        <v>4842</v>
+        <v>4841</v>
       </c>
     </row>
     <row r="3223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3223" s="1" t="s">
-        <v>1759</v>
+        <v>4842</v>
       </c>
     </row>
     <row r="3224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45222,17 +45219,17 @@
     </row>
     <row r="3231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3231" s="1" t="s">
-        <v>4850</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="3232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3232" s="1" t="s">
-        <v>4851</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="3233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3233" s="1" t="s">
-        <v>1762</v>
+        <v>4851</v>
       </c>
     </row>
     <row r="3234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45367,27 +45364,27 @@
     </row>
     <row r="3260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3260" s="1" t="s">
-        <v>4878</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="3261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3261" s="1" t="s">
-        <v>4879</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="3262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3262" s="1" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="3263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3263" s="1" t="s">
-        <v>4880</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="3264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3264" s="1" t="s">
-        <v>1767</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="3265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45462,17 +45459,17 @@
     </row>
     <row r="3279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3279" s="1" t="s">
-        <v>4895</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="3280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3280" s="1" t="s">
-        <v>4896</v>
+        <v>4895</v>
       </c>
     </row>
     <row r="3281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3281" s="1" t="s">
-        <v>1768</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="3282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45502,17 +45499,17 @@
     </row>
     <row r="3287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3287" s="1" t="s">
-        <v>4902</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="3288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3288" s="1" t="s">
-        <v>4903</v>
+        <v>4902</v>
       </c>
     </row>
     <row r="3289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3289" s="1" t="s">
-        <v>1770</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="3290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45587,17 +45584,17 @@
     </row>
     <row r="3304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3304" s="1" t="s">
-        <v>4918</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="3305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3305" s="1" t="s">
-        <v>4919</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="3306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3306" s="1" t="s">
-        <v>1772</v>
+        <v>4919</v>
       </c>
     </row>
     <row r="3307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45937,17 +45934,17 @@
     </row>
     <row r="3374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3374" s="1" t="s">
-        <v>4987</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="3375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3375" s="1" t="s">
-        <v>4988</v>
+        <v>4987</v>
       </c>
     </row>
     <row r="3376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3376" s="1" t="s">
-        <v>1774</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="3377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46062,17 +46059,17 @@
     </row>
     <row r="3399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3399" s="1" t="s">
-        <v>5011</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="3400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3400" s="1" t="s">
-        <v>5012</v>
+        <v>5011</v>
       </c>
     </row>
     <row r="3401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3401" s="1" t="s">
-        <v>1777</v>
+        <v>5012</v>
       </c>
     </row>
     <row r="3402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46102,17 +46099,17 @@
     </row>
     <row r="3407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3407" s="1" t="s">
-        <v>5018</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="3408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3408" s="1" t="s">
-        <v>5019</v>
+        <v>5018</v>
       </c>
     </row>
     <row r="3409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3409" s="1" t="s">
-        <v>1780</v>
+        <v>5019</v>
       </c>
     </row>
     <row r="3410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46207,17 +46204,17 @@
     </row>
     <row r="3428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3428" s="1" t="s">
-        <v>5038</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="3429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3429" s="1" t="s">
-        <v>5039</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="3430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3430" s="1" t="s">
-        <v>1783</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="3431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46272,17 +46269,17 @@
     </row>
     <row r="3441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3441" s="1" t="s">
-        <v>5050</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="3442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3442" s="1" t="s">
-        <v>5051</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="3443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3443" s="1" t="s">
-        <v>1786</v>
+        <v>5051</v>
       </c>
     </row>
     <row r="3444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46412,17 +46409,17 @@
     </row>
     <row r="3469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3469" s="1" t="s">
-        <v>5077</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="3470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3470" s="1" t="s">
-        <v>5078</v>
+        <v>5077</v>
       </c>
     </row>
     <row r="3471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3471" s="1" t="s">
-        <v>1788</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="3472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46552,17 +46549,17 @@
     </row>
     <row r="3497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3497" s="1" t="s">
-        <v>5104</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="3498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3498" s="1" t="s">
-        <v>5105</v>
+        <v>5104</v>
       </c>
     </row>
     <row r="3499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3499" s="1" t="s">
-        <v>1791</v>
+        <v>5105</v>
       </c>
     </row>
     <row r="3500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46577,17 +46574,17 @@
     </row>
     <row r="3502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3502" s="1" t="s">
-        <v>5108</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="3503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3503" s="1" t="s">
-        <v>5109</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="3504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3504" s="1" t="s">
-        <v>1793</v>
+        <v>5109</v>
       </c>
     </row>
     <row r="3505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46677,17 +46674,17 @@
     </row>
     <row r="3522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3522" s="1" t="s">
-        <v>5127</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="3523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3523" s="1" t="s">
-        <v>5128</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="3524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3524" s="1" t="s">
-        <v>1795</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="3525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46712,17 +46709,17 @@
     </row>
     <row r="3529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3529" s="1" t="s">
-        <v>5133</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="3530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3530" s="1" t="s">
-        <v>5134</v>
+        <v>5133</v>
       </c>
     </row>
     <row r="3531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3531" s="1" t="s">
-        <v>1797</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="3532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46742,17 +46739,17 @@
     </row>
     <row r="3535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3535" s="1" t="s">
-        <v>5138</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="3536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3536" s="1" t="s">
-        <v>5139</v>
+        <v>5138</v>
       </c>
     </row>
     <row r="3537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3537" s="1" t="s">
-        <v>1799</v>
+        <v>5139</v>
       </c>
     </row>
     <row r="3538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46832,27 +46829,27 @@
     </row>
     <row r="3553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3553" s="1" t="s">
-        <v>5155</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="3554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3554" s="1" t="s">
-        <v>5156</v>
+        <v>5155</v>
       </c>
     </row>
     <row r="3555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3555" s="1" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="3556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3556" s="1" t="s">
-        <v>5157</v>
+        <v>5156</v>
       </c>
     </row>
     <row r="3557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3557" s="1" t="s">
-        <v>1803</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="3558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46872,17 +46869,17 @@
     </row>
     <row r="3561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3561" s="1" t="s">
-        <v>5161</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="3562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3562" s="1" t="s">
-        <v>5162</v>
+        <v>5161</v>
       </c>
     </row>
     <row r="3563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3563" s="1" t="s">
-        <v>1806</v>
+        <v>5162</v>
       </c>
     </row>
     <row r="3564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46922,17 +46919,17 @@
     </row>
     <row r="3571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3571" s="1" t="s">
-        <v>5170</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="3572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3572" s="1" t="s">
-        <v>5171</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="3573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3573" s="1" t="s">
-        <v>1808</v>
+        <v>5171</v>
       </c>
     </row>
     <row r="3574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47002,17 +46999,17 @@
     </row>
     <row r="3587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3587" s="1" t="s">
-        <v>5185</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="3588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3588" s="1" t="s">
-        <v>5186</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="3589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3589" s="1" t="s">
-        <v>1810</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="3590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47192,32 +47189,32 @@
     </row>
     <row r="3625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3625" s="1" t="s">
-        <v>5222</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="3626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3626" s="1" t="s">
-        <v>5223</v>
+        <v>5222</v>
       </c>
     </row>
     <row r="3627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3627" s="1" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="3628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3628" s="1" t="s">
-        <v>5224</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="3629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3629" s="1" t="s">
-        <v>1814</v>
+        <v>5223</v>
       </c>
     </row>
     <row r="3630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3630" s="1" t="s">
-        <v>1817</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="3631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47237,17 +47234,17 @@
     </row>
     <row r="3634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3634" s="1" t="s">
-        <v>5228</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="3635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3635" s="1" t="s">
-        <v>5229</v>
+        <v>5228</v>
       </c>
     </row>
     <row r="3636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3636" s="1" t="s">
-        <v>1820</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="3637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47312,17 +47309,17 @@
     </row>
     <row r="3649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3649" s="1" t="s">
-        <v>5242</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="3650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3650" s="1" t="s">
-        <v>5243</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="3651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3651" s="1" t="s">
-        <v>1823</v>
+        <v>5243</v>
       </c>
     </row>
     <row r="3652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47372,17 +47369,17 @@
     </row>
     <row r="3661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3661" s="1" t="s">
-        <v>5253</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="3662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3662" s="1" t="s">
-        <v>5254</v>
+        <v>5253</v>
       </c>
     </row>
     <row r="3663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3663" s="1" t="s">
-        <v>1826</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="3664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47457,17 +47454,17 @@
     </row>
     <row r="3678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3678" s="1" t="s">
-        <v>5269</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="3679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3679" s="1" t="s">
-        <v>5270</v>
+        <v>5269</v>
       </c>
     </row>
     <row r="3680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3680" s="1" t="s">
-        <v>1827</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="3681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47512,17 +47509,17 @@
     </row>
     <row r="3689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3689" s="1" t="s">
-        <v>5279</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="3690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3690" s="1" t="s">
-        <v>5280</v>
+        <v>5279</v>
       </c>
     </row>
     <row r="3691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3691" s="1" t="s">
-        <v>1830</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="3692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47552,22 +47549,22 @@
     </row>
     <row r="3697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3697" s="1" t="s">
-        <v>5286</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="3698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3698" s="1" t="s">
-        <v>5287</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="3699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3699" s="1" t="s">
-        <v>1832</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="3700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3700" s="1" t="s">
-        <v>1834</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="3701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47582,17 +47579,17 @@
     </row>
     <row r="3703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3703" s="1" t="s">
-        <v>5290</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="3704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3704" s="1" t="s">
-        <v>5291</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="3705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3705" s="1" t="s">
-        <v>1837</v>
+        <v>5291</v>
       </c>
     </row>
     <row r="3706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47662,17 +47659,17 @@
     </row>
     <row r="3719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3719" s="1" t="s">
-        <v>5305</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="3720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3720" s="1" t="s">
-        <v>5306</v>
+        <v>5305</v>
       </c>
     </row>
     <row r="3721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3721" s="1" t="s">
-        <v>1840</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="3722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47702,17 +47699,17 @@
     </row>
     <row r="3727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3727" s="1" t="s">
-        <v>5312</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="3728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3728" s="1" t="s">
-        <v>5313</v>
+        <v>5312</v>
       </c>
     </row>
     <row r="3729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3729" s="1" t="s">
-        <v>1842</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="3730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47727,22 +47724,22 @@
     </row>
     <row r="3732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3732" s="1" t="s">
-        <v>5316</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="3733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3733" s="1" t="s">
-        <v>5317</v>
+        <v>5316</v>
       </c>
     </row>
     <row r="3734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3734" s="1" t="s">
-        <v>5318</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="3735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3735" s="1" t="s">
-        <v>1844</v>
+        <v>5318</v>
       </c>
     </row>
     <row r="3736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47772,22 +47769,22 @@
     </row>
     <row r="3741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3741" s="1" t="s">
-        <v>5324</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="3742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3742" s="1" t="s">
-        <v>5325</v>
+        <v>5324</v>
       </c>
     </row>
     <row r="3743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3743" s="1" t="s">
-        <v>5326</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="3744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3744" s="1" t="s">
-        <v>1846</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="3745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47802,22 +47799,22 @@
     </row>
     <row r="3747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3747" s="1" t="s">
-        <v>5329</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="3748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3748" s="1" t="s">
-        <v>5330</v>
+        <v>5329</v>
       </c>
     </row>
     <row r="3749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3749" s="1" t="s">
-        <v>5331</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="3750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3750" s="1" t="s">
-        <v>1848</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="3751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47832,37 +47829,37 @@
     </row>
     <row r="3753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3753" s="1" t="s">
-        <v>5334</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="3754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3754" s="1" t="s">
-        <v>5335</v>
+        <v>5334</v>
       </c>
     </row>
     <row r="3755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3755" s="1" t="s">
-        <v>5336</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="3756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3756" s="1" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="3757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3757" s="1" t="s">
-        <v>5337</v>
+        <v>5336</v>
       </c>
     </row>
     <row r="3758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3758" s="1" t="s">
-        <v>5338</v>
+        <v>5337</v>
       </c>
     </row>
     <row r="3759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3759" s="1" t="s">
-        <v>1853</v>
+        <v>5338</v>
       </c>
     </row>
     <row r="3760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48297,22 +48294,22 @@
     </row>
     <row r="3846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3846" s="1" t="s">
-        <v>5425</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="3847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3847" s="1" t="s">
-        <v>5426</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="3848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3848" s="1" t="s">
-        <v>5427</v>
+        <v>5426</v>
       </c>
     </row>
     <row r="3849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3849" s="1" t="s">
-        <v>1855</v>
+        <v>5427</v>
       </c>
     </row>
     <row r="3850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48402,22 +48399,22 @@
     </row>
     <row r="3867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3867" s="1" t="s">
-        <v>5445</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="3868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3868" s="1" t="s">
-        <v>5446</v>
+        <v>5445</v>
       </c>
     </row>
     <row r="3869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3869" s="1" t="s">
-        <v>5447</v>
+        <v>5446</v>
       </c>
     </row>
     <row r="3870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3870" s="1" t="s">
-        <v>1857</v>
+        <v>5447</v>
       </c>
     </row>
     <row r="3871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48547,32 +48544,32 @@
     </row>
     <row r="3896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3896" s="1" t="s">
-        <v>5473</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="3897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3897" s="1" t="s">
-        <v>5474</v>
+        <v>5473</v>
       </c>
     </row>
     <row r="3898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3898" s="1" t="s">
-        <v>5475</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="3899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3899" s="1" t="s">
-        <v>1859</v>
+        <v>5474</v>
       </c>
     </row>
     <row r="3900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3900" s="1" t="s">
-        <v>5476</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="3901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3901" s="1" t="s">
-        <v>1862</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="3902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48627,42 +48624,42 @@
     </row>
     <row r="3912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3912" s="1" t="s">
-        <v>5487</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="3913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3913" s="1" t="s">
-        <v>5488</v>
+        <v>5487</v>
       </c>
     </row>
     <row r="3914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3914" s="1" t="s">
-        <v>5489</v>
+        <v>5488</v>
       </c>
     </row>
     <row r="3915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3915" s="1" t="s">
-        <v>1864</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="3916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3916" s="1" t="s">
-        <v>5490</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="3917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3917" s="1" t="s">
-        <v>5491</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="3918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3918" s="1" t="s">
-        <v>5492</v>
+        <v>5491</v>
       </c>
     </row>
     <row r="3919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3919" s="1" t="s">
-        <v>1865</v>
+        <v>5492</v>
       </c>
     </row>
     <row r="3920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48742,22 +48739,22 @@
     </row>
     <row r="3935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3935" s="1" t="s">
-        <v>5508</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="3936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3936" s="1" t="s">
-        <v>5509</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="3937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3937" s="1" t="s">
-        <v>5510</v>
+        <v>5509</v>
       </c>
     </row>
     <row r="3938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3938" s="1" t="s">
-        <v>1866</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="3939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48787,22 +48784,22 @@
     </row>
     <row r="3944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3944" s="1" t="s">
-        <v>5516</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="3945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3945" s="1" t="s">
-        <v>5517</v>
+        <v>5516</v>
       </c>
     </row>
     <row r="3946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3946" s="1" t="s">
-        <v>5518</v>
+        <v>5517</v>
       </c>
     </row>
     <row r="3947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3947" s="1" t="s">
-        <v>1868</v>
+        <v>5518</v>
       </c>
     </row>
     <row r="3948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48997,37 +48994,37 @@
     </row>
     <row r="3986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3986" s="1" t="s">
-        <v>5557</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="3987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3987" s="1" t="s">
-        <v>5558</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="3988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3988" s="1" t="s">
-        <v>5559</v>
+        <v>5558</v>
       </c>
     </row>
     <row r="3989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3989" s="1" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="3990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3990" s="1" t="s">
-        <v>5560</v>
+        <v>5559</v>
       </c>
     </row>
     <row r="3991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3991" s="1" t="s">
-        <v>5561</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="3992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3992" s="1" t="s">
-        <v>1872</v>
+        <v>5561</v>
       </c>
     </row>
     <row r="3993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49187,42 +49184,42 @@
     </row>
     <row r="4024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4024" s="1" t="s">
-        <v>5593</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="4025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4025" s="1" t="s">
-        <v>5594</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="4026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4026" s="1" t="s">
-        <v>5595</v>
+        <v>5594</v>
       </c>
     </row>
     <row r="4027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4027" s="1" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="4028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4028" s="1" t="s">
-        <v>5596</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="4029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4029" s="1" t="s">
-        <v>5597</v>
+        <v>5595</v>
       </c>
     </row>
     <row r="4030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4030" s="1" t="s">
-        <v>1875</v>
+        <v>5596</v>
       </c>
     </row>
     <row r="4031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4031" s="1" t="s">
-        <v>1876</v>
+        <v>5597</v>
       </c>
     </row>
     <row r="4032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49272,42 +49269,42 @@
     </row>
     <row r="4041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4041" s="1" t="s">
-        <v>5607</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="4042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4042" s="1" t="s">
-        <v>5608</v>
+        <v>5607</v>
       </c>
     </row>
     <row r="4043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4043" s="1" t="s">
-        <v>5609</v>
+        <v>5608</v>
       </c>
     </row>
     <row r="4044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4044" s="1" t="s">
-        <v>1878</v>
+        <v>5609</v>
       </c>
     </row>
     <row r="4045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4045" s="1" t="s">
-        <v>5610</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="4046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4046" s="1" t="s">
-        <v>5611</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="4047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4047" s="1" t="s">
-        <v>5612</v>
+        <v>5611</v>
       </c>
     </row>
     <row r="4048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4048" s="1" t="s">
-        <v>1880</v>
+        <v>5612</v>
       </c>
     </row>
     <row r="4049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49342,22 +49339,22 @@
     </row>
     <row r="4055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4055" s="1" t="s">
-        <v>5619</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="4056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4056" s="1" t="s">
-        <v>5620</v>
+        <v>5619</v>
       </c>
     </row>
     <row r="4057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4057" s="1" t="s">
-        <v>5621</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="4058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4058" s="1" t="s">
-        <v>1882</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="4059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49437,22 +49434,22 @@
     </row>
     <row r="4074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4074" s="1" t="s">
-        <v>5637</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="4075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4075" s="1" t="s">
-        <v>5638</v>
+        <v>5637</v>
       </c>
     </row>
     <row r="4076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4076" s="1" t="s">
-        <v>5639</v>
+        <v>5638</v>
       </c>
     </row>
     <row r="4077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4077" s="1" t="s">
-        <v>1885</v>
+        <v>5639</v>
       </c>
     </row>
     <row r="4078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49567,22 +49564,22 @@
     </row>
     <row r="4100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4100" s="1" t="s">
-        <v>5662</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="4101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4101" s="1" t="s">
-        <v>5663</v>
+        <v>5662</v>
       </c>
     </row>
     <row r="4102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4102" s="1" t="s">
-        <v>5664</v>
+        <v>5663</v>
       </c>
     </row>
     <row r="4103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4103" s="1" t="s">
-        <v>1887</v>
+        <v>5664</v>
       </c>
     </row>
     <row r="4104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49627,22 +49624,22 @@
     </row>
     <row r="4112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4112" s="1" t="s">
-        <v>5673</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="4113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4113" s="1" t="s">
-        <v>5674</v>
+        <v>5673</v>
       </c>
     </row>
     <row r="4114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4114" s="1" t="s">
-        <v>5675</v>
+        <v>5674</v>
       </c>
     </row>
     <row r="4115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4115" s="1" t="s">
-        <v>1890</v>
+        <v>5675</v>
       </c>
     </row>
     <row r="4116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49777,22 +49774,22 @@
     </row>
     <row r="4142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4142" s="1" t="s">
-        <v>5702</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="4143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4143" s="1" t="s">
-        <v>5703</v>
+        <v>5702</v>
       </c>
     </row>
     <row r="4144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4144" s="1" t="s">
-        <v>5704</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="4145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4145" s="1" t="s">
-        <v>1893</v>
+        <v>5704</v>
       </c>
     </row>
     <row r="4146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49822,22 +49819,22 @@
     </row>
     <row r="4151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4151" s="1" t="s">
-        <v>5710</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="4152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4152" s="1" t="s">
-        <v>5711</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="4153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4153" s="1" t="s">
-        <v>5712</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="4154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4154" s="1" t="s">
-        <v>1894</v>
+        <v>5712</v>
       </c>
     </row>
     <row r="4155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49987,22 +49984,22 @@
     </row>
     <row r="4184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4184" s="1" t="s">
-        <v>5742</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="4185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4185" s="1" t="s">
-        <v>5743</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="4186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4186" s="1" t="s">
-        <v>5744</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="4187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4187" s="1" t="s">
-        <v>1897</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="4188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50077,32 +50074,32 @@
     </row>
     <row r="4202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4202" s="1" t="s">
-        <v>5759</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="4203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4203" s="1" t="s">
-        <v>5760</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="4204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4204" s="1" t="s">
-        <v>5761</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="4205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4205" s="1" t="s">
-        <v>1900</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="4206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4206" s="1" t="s">
-        <v>5762</v>
+        <v>5761</v>
       </c>
     </row>
     <row r="4207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4207" s="1" t="s">
-        <v>1903</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="4208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50282,22 +50279,22 @@
     </row>
     <row r="4243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4243" s="1" t="s">
-        <v>5798</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="4244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4244" s="1" t="s">
-        <v>5799</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="4245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4245" s="1" t="s">
-        <v>5800</v>
+        <v>5799</v>
       </c>
     </row>
     <row r="4246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4246" s="1" t="s">
-        <v>1906</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="4247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50372,57 +50369,57 @@
     </row>
     <row r="4261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4261" s="1" t="s">
-        <v>5815</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="4262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4262" s="1" t="s">
-        <v>5816</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="4263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4263" s="1" t="s">
-        <v>5817</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="4264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4264" s="1" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="4265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4265" s="1" t="s">
-        <v>5818</v>
+        <v>5817</v>
       </c>
     </row>
     <row r="4266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4266" s="1" t="s">
-        <v>5819</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="4267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4267" s="1" t="s">
-        <v>1911</v>
+        <v>5819</v>
       </c>
     </row>
     <row r="4268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4268" s="1" t="s">
-        <v>5820</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="4269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4269" s="1" t="s">
-        <v>5821</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="4270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4270" s="1" t="s">
-        <v>5822</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="4271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4271" s="1" t="s">
-        <v>1913</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="4272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50512,22 +50509,22 @@
     </row>
     <row r="4289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4289" s="1" t="s">
-        <v>5840</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="4290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4290" s="1" t="s">
-        <v>5841</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="4291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4291" s="1" t="s">
-        <v>5842</v>
+        <v>5841</v>
       </c>
     </row>
     <row r="4292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4292" s="1" t="s">
-        <v>1915</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="4293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50557,42 +50554,42 @@
     </row>
     <row r="4298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4298" s="1" t="s">
-        <v>5848</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="4299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4299" s="1" t="s">
-        <v>5849</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="4300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4300" s="1" t="s">
-        <v>5850</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="4301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4301" s="1" t="s">
-        <v>1917</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="4302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4302" s="1" t="s">
-        <v>5851</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="4303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4303" s="1" t="s">
-        <v>5852</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="4304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4304" s="1" t="s">
-        <v>5853</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="4305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4305" s="1" t="s">
-        <v>1919</v>
+        <v>5853</v>
       </c>
     </row>
     <row r="4306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50687,22 +50684,22 @@
     </row>
     <row r="4324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4324" s="1" t="s">
-        <v>5872</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="4325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4325" s="1" t="s">
-        <v>5873</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="4326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4326" s="1" t="s">
-        <v>5874</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="4327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4327" s="1" t="s">
-        <v>1921</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="4328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50757,22 +50754,22 @@
     </row>
     <row r="4338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4338" s="1" t="s">
-        <v>5885</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="4339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4339" s="1" t="s">
-        <v>5886</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="4340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4340" s="1" t="s">
-        <v>5887</v>
+        <v>5886</v>
       </c>
     </row>
     <row r="4341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4341" s="1" t="s">
-        <v>1923</v>
+        <v>5887</v>
       </c>
     </row>
     <row r="4342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50837,32 +50834,32 @@
     </row>
     <row r="4354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4354" s="1" t="s">
-        <v>5900</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="4355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4355" s="1" t="s">
-        <v>5901</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="4356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4356" s="1" t="s">
-        <v>5902</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="4357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4357" s="1" t="s">
-        <v>1925</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="4358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4358" s="1" t="s">
-        <v>5903</v>
+        <v>5902</v>
       </c>
     </row>
     <row r="4359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4359" s="1" t="s">
-        <v>1927</v>
+        <v>5903</v>
       </c>
     </row>
     <row r="4360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50912,42 +50909,42 @@
     </row>
     <row r="4369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4369" s="1" t="s">
-        <v>5913</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="4370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4370" s="1" t="s">
-        <v>5914</v>
+        <v>5913</v>
       </c>
     </row>
     <row r="4371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4371" s="1" t="s">
-        <v>5915</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="4372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4372" s="1" t="s">
-        <v>1929</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="4373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4373" s="1" t="s">
-        <v>5916</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="4374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4374" s="1" t="s">
-        <v>5917</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="4375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4375" s="1" t="s">
-        <v>5918</v>
+        <v>5917</v>
       </c>
     </row>
     <row r="4376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4376" s="1" t="s">
-        <v>1931</v>
+        <v>5918</v>
       </c>
     </row>
     <row r="4377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50962,22 +50959,22 @@
     </row>
     <row r="4379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4379" s="1" t="s">
-        <v>5921</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="4380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4380" s="1" t="s">
-        <v>5922</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="4381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4381" s="1" t="s">
-        <v>5923</v>
+        <v>5922</v>
       </c>
     </row>
     <row r="4382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4382" s="1" t="s">
-        <v>1933</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="4383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51072,22 +51069,22 @@
     </row>
     <row r="4401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4401" s="1" t="s">
-        <v>5942</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="4402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4402" s="1" t="s">
-        <v>5943</v>
+        <v>5942</v>
       </c>
     </row>
     <row r="4403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4403" s="1" t="s">
-        <v>5944</v>
+        <v>5943</v>
       </c>
     </row>
     <row r="4404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4404" s="1" t="s">
-        <v>1935</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="4405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51172,22 +51169,22 @@
     </row>
     <row r="4421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4421" s="1" t="s">
-        <v>5961</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="4422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4422" s="1" t="s">
-        <v>5962</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="4423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4423" s="1" t="s">
-        <v>5963</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="4424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4424" s="1" t="s">
-        <v>1938</v>
+        <v>5963</v>
       </c>
     </row>
     <row r="4425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51217,22 +51214,22 @@
     </row>
     <row r="4430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4430" s="1" t="s">
-        <v>5969</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="4431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4431" s="1" t="s">
-        <v>5970</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="4432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4432" s="1" t="s">
-        <v>5971</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="4433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4433" s="1" t="s">
-        <v>1940</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="4434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51247,42 +51244,42 @@
     </row>
     <row r="4436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4436" s="1" t="s">
-        <v>5974</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="4437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4437" s="1" t="s">
-        <v>5975</v>
+        <v>5974</v>
       </c>
     </row>
     <row r="4438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4438" s="1" t="s">
-        <v>5976</v>
+        <v>5975</v>
       </c>
     </row>
     <row r="4439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4439" s="1" t="s">
-        <v>1942</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="4440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4440" s="1" t="s">
-        <v>5977</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="4441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4441" s="1" t="s">
-        <v>5978</v>
+        <v>5977</v>
       </c>
     </row>
     <row r="4442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4442" s="1" t="s">
-        <v>5979</v>
+        <v>5978</v>
       </c>
     </row>
     <row r="4443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4443" s="1" t="s">
-        <v>1944</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="4444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51352,27 +51349,27 @@
     </row>
     <row r="4457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4457" s="1" t="s">
-        <v>5993</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="4458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4458" s="1" t="s">
-        <v>5994</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="4459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4459" s="1" t="s">
-        <v>5995</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="4460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4460" s="1" t="s">
-        <v>1946</v>
+        <v>5994</v>
       </c>
     </row>
     <row r="4461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4461" s="1" t="s">
-        <v>1948</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="4462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51387,37 +51384,37 @@
     </row>
     <row r="4464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4464" s="1" t="s">
-        <v>5998</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="4465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4465" s="1" t="s">
-        <v>5999</v>
+        <v>5998</v>
       </c>
     </row>
     <row r="4466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4466" s="1" t="s">
-        <v>6000</v>
+        <v>5999</v>
       </c>
     </row>
     <row r="4467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4467" s="1" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="4468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4468" s="1" t="s">
-        <v>6001</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="4469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4469" s="1" t="s">
-        <v>6002</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="4470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4470" s="1" t="s">
-        <v>1953</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="4471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51432,22 +51429,22 @@
     </row>
     <row r="4473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4473" s="1" t="s">
-        <v>6005</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="4474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4474" s="1" t="s">
-        <v>6006</v>
+        <v>6005</v>
       </c>
     </row>
     <row r="4475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4475" s="1" t="s">
-        <v>6007</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="4476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4476" s="1" t="s">
-        <v>1955</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="4477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51482,42 +51479,42 @@
     </row>
     <row r="4483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4483" s="1" t="s">
-        <v>6014</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="4484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4484" s="1" t="s">
-        <v>6015</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="4485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4485" s="1" t="s">
-        <v>6016</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="4486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4486" s="1" t="s">
-        <v>1958</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="4487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4487" s="1" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="4488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4488" s="1" t="s">
-        <v>6017</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="4489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4489" s="1" t="s">
-        <v>6018</v>
+        <v>6017</v>
       </c>
     </row>
     <row r="4490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4490" s="1" t="s">
-        <v>1964</v>
+        <v>6018</v>
       </c>
     </row>
     <row r="4491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51787,22 +51784,22 @@
     </row>
     <row r="4544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4544" s="1" t="s">
-        <v>6072</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="4545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4545" s="1" t="s">
-        <v>6073</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="4546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4546" s="1" t="s">
-        <v>6074</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="4547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4547" s="1" t="s">
-        <v>1967</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="4548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51832,22 +51829,22 @@
     </row>
     <row r="4553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4553" s="1" t="s">
-        <v>6080</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="4554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4554" s="1" t="s">
-        <v>6081</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="4555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4555" s="1" t="s">
-        <v>6082</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="4556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4556" s="1" t="s">
-        <v>1970</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="4557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51877,22 +51874,22 @@
     </row>
     <row r="4562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4562" s="1" t="s">
-        <v>6088</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="4563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4563" s="1" t="s">
-        <v>6089</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="4564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4564" s="1" t="s">
-        <v>6090</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="4565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4565" s="1" t="s">
-        <v>1973</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="4566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51972,22 +51969,22 @@
     </row>
     <row r="4581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4581" s="1" t="s">
-        <v>6106</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="4582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4582" s="1" t="s">
-        <v>6107</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="4583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4583" s="1" t="s">
-        <v>6108</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="4584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4584" s="1" t="s">
-        <v>1976</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="4585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52122,22 +52119,22 @@
     </row>
     <row r="4611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4611" s="1" t="s">
-        <v>6135</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="4612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4612" s="1" t="s">
-        <v>6136</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="4613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4613" s="1" t="s">
-        <v>6137</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="4614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4614" s="1" t="s">
-        <v>1979</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="4615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52182,37 +52179,37 @@
     </row>
     <row r="4623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4623" s="1" t="s">
-        <v>6146</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="4624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4624" s="1" t="s">
-        <v>6147</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="4625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4625" s="1" t="s">
-        <v>6148</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="4626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4626" s="1" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="4627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4627" s="1" t="s">
-        <v>6149</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="4628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4628" s="1" t="s">
-        <v>6150</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="4629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4629" s="1" t="s">
-        <v>1985</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="4630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52287,22 +52284,22 @@
     </row>
     <row r="4644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4644" s="1" t="s">
-        <v>6165</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="4645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4645" s="1" t="s">
-        <v>6166</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="4646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4646" s="1" t="s">
-        <v>6167</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="4647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4647" s="1" t="s">
-        <v>1987</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="4648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52317,57 +52314,57 @@
     </row>
     <row r="4650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4650" s="1" t="s">
-        <v>6170</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="4651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4651" s="1" t="s">
-        <v>6171</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="4652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4652" s="1" t="s">
-        <v>6172</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="4653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4653" s="1" t="s">
-        <v>1989</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="4654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4654" s="1" t="s">
-        <v>6173</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="4655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4655" s="1" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="4656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4656" s="1" t="s">
-        <v>6174</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="4657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4657" s="1" t="s">
-        <v>6175</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="4658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4658" s="1" t="s">
-        <v>1995</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="4659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4659" s="1" t="s">
-        <v>6176</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="4660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4660" s="1" t="s">
-        <v>1998</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="4661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52412,37 +52409,37 @@
     </row>
     <row r="4669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4669" s="1" t="s">
-        <v>6185</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4670" s="1" t="s">
-        <v>6186</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="4671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4671" s="1" t="s">
-        <v>6187</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="4672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4672" s="1" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="4673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4673" s="1" t="s">
-        <v>6188</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="4674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4674" s="1" t="s">
-        <v>6189</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="4675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4675" s="1" t="s">
-        <v>2003</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="4676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52502,27 +52499,12 @@
     </row>
     <row r="4687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4687" s="1" t="s">
-        <v>6201</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="4688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4688" s="1" t="s">
-        <v>6202</v>
-      </c>
-    </row>
-    <row r="4689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4689" s="1" t="s">
-        <v>6203</v>
-      </c>
-    </row>
-    <row r="4690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4690" s="1" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="4691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4691" s="1" t="s">
-        <v>6204</v>
+        <v>6201</v>
       </c>
     </row>
   </sheetData>

--- a/Data/examples.xlsx
+++ b/Data/examples.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="_AOValves" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8762" uniqueCount="6630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8794" uniqueCount="6630">
   <si>
     <t xml:space="preserve">BackgroundLipids</t>
   </si>
@@ -5957,6 +5957,9 @@
     <t xml:space="preserve">Chol</t>
   </si>
   <si>
+    <t xml:space="preserve">CE 20:3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gender, Contraceptives and Individual Metabolic Predisposition Shape a Healthy Plasma Lipidome</t>
   </si>
   <si>
@@ -5978,60 +5981,75 @@
     <t xml:space="preserve">CE 16:0</t>
   </si>
   <si>
+    <t xml:space="preserve">CE 16:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 17:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 18:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 18:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 18:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 19:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 20:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 20:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAG 34:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 20:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAG 34:2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 22:5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE 22:6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 34:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 37:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC 37:4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC-O 16:0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC-O 16:1</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPC-O 18:1</t>
   </si>
   <si>
-    <t xml:space="preserve">CE 16:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 17:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 18:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 18:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 18:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 19:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 20:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 20:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 20:4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 20:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 22:5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE 22:6</t>
-  </si>
-  <si>
     <t xml:space="preserve">TAG 51:1</t>
   </si>
   <si>
+    <t xml:space="preserve">PI 36:1</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAG 32:1</t>
   </si>
   <si>
     <t xml:space="preserve">DAG 32:2</t>
   </si>
   <si>
-    <t xml:space="preserve">DAG 34:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAG 34:2</t>
-  </si>
-  <si>
     <t xml:space="preserve">DAG 34:3</t>
   </si>
   <si>
@@ -6059,9 +6077,6 @@
     <t xml:space="preserve">PC 30:0</t>
   </si>
   <si>
-    <t xml:space="preserve">PC 34:4</t>
-  </si>
-  <si>
     <t xml:space="preserve">PC 35:3</t>
   </si>
   <si>
@@ -6071,12 +6086,6 @@
     <t xml:space="preserve">PC 37:2</t>
   </si>
   <si>
-    <t xml:space="preserve">PC 37:3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC 37:4</t>
-  </si>
-  <si>
     <t xml:space="preserve">PC 38:3</t>
   </si>
   <si>
@@ -6122,12 +6131,6 @@
     <t xml:space="preserve">PC O-40:7</t>
   </si>
   <si>
-    <t xml:space="preserve">LPC-O 16:0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC-O 16:1</t>
-  </si>
-  <si>
     <t xml:space="preserve">PE O-38:6</t>
   </si>
   <si>
@@ -6141,9 +6144,6 @@
   </si>
   <si>
     <t xml:space="preserve">LPE 20:2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PI 36:1</t>
   </si>
   <si>
     <t xml:space="preserve">Cer 34:1;2</t>
@@ -20042,19 +20042,19 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -23561,396 +23561,396 @@
   <dimension ref="A1:K718"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>643</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>10090</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>653</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>659</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>662</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>663</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>669</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>675</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>681</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>687</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>693</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>699</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>705</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>710</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>711</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>717</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>721</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>722</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>727</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>732</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>742</v>
       </c>
     </row>
@@ -23961,16 +23961,16 @@
       <c r="B19" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>647</v>
       </c>
     </row>
@@ -23981,16 +23981,16 @@
       <c r="B20" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>749</v>
       </c>
     </row>
@@ -24001,16 +24001,16 @@
       <c r="B21" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>753</v>
       </c>
     </row>
@@ -24021,16 +24021,16 @@
       <c r="B22" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>709</v>
       </c>
     </row>
@@ -24041,16 +24041,16 @@
       <c r="B23" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>736</v>
       </c>
     </row>
@@ -24061,16 +24061,16 @@
       <c r="B24" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>657</v>
       </c>
     </row>
@@ -24081,16 +24081,16 @@
       <c r="B25" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>769</v>
       </c>
     </row>
@@ -24101,13 +24101,13 @@
       <c r="B26" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>773</v>
       </c>
     </row>
@@ -24118,13 +24118,13 @@
       <c r="B27" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>778</v>
       </c>
     </row>
@@ -24135,13 +24135,13 @@
       <c r="B28" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>782</v>
       </c>
     </row>
@@ -24152,13 +24152,13 @@
       <c r="B29" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>786</v>
       </c>
     </row>
@@ -24169,13 +24169,13 @@
       <c r="B30" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>674</v>
       </c>
     </row>
@@ -24186,13 +24186,13 @@
       <c r="B31" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>793</v>
       </c>
     </row>
@@ -24203,13 +24203,13 @@
       <c r="B32" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>680</v>
       </c>
     </row>
@@ -24220,13 +24220,13 @@
       <c r="B33" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>799</v>
       </c>
     </row>
@@ -24237,13 +24237,13 @@
       <c r="B34" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>803</v>
       </c>
     </row>
@@ -24254,13 +24254,13 @@
       <c r="B35" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>721</v>
       </c>
     </row>
@@ -24268,16 +24268,16 @@
       <c r="A36" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>662</v>
       </c>
     </row>
@@ -24288,13 +24288,13 @@
       <c r="B37" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>813</v>
       </c>
     </row>
@@ -24305,13 +24305,13 @@
       <c r="B38" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" s="1" t="s">
         <v>692</v>
       </c>
     </row>
@@ -24322,13 +24322,13 @@
       <c r="B39" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>819</v>
       </c>
     </row>
@@ -24339,13 +24339,13 @@
       <c r="B40" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>823</v>
       </c>
     </row>
@@ -24356,13 +24356,13 @@
       <c r="B41" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>826</v>
       </c>
     </row>
@@ -24373,13 +24373,13 @@
       <c r="B42" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>831</v>
       </c>
     </row>
@@ -24390,13 +24390,13 @@
       <c r="B43" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="E43" s="0" t="s">
+      <c r="E43" s="1" t="s">
         <v>835</v>
       </c>
     </row>
@@ -24407,13 +24407,13 @@
       <c r="B44" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1" t="s">
         <v>839</v>
       </c>
     </row>
@@ -24424,13 +24424,13 @@
       <c r="B45" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="E45" s="0" t="s">
+      <c r="E45" s="1" t="s">
         <v>843</v>
       </c>
     </row>
@@ -24438,16 +24438,16 @@
       <c r="A46" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="E46" s="0" t="s">
+      <c r="E46" s="1" t="s">
         <v>846</v>
       </c>
     </row>
@@ -24458,13 +24458,13 @@
       <c r="B47" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="E47" s="0" t="s">
+      <c r="E47" s="1" t="s">
         <v>726</v>
       </c>
     </row>
@@ -24475,13 +24475,13 @@
       <c r="B48" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="E48" s="0" t="s">
+      <c r="E48" s="1" t="s">
         <v>854</v>
       </c>
     </row>
@@ -24492,13 +24492,13 @@
       <c r="B49" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="E49" s="0" t="s">
+      <c r="E49" s="1" t="s">
         <v>859</v>
       </c>
     </row>
@@ -24506,16 +24506,16 @@
       <c r="A50" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="E50" s="0" t="s">
+      <c r="E50" s="1" t="s">
         <v>863</v>
       </c>
     </row>
@@ -24526,13 +24526,13 @@
       <c r="B51" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="E51" s="1" t="s">
         <v>868</v>
       </c>
     </row>
@@ -24543,13 +24543,13 @@
       <c r="B52" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" s="1" t="s">
         <v>716</v>
       </c>
     </row>
@@ -24560,13 +24560,13 @@
       <c r="B53" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" s="1" t="s">
         <v>876</v>
       </c>
     </row>
@@ -24577,13 +24577,13 @@
       <c r="B54" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" s="1" t="s">
         <v>880</v>
       </c>
     </row>
@@ -24594,13 +24594,13 @@
       <c r="B55" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" s="1" t="s">
         <v>884</v>
       </c>
     </row>
@@ -24611,13 +24611,13 @@
       <c r="B56" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="C56" s="0" t="s">
+      <c r="C56" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="E56" s="1" t="s">
         <v>887</v>
       </c>
     </row>
@@ -24628,13 +24628,13 @@
       <c r="B57" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="C57" s="0" t="s">
+      <c r="C57" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E57" s="0" t="s">
+      <c r="E57" s="1" t="s">
         <v>749</v>
       </c>
     </row>
@@ -24645,13 +24645,13 @@
       <c r="B58" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="C58" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" s="1" t="s">
         <v>894</v>
       </c>
     </row>
@@ -24662,13 +24662,13 @@
       <c r="B59" s="5" t="s">
         <v>895</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" s="1" t="s">
         <v>898</v>
       </c>
     </row>
@@ -24679,13 +24679,13 @@
       <c r="B60" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="E60" s="0" t="s">
+      <c r="E60" s="1" t="s">
         <v>769</v>
       </c>
     </row>
@@ -24696,13 +24696,13 @@
       <c r="B61" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="E61" s="0" t="s">
+      <c r="E61" s="1" t="s">
         <v>906</v>
       </c>
     </row>
@@ -24713,13 +24713,13 @@
       <c r="B62" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="E62" s="0" t="s">
+      <c r="E62" s="1" t="s">
         <v>910</v>
       </c>
     </row>
@@ -24730,13 +24730,13 @@
       <c r="B63" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="E63" s="0" t="s">
+      <c r="E63" s="1" t="s">
         <v>914</v>
       </c>
     </row>
@@ -24747,13 +24747,13 @@
       <c r="B64" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="E64" s="0" t="s">
+      <c r="E64" s="1" t="s">
         <v>919</v>
       </c>
     </row>
@@ -24764,13 +24764,13 @@
       <c r="B65" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="C65" s="0" t="s">
+      <c r="C65" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="E65" s="0" t="s">
+      <c r="E65" s="1" t="s">
         <v>924</v>
       </c>
     </row>
@@ -24781,13 +24781,13 @@
       <c r="B66" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="E66" s="1" t="s">
         <v>648</v>
       </c>
     </row>
@@ -24798,13 +24798,13 @@
       <c r="B67" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="E67" s="0" t="s">
+      <c r="E67" s="1" t="s">
         <v>710</v>
       </c>
     </row>
@@ -24815,13 +24815,13 @@
       <c r="B68" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="E68" s="1" t="s">
         <v>753</v>
       </c>
     </row>
@@ -24832,13 +24832,13 @@
       <c r="B69" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="E69" s="0" t="s">
+      <c r="E69" s="1" t="s">
         <v>940</v>
       </c>
     </row>
@@ -24849,13 +24849,13 @@
       <c r="B70" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="E70" s="1" t="s">
         <v>704</v>
       </c>
     </row>
@@ -24866,13 +24866,13 @@
       <c r="B71" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C71" s="0" t="s">
+      <c r="C71" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="E71" s="1" t="s">
         <v>686</v>
       </c>
     </row>
@@ -24883,13 +24883,13 @@
       <c r="B72" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="C72" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="E72" s="1" t="s">
         <v>949</v>
       </c>
     </row>
@@ -24900,13 +24900,13 @@
       <c r="B73" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="C73" s="0" t="s">
+      <c r="C73" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="E73" s="1" t="s">
         <v>954</v>
       </c>
     </row>
@@ -24914,13 +24914,13 @@
       <c r="A74" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="E74" s="2" t="s">
         <v>742</v>
       </c>
     </row>
@@ -24928,10 +24928,10 @@
       <c r="A75" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="2" t="s">
         <v>959</v>
       </c>
     </row>
@@ -24939,10 +24939,10 @@
       <c r="A76" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="2" t="s">
         <v>962</v>
       </c>
     </row>
@@ -24950,10 +24950,10 @@
       <c r="A77" s="5" t="s">
         <v>895</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="2" t="s">
         <v>964</v>
       </c>
     </row>
@@ -24961,10 +24961,10 @@
       <c r="A78" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="2" t="s">
         <v>967</v>
       </c>
     </row>
@@ -24972,10 +24972,10 @@
       <c r="A79" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="2" t="s">
         <v>969</v>
       </c>
     </row>
@@ -24983,10 +24983,10 @@
       <c r="A80" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="2" t="s">
         <v>972</v>
       </c>
     </row>
@@ -24994,10 +24994,10 @@
       <c r="A81" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="2" t="s">
         <v>975</v>
       </c>
     </row>
@@ -25005,10 +25005,10 @@
       <c r="A82" s="5" t="s">
         <v>976</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="2" t="s">
         <v>978</v>
       </c>
     </row>
@@ -25016,10 +25016,10 @@
       <c r="A83" s="5" t="s">
         <v>979</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="2" t="s">
         <v>981</v>
       </c>
     </row>
@@ -25027,10 +25027,10 @@
       <c r="A84" s="5" t="s">
         <v>982</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="2" t="s">
         <v>984</v>
       </c>
     </row>
@@ -25038,10 +25038,10 @@
       <c r="A85" s="5" t="s">
         <v>985</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="2" t="s">
         <v>987</v>
       </c>
     </row>
@@ -25049,10 +25049,10 @@
       <c r="A86" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="2" t="s">
         <v>990</v>
       </c>
     </row>
@@ -25060,10 +25060,10 @@
       <c r="A87" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="2" t="s">
         <v>992</v>
       </c>
     </row>
@@ -25071,10 +25071,10 @@
       <c r="A88" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="2" t="s">
         <v>994</v>
       </c>
     </row>
@@ -25082,10 +25082,10 @@
       <c r="A89" s="5" t="s">
         <v>995</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="2" t="s">
         <v>997</v>
       </c>
     </row>
@@ -25093,10 +25093,10 @@
       <c r="A90" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="2" t="s">
         <v>1000</v>
       </c>
     </row>
@@ -25104,10 +25104,10 @@
       <c r="A91" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="2" t="s">
         <v>1003</v>
       </c>
     </row>
@@ -25115,10 +25115,10 @@
       <c r="A92" s="5" t="s">
         <v>1004</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="2" t="s">
         <v>1006</v>
       </c>
     </row>
@@ -25126,10 +25126,10 @@
       <c r="A93" s="5" t="s">
         <v>1007</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="2" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -25137,10 +25137,10 @@
       <c r="A94" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
@@ -25148,10 +25148,10 @@
       <c r="A95" s="5" t="s">
         <v>1012</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="2" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -25159,10 +25159,10 @@
       <c r="A96" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="2" t="s">
         <v>1016</v>
       </c>
     </row>
@@ -25170,10 +25170,10 @@
       <c r="A97" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
@@ -25181,10 +25181,10 @@
       <c r="A98" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="2" t="s">
         <v>1020</v>
       </c>
     </row>
@@ -25192,10 +25192,10 @@
       <c r="A99" s="5" t="s">
         <v>1021</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="2" t="s">
         <v>1023</v>
       </c>
     </row>
@@ -25203,10 +25203,10 @@
       <c r="A100" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="2" t="s">
         <v>1026</v>
       </c>
     </row>
@@ -25214,10 +25214,10 @@
       <c r="A101" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -25225,10 +25225,10 @@
       <c r="A102" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="2" t="s">
         <v>1032</v>
       </c>
     </row>
@@ -25236,10 +25236,10 @@
       <c r="A103" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="2" t="s">
         <v>1035</v>
       </c>
     </row>
@@ -25247,10 +25247,10 @@
       <c r="A104" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="2" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -25258,10 +25258,10 @@
       <c r="A105" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="2" t="s">
         <v>1041</v>
       </c>
     </row>
@@ -25269,10 +25269,10 @@
       <c r="A106" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
@@ -25280,10 +25280,10 @@
       <c r="A107" s="5" t="s">
         <v>1045</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -25291,10 +25291,10 @@
       <c r="A108" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="2" t="s">
         <v>1049</v>
       </c>
     </row>
@@ -25302,10 +25302,10 @@
       <c r="A109" s="5" t="s">
         <v>1050</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="2" t="s">
         <v>1052</v>
       </c>
     </row>
@@ -25313,10 +25313,10 @@
       <c r="A110" s="5" t="s">
         <v>1053</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="2" t="s">
         <v>1055</v>
       </c>
     </row>
@@ -25324,10 +25324,10 @@
       <c r="A111" s="5" t="s">
         <v>1056</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="2" t="s">
         <v>1058</v>
       </c>
     </row>
@@ -25335,10 +25335,10 @@
       <c r="A112" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="2" t="s">
         <v>1060</v>
       </c>
     </row>
@@ -25346,10 +25346,10 @@
       <c r="A113" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="2" t="s">
         <v>1063</v>
       </c>
     </row>
@@ -25357,10 +25357,10 @@
       <c r="A114" s="5" t="s">
         <v>1064</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="2" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -25368,10 +25368,10 @@
       <c r="A115" s="5" t="s">
         <v>1067</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="D115" s="2" t="s">
         <v>1069</v>
       </c>
     </row>
@@ -25379,10 +25379,10 @@
       <c r="A116" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="2" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -25390,10 +25390,10 @@
       <c r="A117" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="C117" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="2" t="s">
         <v>1073</v>
       </c>
     </row>
@@ -25401,10 +25401,10 @@
       <c r="A118" s="5" t="s">
         <v>1074</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="2" t="s">
         <v>1076</v>
       </c>
     </row>
@@ -25412,10 +25412,10 @@
       <c r="A119" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="2" t="s">
         <v>1078</v>
       </c>
     </row>
@@ -25423,10 +25423,10 @@
       <c r="A120" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C120" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="D120" s="2" t="s">
         <v>1080</v>
       </c>
     </row>
@@ -25434,10 +25434,10 @@
       <c r="A121" s="5" t="s">
         <v>1081</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="2" t="s">
         <v>1083</v>
       </c>
     </row>
@@ -25445,10 +25445,10 @@
       <c r="A122" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D122" s="2" t="s">
         <v>1086</v>
       </c>
     </row>
@@ -25456,10 +25456,10 @@
       <c r="A123" s="5" t="s">
         <v>1087</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C123" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D123" s="2" t="s">
         <v>1089</v>
       </c>
     </row>
@@ -25467,10 +25467,10 @@
       <c r="A124" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="2" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -25478,10 +25478,10 @@
       <c r="A125" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C125" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="D125" s="2" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -25489,10 +25489,10 @@
       <c r="A126" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D126" s="2" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -25500,10 +25500,10 @@
       <c r="A127" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C127" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="D127" s="6" t="s">
+      <c r="D127" s="2" t="s">
         <v>1099</v>
       </c>
     </row>
@@ -25511,10 +25511,10 @@
       <c r="A128" s="5" t="s">
         <v>1100</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="C128" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D128" s="2" t="s">
         <v>1102</v>
       </c>
     </row>
@@ -25522,10 +25522,10 @@
       <c r="A129" s="4" t="s">
         <v>1103</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D129" s="2" t="s">
         <v>1105</v>
       </c>
     </row>
@@ -25533,10 +25533,10 @@
       <c r="A130" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="C130" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="D130" s="2" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -25544,10 +25544,10 @@
       <c r="A131" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="C131" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="D131" s="6" t="s">
+      <c r="D131" s="2" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -25555,10 +25555,10 @@
       <c r="A132" s="5" t="s">
         <v>1110</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D132" s="2" t="s">
         <v>1112</v>
       </c>
     </row>
@@ -25566,10 +25566,10 @@
       <c r="A133" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="D133" s="6" t="s">
+      <c r="D133" s="2" t="s">
         <v>1114</v>
       </c>
     </row>
@@ -25577,10 +25577,10 @@
       <c r="A134" s="5" t="s">
         <v>1115</v>
       </c>
-      <c r="C134" s="6" t="s">
+      <c r="C134" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="2" t="s">
         <v>1117</v>
       </c>
     </row>
@@ -25588,10 +25588,10 @@
       <c r="A135" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="C135" s="6" t="s">
+      <c r="C135" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="D135" s="2" t="s">
         <v>1119</v>
       </c>
     </row>
@@ -25599,10 +25599,10 @@
       <c r="A136" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="D136" s="6" t="s">
+      <c r="D136" s="2" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -25610,10 +25610,10 @@
       <c r="A137" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="C137" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D137" s="2" t="s">
         <v>1124</v>
       </c>
     </row>
@@ -25621,10 +25621,10 @@
       <c r="A138" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="C138" s="6" t="s">
+      <c r="C138" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="2" t="s">
         <v>1126</v>
       </c>
     </row>
@@ -25632,10 +25632,10 @@
       <c r="A139" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="C139" s="6" t="s">
+      <c r="C139" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D139" s="2" t="s">
         <v>1128</v>
       </c>
     </row>
@@ -25643,10 +25643,10 @@
       <c r="A140" s="5" t="s">
         <v>1129</v>
       </c>
-      <c r="C140" s="6" t="s">
+      <c r="C140" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="2" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -25654,10 +25654,10 @@
       <c r="A141" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D141" s="2" t="s">
         <v>1133</v>
       </c>
     </row>
@@ -25665,10 +25665,10 @@
       <c r="A142" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="C142" s="6" t="s">
+      <c r="C142" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D142" s="2" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -25676,10 +25676,10 @@
       <c r="A143" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D143" s="2" t="s">
         <v>1137</v>
       </c>
     </row>
@@ -25687,10 +25687,10 @@
       <c r="A144" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C144" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="D144" s="2" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -25698,10 +25698,10 @@
       <c r="A145" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C145" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D145" s="2" t="s">
         <v>1141</v>
       </c>
     </row>
@@ -25709,10 +25709,10 @@
       <c r="A146" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C146" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="2" t="s">
         <v>1143</v>
       </c>
     </row>
@@ -25720,10 +25720,10 @@
       <c r="A147" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C147" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="D147" s="2" t="s">
         <v>1145</v>
       </c>
     </row>
@@ -25731,10 +25731,10 @@
       <c r="A148" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="D148" s="2" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -25742,10 +25742,10 @@
       <c r="A149" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C149" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="D149" s="2" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -25753,10 +25753,10 @@
       <c r="A150" s="5" t="s">
         <v>1150</v>
       </c>
-      <c r="C150" s="6" t="s">
+      <c r="C150" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="D150" s="2" t="s">
         <v>1152</v>
       </c>
     </row>
@@ -25764,10 +25764,10 @@
       <c r="A151" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="C151" s="6" t="s">
+      <c r="C151" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="D151" s="2" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -25775,10 +25775,10 @@
       <c r="A152" s="5" t="s">
         <v>1156</v>
       </c>
-      <c r="C152" s="6" t="s">
+      <c r="C152" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D152" s="2" t="s">
         <v>1158</v>
       </c>
     </row>
@@ -25786,10 +25786,10 @@
       <c r="A153" s="5" t="s">
         <v>1159</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="D153" s="2" t="s">
         <v>1161</v>
       </c>
     </row>
@@ -25797,10 +25797,10 @@
       <c r="A154" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C154" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D154" s="2" t="s">
         <v>1164</v>
       </c>
     </row>
@@ -25808,10 +25808,10 @@
       <c r="A155" s="5" t="s">
         <v>1165</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C155" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="2" t="s">
         <v>1167</v>
       </c>
     </row>
@@ -25819,10 +25819,10 @@
       <c r="A156" s="5" t="s">
         <v>1168</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C156" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="D156" s="6" t="s">
+      <c r="D156" s="2" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -25830,10 +25830,10 @@
       <c r="A157" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C157" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="D157" s="6" t="s">
+      <c r="D157" s="2" t="s">
         <v>1172</v>
       </c>
     </row>
@@ -25841,10 +25841,10 @@
       <c r="A158" s="5" t="s">
         <v>1173</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="D158" s="2" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -25852,10 +25852,10 @@
       <c r="A159" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="C159" s="6" t="s">
+      <c r="C159" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="D159" s="6" t="s">
+      <c r="D159" s="2" t="s">
         <v>1178</v>
       </c>
     </row>
@@ -25863,10 +25863,10 @@
       <c r="A160" s="5" t="s">
         <v>1179</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C160" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="D160" s="2" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -25874,10 +25874,10 @@
       <c r="A161" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C161" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="D161" s="6" t="s">
+      <c r="D161" s="2" t="s">
         <v>1183</v>
       </c>
     </row>
@@ -25885,10 +25885,10 @@
       <c r="A162" s="5" t="s">
         <v>1184</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C162" s="2" t="s">
         <v>1185</v>
       </c>
-      <c r="D162" s="6" t="s">
+      <c r="D162" s="2" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -25896,10 +25896,10 @@
       <c r="A163" s="5" t="s">
         <v>1187</v>
       </c>
-      <c r="C163" s="6" t="s">
+      <c r="C163" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="D163" s="6" t="s">
+      <c r="D163" s="2" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -25907,10 +25907,10 @@
       <c r="A164" s="5" t="s">
         <v>1190</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C164" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="D164" s="6" t="s">
+      <c r="D164" s="2" t="s">
         <v>1192</v>
       </c>
     </row>
@@ -25918,10 +25918,10 @@
       <c r="A165" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C165" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="D165" s="6" t="s">
+      <c r="D165" s="2" t="s">
         <v>1194</v>
       </c>
     </row>
@@ -25929,10 +25929,10 @@
       <c r="A166" s="5" t="s">
         <v>1195</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C166" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="D166" s="6" t="s">
+      <c r="D166" s="2" t="s">
         <v>1197</v>
       </c>
     </row>
@@ -25940,10 +25940,10 @@
       <c r="A167" s="5" t="s">
         <v>1198</v>
       </c>
-      <c r="C167" s="6" t="s">
+      <c r="C167" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="D167" s="6" t="s">
+      <c r="D167" s="2" t="s">
         <v>1200</v>
       </c>
     </row>
@@ -25951,10 +25951,10 @@
       <c r="A168" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="C168" s="6" t="s">
+      <c r="C168" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="D168" s="6" t="s">
+      <c r="D168" s="2" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -25962,10 +25962,10 @@
       <c r="A169" s="5" t="s">
         <v>1204</v>
       </c>
-      <c r="C169" s="6" t="s">
+      <c r="C169" s="2" t="s">
         <v>1205</v>
       </c>
-      <c r="D169" s="6" t="s">
+      <c r="D169" s="2" t="s">
         <v>1206</v>
       </c>
     </row>
@@ -25973,10 +25973,10 @@
       <c r="A170" s="5" t="s">
         <v>1207</v>
       </c>
-      <c r="C170" s="6" t="s">
+      <c r="C170" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="D170" s="6" t="s">
+      <c r="D170" s="2" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -25984,10 +25984,10 @@
       <c r="A171" s="5" t="s">
         <v>1210</v>
       </c>
-      <c r="C171" s="6" t="s">
+      <c r="C171" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="D171" s="6" t="s">
+      <c r="D171" s="2" t="s">
         <v>1212</v>
       </c>
     </row>
@@ -25995,10 +25995,10 @@
       <c r="A172" s="4" t="s">
         <v>1213</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C172" s="2" t="s">
         <v>1214</v>
       </c>
-      <c r="D172" s="6" t="s">
+      <c r="D172" s="2" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -26006,10 +26006,10 @@
       <c r="A173" s="5" t="s">
         <v>1216</v>
       </c>
-      <c r="C173" s="6" t="s">
+      <c r="C173" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="D173" s="6" t="s">
+      <c r="D173" s="2" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -26017,10 +26017,10 @@
       <c r="A174" s="5" t="s">
         <v>1219</v>
       </c>
-      <c r="C174" s="6" t="s">
+      <c r="C174" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="D174" s="6" t="s">
+      <c r="D174" s="2" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -26028,10 +26028,10 @@
       <c r="A175" s="5" t="s">
         <v>1222</v>
       </c>
-      <c r="C175" s="6" t="s">
+      <c r="C175" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="D175" s="6" t="s">
+      <c r="D175" s="2" t="s">
         <v>1224</v>
       </c>
     </row>
@@ -26039,10 +26039,10 @@
       <c r="A176" s="5" t="s">
         <v>1225</v>
       </c>
-      <c r="C176" s="6" t="s">
+      <c r="C176" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="D176" s="6" t="s">
+      <c r="D176" s="2" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -26050,10 +26050,10 @@
       <c r="A177" s="5" t="s">
         <v>1228</v>
       </c>
-      <c r="C177" s="6" t="s">
+      <c r="C177" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="D177" s="6" t="s">
+      <c r="D177" s="2" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -26061,10 +26061,10 @@
       <c r="A178" s="5" t="s">
         <v>1231</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C178" s="2" t="s">
         <v>1232</v>
       </c>
-      <c r="D178" s="6" t="s">
+      <c r="D178" s="2" t="s">
         <v>1233</v>
       </c>
     </row>
@@ -26072,10 +26072,10 @@
       <c r="A179" s="5" t="s">
         <v>1234</v>
       </c>
-      <c r="C179" s="6" t="s">
+      <c r="C179" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="D179" s="6" t="s">
+      <c r="D179" s="2" t="s">
         <v>1236</v>
       </c>
     </row>
@@ -26083,10 +26083,10 @@
       <c r="A180" s="5" t="s">
         <v>1237</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C180" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="D180" s="6" t="s">
+      <c r="D180" s="2" t="s">
         <v>1239</v>
       </c>
     </row>
@@ -26094,10 +26094,10 @@
       <c r="A181" s="5" t="s">
         <v>1240</v>
       </c>
-      <c r="C181" s="6" t="s">
+      <c r="C181" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="D181" s="6" t="s">
+      <c r="D181" s="2" t="s">
         <v>1242</v>
       </c>
     </row>
@@ -26105,10 +26105,10 @@
       <c r="A182" s="5" t="s">
         <v>1243</v>
       </c>
-      <c r="C182" s="6" t="s">
+      <c r="C182" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="D182" s="6" t="s">
+      <c r="D182" s="2" t="s">
         <v>1245</v>
       </c>
     </row>
@@ -26116,10 +26116,10 @@
       <c r="A183" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="C183" s="6" t="s">
+      <c r="C183" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="D183" s="6" t="s">
+      <c r="D183" s="2" t="s">
         <v>1247</v>
       </c>
     </row>
@@ -26127,10 +26127,10 @@
       <c r="A184" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="C184" s="6" t="s">
+      <c r="C184" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="D184" s="6" t="s">
+      <c r="D184" s="2" t="s">
         <v>1249</v>
       </c>
     </row>
@@ -26138,54 +26138,54 @@
       <c r="A185" s="5" t="s">
         <v>1250</v>
       </c>
-      <c r="C185" s="6" t="s">
+      <c r="C185" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="D185" s="6" t="s">
+      <c r="D185" s="2" t="s">
         <v>1252</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0" t="s">
+      <c r="A186" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="C186" s="0" t="s">
+      <c r="C186" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="D186" s="0" t="s">
+      <c r="D186" s="1" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0" t="s">
+      <c r="A187" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="C187" s="0" t="s">
+      <c r="C187" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="D187" s="0" t="s">
+      <c r="D187" s="1" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0" t="s">
+      <c r="A188" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="C188" s="0" t="s">
+      <c r="C188" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="D188" s="0" t="s">
+      <c r="D188" s="1" t="s">
         <v>1261</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0" t="s">
+      <c r="A189" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="C189" s="0" t="s">
+      <c r="C189" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="D189" s="0" t="s">
+      <c r="D189" s="1" t="s">
         <v>1264</v>
       </c>
     </row>
@@ -26193,10 +26193,10 @@
       <c r="A190" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="C190" s="6" t="s">
+      <c r="C190" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="D190" s="6" t="s">
+      <c r="D190" s="2" t="s">
         <v>1266</v>
       </c>
     </row>
@@ -26204,10 +26204,10 @@
       <c r="A191" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="C191" s="6" t="s">
+      <c r="C191" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="D191" s="6" t="s">
+      <c r="D191" s="2" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -26215,10 +26215,10 @@
       <c r="A192" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="C192" s="6" t="s">
+      <c r="C192" s="2" t="s">
         <v>1269</v>
       </c>
-      <c r="D192" s="6" t="s">
+      <c r="D192" s="2" t="s">
         <v>1270</v>
       </c>
     </row>
@@ -26226,10 +26226,10 @@
       <c r="A193" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="C193" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="D193" s="6" t="s">
+      <c r="D193" s="2" t="s">
         <v>1272</v>
       </c>
     </row>
@@ -26237,10 +26237,10 @@
       <c r="A194" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="C194" s="6" t="s">
+      <c r="C194" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="D194" s="6" t="s">
+      <c r="D194" s="2" t="s">
         <v>1274</v>
       </c>
     </row>
@@ -26248,10 +26248,10 @@
       <c r="A195" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="C195" s="6" t="s">
+      <c r="C195" s="2" t="s">
         <v>1275</v>
       </c>
-      <c r="D195" s="6" t="s">
+      <c r="D195" s="2" t="s">
         <v>1276</v>
       </c>
     </row>
@@ -26259,10 +26259,10 @@
       <c r="A196" s="5" t="s">
         <v>1277</v>
       </c>
-      <c r="C196" s="6" t="s">
+      <c r="C196" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="D196" s="6" t="s">
+      <c r="D196" s="2" t="s">
         <v>1279</v>
       </c>
     </row>
@@ -26270,10 +26270,10 @@
       <c r="A197" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="C197" s="6" t="s">
+      <c r="C197" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="D197" s="6" t="s">
+      <c r="D197" s="2" t="s">
         <v>1281</v>
       </c>
     </row>
@@ -26281,10 +26281,10 @@
       <c r="A198" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="C198" s="6" t="s">
+      <c r="C198" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="D198" s="6" t="s">
+      <c r="D198" s="2" t="s">
         <v>1283</v>
       </c>
     </row>
@@ -26292,10 +26292,10 @@
       <c r="A199" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="C199" s="6" t="s">
+      <c r="C199" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="D199" s="6" t="s">
+      <c r="D199" s="2" t="s">
         <v>1285</v>
       </c>
     </row>
@@ -26303,10 +26303,10 @@
       <c r="A200" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="C200" s="6" t="s">
+      <c r="C200" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="D200" s="6" t="s">
+      <c r="D200" s="2" t="s">
         <v>1288</v>
       </c>
     </row>
@@ -26314,10 +26314,10 @@
       <c r="A201" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="C201" s="6" t="s">
+      <c r="C201" s="2" t="s">
         <v>1289</v>
       </c>
-      <c r="D201" s="6" t="s">
+      <c r="D201" s="2" t="s">
         <v>1290</v>
       </c>
     </row>
@@ -26325,10 +26325,10 @@
       <c r="A202" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="C202" s="6" t="s">
+      <c r="C202" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="D202" s="6" t="s">
+      <c r="D202" s="2" t="s">
         <v>1292</v>
       </c>
     </row>
@@ -26336,10 +26336,10 @@
       <c r="A203" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="C203" s="6" t="s">
+      <c r="C203" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="D203" s="6" t="s">
+      <c r="D203" s="2" t="s">
         <v>1294</v>
       </c>
     </row>
@@ -26347,10 +26347,10 @@
       <c r="A204" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C204" s="6" t="s">
+      <c r="C204" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="D204" s="6" t="s">
+      <c r="D204" s="2" t="s">
         <v>1296</v>
       </c>
     </row>
@@ -26358,10 +26358,10 @@
       <c r="A205" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C205" s="2" t="s">
         <v>1297</v>
       </c>
-      <c r="D205" s="6" t="s">
+      <c r="D205" s="2" t="s">
         <v>1298</v>
       </c>
     </row>
@@ -26369,10 +26369,10 @@
       <c r="A206" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C206" s="6" t="s">
+      <c r="C206" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="D206" s="6" t="s">
+      <c r="D206" s="2" t="s">
         <v>1300</v>
       </c>
     </row>
@@ -26380,10 +26380,10 @@
       <c r="A207" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="C207" s="6" t="s">
+      <c r="C207" s="2" t="s">
         <v>1301</v>
       </c>
-      <c r="D207" s="6" t="s">
+      <c r="D207" s="2" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -26391,10 +26391,10 @@
       <c r="A208" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="C208" s="6" t="s">
+      <c r="C208" s="2" t="s">
         <v>1303</v>
       </c>
-      <c r="D208" s="6" t="s">
+      <c r="D208" s="2" t="s">
         <v>1304</v>
       </c>
     </row>
@@ -26402,10 +26402,10 @@
       <c r="A209" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="C209" s="6" t="s">
+      <c r="C209" s="2" t="s">
         <v>1305</v>
       </c>
-      <c r="D209" s="6" t="s">
+      <c r="D209" s="2" t="s">
         <v>1306</v>
       </c>
     </row>
@@ -26413,10 +26413,10 @@
       <c r="A210" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="C210" s="6" t="s">
+      <c r="C210" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="D210" s="6" t="s">
+      <c r="D210" s="2" t="s">
         <v>1308</v>
       </c>
     </row>
@@ -26424,10 +26424,10 @@
       <c r="A211" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="C211" s="6" t="s">
+      <c r="C211" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="D211" s="6" t="s">
+      <c r="D211" s="2" t="s">
         <v>1310</v>
       </c>
     </row>
@@ -26435,10 +26435,10 @@
       <c r="A212" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C212" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="D212" s="6" t="s">
+      <c r="D212" s="2" t="s">
         <v>1312</v>
       </c>
     </row>
@@ -26446,10 +26446,10 @@
       <c r="A213" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="C213" s="6" t="s">
+      <c r="C213" s="2" t="s">
         <v>1313</v>
       </c>
-      <c r="D213" s="6" t="s">
+      <c r="D213" s="2" t="s">
         <v>1314</v>
       </c>
     </row>
@@ -26457,10 +26457,10 @@
       <c r="A214" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C214" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="D214" s="6" t="s">
+      <c r="D214" s="2" t="s">
         <v>1316</v>
       </c>
     </row>
@@ -26468,10 +26468,10 @@
       <c r="A215" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C215" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="D215" s="6" t="s">
+      <c r="D215" s="2" t="s">
         <v>1318</v>
       </c>
     </row>
@@ -26479,10 +26479,10 @@
       <c r="A216" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C216" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="D216" s="6" t="s">
+      <c r="D216" s="2" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -26490,10 +26490,10 @@
       <c r="A217" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C217" s="2" t="s">
         <v>1321</v>
       </c>
-      <c r="D217" s="6" t="s">
+      <c r="D217" s="2" t="s">
         <v>1322</v>
       </c>
     </row>
@@ -26501,10 +26501,10 @@
       <c r="A218" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="C218" s="6" t="s">
+      <c r="C218" s="2" t="s">
         <v>1323</v>
       </c>
-      <c r="D218" s="6" t="s">
+      <c r="D218" s="2" t="s">
         <v>1324</v>
       </c>
     </row>
@@ -26512,10 +26512,10 @@
       <c r="A219" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C219" s="6" t="s">
+      <c r="C219" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="D219" s="6" t="s">
+      <c r="D219" s="2" t="s">
         <v>1326</v>
       </c>
     </row>
@@ -26523,10 +26523,10 @@
       <c r="A220" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="C220" s="6" t="s">
+      <c r="C220" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="D220" s="6" t="s">
+      <c r="D220" s="2" t="s">
         <v>1328</v>
       </c>
     </row>
@@ -26534,10 +26534,10 @@
       <c r="A221" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="C221" s="6" t="s">
+      <c r="C221" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="D221" s="6" t="s">
+      <c r="D221" s="2" t="s">
         <v>1330</v>
       </c>
     </row>
@@ -26545,10 +26545,10 @@
       <c r="A222" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="C222" s="6" t="s">
+      <c r="C222" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="D222" s="6" t="s">
+      <c r="D222" s="2" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -26556,10 +26556,10 @@
       <c r="A223" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="C223" s="6" t="s">
+      <c r="C223" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="D223" s="6" t="s">
+      <c r="D223" s="2" t="s">
         <v>1334</v>
       </c>
     </row>
@@ -26567,10 +26567,10 @@
       <c r="A224" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="C224" s="6" t="s">
+      <c r="C224" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="D224" s="6" t="s">
+      <c r="D224" s="2" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -26578,10 +26578,10 @@
       <c r="A225" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="C225" s="6" t="s">
+      <c r="C225" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="D225" s="6" t="s">
+      <c r="D225" s="2" t="s">
         <v>1338</v>
       </c>
     </row>
@@ -26589,10 +26589,10 @@
       <c r="A226" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C226" s="6" t="s">
+      <c r="C226" s="2" t="s">
         <v>1339</v>
       </c>
-      <c r="D226" s="6" t="s">
+      <c r="D226" s="2" t="s">
         <v>1340</v>
       </c>
     </row>
@@ -26600,10 +26600,10 @@
       <c r="A227" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="C227" s="6" t="s">
+      <c r="C227" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="D227" s="6" t="s">
+      <c r="D227" s="2" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -26611,10 +26611,10 @@
       <c r="A228" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="C228" s="6" t="s">
+      <c r="C228" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="D228" s="6" t="s">
+      <c r="D228" s="2" t="s">
         <v>1344</v>
       </c>
     </row>
@@ -26622,10 +26622,10 @@
       <c r="A229" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="C229" s="6" t="s">
+      <c r="C229" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="D229" s="6" t="s">
+      <c r="D229" s="2" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -26633,10 +26633,10 @@
       <c r="A230" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="C230" s="6" t="s">
+      <c r="C230" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="D230" s="6" t="s">
+      <c r="D230" s="2" t="s">
         <v>1348</v>
       </c>
     </row>
@@ -26644,10 +26644,10 @@
       <c r="A231" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="C231" s="6" t="s">
+      <c r="C231" s="2" t="s">
         <v>1349</v>
       </c>
-      <c r="D231" s="6" t="s">
+      <c r="D231" s="2" t="s">
         <v>1350</v>
       </c>
     </row>
@@ -26655,10 +26655,10 @@
       <c r="A232" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C232" s="6" t="s">
+      <c r="C232" s="2" t="s">
         <v>1351</v>
       </c>
-      <c r="D232" s="6" t="s">
+      <c r="D232" s="2" t="s">
         <v>1352</v>
       </c>
     </row>
@@ -26666,10 +26666,10 @@
       <c r="A233" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="C233" s="6" t="s">
+      <c r="C233" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="D233" s="6" t="s">
+      <c r="D233" s="2" t="s">
         <v>1354</v>
       </c>
     </row>
@@ -26677,10 +26677,10 @@
       <c r="A234" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C234" s="6" t="s">
+      <c r="C234" s="2" t="s">
         <v>1355</v>
       </c>
-      <c r="D234" s="6" t="s">
+      <c r="D234" s="2" t="s">
         <v>1356</v>
       </c>
     </row>
@@ -26688,10 +26688,10 @@
       <c r="A235" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="C235" s="6" t="s">
+      <c r="C235" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="D235" s="6" t="s">
+      <c r="D235" s="2" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -26699,10 +26699,10 @@
       <c r="A236" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="C236" s="6" t="s">
+      <c r="C236" s="2" t="s">
         <v>1359</v>
       </c>
-      <c r="D236" s="6" t="s">
+      <c r="D236" s="2" t="s">
         <v>1360</v>
       </c>
     </row>
@@ -26710,10 +26710,10 @@
       <c r="A237" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="C237" s="6" t="s">
+      <c r="C237" s="2" t="s">
         <v>1361</v>
       </c>
-      <c r="D237" s="6" t="s">
+      <c r="D237" s="2" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -26721,10 +26721,10 @@
       <c r="A238" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="C238" s="6" t="s">
+      <c r="C238" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="D238" s="6" t="s">
+      <c r="D238" s="2" t="s">
         <v>1364</v>
       </c>
     </row>
@@ -26732,10 +26732,10 @@
       <c r="A239" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="C239" s="6" t="s">
+      <c r="C239" s="2" t="s">
         <v>1365</v>
       </c>
-      <c r="D239" s="6" t="s">
+      <c r="D239" s="2" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -26743,10 +26743,10 @@
       <c r="A240" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="C240" s="6" t="s">
+      <c r="C240" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="D240" s="6" t="s">
+      <c r="D240" s="2" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -26754,10 +26754,10 @@
       <c r="A241" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="C241" s="6" t="s">
+      <c r="C241" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="D241" s="6" t="s">
+      <c r="D241" s="2" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -26765,2906 +26765,2906 @@
       <c r="A242" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="C242" s="6" t="s">
+      <c r="C242" s="2" t="s">
         <v>1371</v>
       </c>
-      <c r="D242" s="6" t="s">
+      <c r="D242" s="2" t="s">
         <v>1372</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C243" s="0" t="s">
+      <c r="C243" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="D243" s="0" t="s">
+      <c r="D243" s="1" t="s">
         <v>1374</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C244" s="0" t="s">
+      <c r="C244" s="1" t="s">
         <v>1375</v>
       </c>
-      <c r="D244" s="0" t="s">
+      <c r="D244" s="1" t="s">
         <v>1376</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C245" s="0" t="s">
+      <c r="C245" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="D245" s="0" t="s">
+      <c r="D245" s="1" t="s">
         <v>1378</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C246" s="0" t="s">
+      <c r="C246" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="D246" s="0" t="s">
+      <c r="D246" s="1" t="s">
         <v>1380</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C247" s="0" t="s">
+      <c r="C247" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="D247" s="0" t="s">
+      <c r="D247" s="1" t="s">
         <v>1382</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C248" s="0" t="s">
+      <c r="C248" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="D248" s="0" t="s">
+      <c r="D248" s="1" t="s">
         <v>1384</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C249" s="0" t="s">
+      <c r="C249" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="D249" s="0" t="s">
+      <c r="D249" s="1" t="s">
         <v>1386</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C250" s="0" t="s">
+      <c r="C250" s="1" t="s">
         <v>1387</v>
       </c>
-      <c r="D250" s="0" t="s">
+      <c r="D250" s="1" t="s">
         <v>1388</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C251" s="0" t="s">
+      <c r="C251" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="D251" s="0" t="s">
+      <c r="D251" s="1" t="s">
         <v>1390</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C252" s="0" t="s">
+      <c r="C252" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="D252" s="0" t="s">
+      <c r="D252" s="1" t="s">
         <v>1392</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C253" s="0" t="s">
+      <c r="C253" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="D253" s="0" t="s">
+      <c r="D253" s="1" t="s">
         <v>1394</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C254" s="0" t="s">
+      <c r="C254" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="D254" s="0" t="s">
+      <c r="D254" s="1" t="s">
         <v>1396</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C255" s="0" t="s">
+      <c r="C255" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="D255" s="0" t="s">
+      <c r="D255" s="1" t="s">
         <v>1398</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C256" s="0" t="s">
+      <c r="C256" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="D256" s="0" t="s">
+      <c r="D256" s="1" t="s">
         <v>1400</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C257" s="0" t="s">
+      <c r="C257" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="D257" s="0" t="s">
+      <c r="D257" s="1" t="s">
         <v>1402</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C258" s="0" t="s">
+      <c r="C258" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="D258" s="0" t="s">
+      <c r="D258" s="1" t="s">
         <v>1404</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C259" s="0" t="s">
+      <c r="C259" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D259" s="0" t="s">
+      <c r="D259" s="1" t="s">
         <v>1406</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C260" s="0" t="s">
+      <c r="C260" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="D260" s="0" t="s">
+      <c r="D260" s="1" t="s">
         <v>1408</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C261" s="0" t="s">
+      <c r="C261" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="D261" s="0" t="s">
+      <c r="D261" s="1" t="s">
         <v>1410</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C262" s="0" t="s">
+      <c r="C262" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="D262" s="0" t="s">
+      <c r="D262" s="1" t="s">
         <v>1412</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C263" s="0" t="s">
+      <c r="C263" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D263" s="0" t="s">
+      <c r="D263" s="1" t="s">
         <v>1414</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C264" s="0" t="s">
+      <c r="C264" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="D264" s="0" t="s">
+      <c r="D264" s="1" t="s">
         <v>1416</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C265" s="0" t="s">
+      <c r="C265" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="D265" s="0" t="s">
+      <c r="D265" s="1" t="s">
         <v>1418</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C266" s="0" t="s">
+      <c r="C266" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="D266" s="0" t="s">
+      <c r="D266" s="1" t="s">
         <v>1420</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C267" s="0" t="s">
+      <c r="C267" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="D267" s="0" t="s">
+      <c r="D267" s="1" t="s">
         <v>1422</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C268" s="0" t="s">
+      <c r="C268" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="D268" s="0" t="s">
+      <c r="D268" s="1" t="s">
         <v>1424</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C269" s="0" t="s">
+      <c r="C269" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="D269" s="0" t="s">
+      <c r="D269" s="1" t="s">
         <v>1426</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C270" s="0" t="s">
+      <c r="C270" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="D270" s="0" t="s">
+      <c r="D270" s="1" t="s">
         <v>1428</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C271" s="0" t="s">
+      <c r="C271" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D271" s="0" t="s">
+      <c r="D271" s="1" t="s">
         <v>1430</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C272" s="0" t="s">
+      <c r="C272" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="D272" s="0" t="s">
+      <c r="D272" s="1" t="s">
         <v>1432</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C273" s="0" t="s">
+      <c r="C273" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="D273" s="0" t="s">
+      <c r="D273" s="1" t="s">
         <v>1434</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C274" s="0" t="s">
+      <c r="C274" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="D274" s="0" t="s">
+      <c r="D274" s="1" t="s">
         <v>1436</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C275" s="0" t="s">
+      <c r="C275" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="D275" s="0" t="s">
+      <c r="D275" s="1" t="s">
         <v>1438</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C276" s="0" t="s">
+      <c r="C276" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="D276" s="0" t="s">
+      <c r="D276" s="1" t="s">
         <v>1440</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C277" s="0" t="s">
+      <c r="C277" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="D277" s="0" t="s">
+      <c r="D277" s="1" t="s">
         <v>1442</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C278" s="0" t="s">
+      <c r="C278" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="D278" s="0" t="s">
+      <c r="D278" s="1" t="s">
         <v>1439</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C279" s="0" t="s">
+      <c r="C279" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="D279" s="0" t="s">
+      <c r="D279" s="1" t="s">
         <v>1437</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C280" s="0" t="s">
+      <c r="C280" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="D280" s="0" t="s">
+      <c r="D280" s="1" t="s">
         <v>1433</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C281" s="0" t="s">
+      <c r="C281" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="D281" s="0" t="s">
+      <c r="D281" s="1" t="s">
         <v>1429</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C282" s="0" t="s">
+      <c r="C282" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="D282" s="0" t="s">
+      <c r="D282" s="1" t="s">
         <v>1427</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C283" s="0" t="s">
+      <c r="C283" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="D283" s="0" t="s">
+      <c r="D283" s="1" t="s">
         <v>1421</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C284" s="0" t="s">
+      <c r="C284" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="D284" s="0" t="s">
+      <c r="D284" s="1" t="s">
         <v>1419</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C285" s="0" t="s">
+      <c r="C285" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="D285" s="0" t="s">
+      <c r="D285" s="1" t="s">
         <v>1413</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C286" s="0" t="s">
+      <c r="C286" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D286" s="0" t="s">
+      <c r="D286" s="1" t="s">
         <v>1411</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C287" s="0" t="s">
+      <c r="C287" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="D287" s="0" t="s">
+      <c r="D287" s="1" t="s">
         <v>1409</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C288" s="0" t="s">
+      <c r="C288" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="D288" s="0" t="s">
+      <c r="D288" s="1" t="s">
         <v>1403</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C289" s="0" t="s">
+      <c r="C289" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="D289" s="0" t="s">
+      <c r="D289" s="1" t="s">
         <v>1393</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C290" s="0" t="s">
+      <c r="C290" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="D290" s="0" t="s">
+      <c r="D290" s="1" t="s">
         <v>1389</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C291" s="0" t="s">
+      <c r="C291" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="D291" s="0" t="s">
+      <c r="D291" s="1" t="s">
         <v>1387</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C292" s="0" t="s">
+      <c r="C292" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="D292" s="0" t="s">
+      <c r="D292" s="1" t="s">
         <v>1383</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C293" s="0" t="s">
+      <c r="C293" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="D293" s="0" t="s">
+      <c r="D293" s="1" t="s">
         <v>1379</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C294" s="0" t="s">
+      <c r="C294" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="D294" s="0" t="s">
+      <c r="D294" s="1" t="s">
         <v>1375</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C295" s="0" t="s">
+      <c r="C295" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="D295" s="0" t="s">
+      <c r="D295" s="1" t="s">
         <v>1371</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C296" s="0" t="s">
+      <c r="C296" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="D296" s="0" t="s">
+      <c r="D296" s="1" t="s">
         <v>1369</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C297" s="0" t="s">
+      <c r="C297" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="D297" s="0" t="s">
+      <c r="D297" s="1" t="s">
         <v>1367</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C298" s="0" t="s">
+      <c r="C298" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="D298" s="0" t="s">
+      <c r="D298" s="1" t="s">
         <v>1359</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C299" s="0" t="s">
+      <c r="C299" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="D299" s="0" t="s">
+      <c r="D299" s="1" t="s">
         <v>1357</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C300" s="0" t="s">
+      <c r="C300" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="D300" s="0" t="s">
+      <c r="D300" s="1" t="s">
         <v>1355</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C301" s="0" t="s">
+      <c r="C301" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="D301" s="0" t="s">
+      <c r="D301" s="1" t="s">
         <v>1347</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C302" s="0" t="s">
+      <c r="C302" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="D302" s="0" t="s">
+      <c r="D302" s="1" t="s">
         <v>1345</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C303" s="0" t="s">
+      <c r="C303" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="D303" s="0" t="s">
+      <c r="D303" s="1" t="s">
         <v>1343</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C304" s="0" t="s">
+      <c r="C304" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="D304" s="0" t="s">
+      <c r="D304" s="1" t="s">
         <v>1341</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C305" s="0" t="s">
+      <c r="C305" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="D305" s="0" t="s">
+      <c r="D305" s="1" t="s">
         <v>1337</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C306" s="0" t="s">
+      <c r="C306" s="1" t="s">
         <v>1414</v>
       </c>
-      <c r="D306" s="0" t="s">
+      <c r="D306" s="1" t="s">
         <v>1331</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C307" s="0" t="s">
+      <c r="C307" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="D307" s="0" t="s">
+      <c r="D307" s="1" t="s">
         <v>1329</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C308" s="0" t="s">
+      <c r="C308" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="D308" s="0" t="s">
+      <c r="D308" s="1" t="s">
         <v>1327</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C309" s="0" t="s">
+      <c r="C309" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="D309" s="0" t="s">
+      <c r="D309" s="1" t="s">
         <v>1325</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C310" s="0" t="s">
+      <c r="C310" s="1" t="s">
         <v>1406</v>
       </c>
-      <c r="D310" s="0" t="s">
+      <c r="D310" s="1" t="s">
         <v>1317</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C311" s="0" t="s">
+      <c r="C311" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="D311" s="0" t="s">
+      <c r="D311" s="1" t="s">
         <v>1311</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C312" s="0" t="s">
+      <c r="C312" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="D312" s="0" t="s">
+      <c r="D312" s="1" t="s">
         <v>1309</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C313" s="0" t="s">
+      <c r="C313" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="D313" s="0" t="s">
+      <c r="D313" s="1" t="s">
         <v>1305</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C314" s="0" t="s">
+      <c r="C314" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="D314" s="0" t="s">
+      <c r="D314" s="1" t="s">
         <v>1303</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C315" s="0" t="s">
+      <c r="C315" s="1" t="s">
         <v>1460</v>
       </c>
-      <c r="D315" s="0" t="s">
+      <c r="D315" s="1" t="s">
         <v>1301</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C316" s="0" t="s">
+      <c r="C316" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="D316" s="0" t="s">
+      <c r="D316" s="1" t="s">
         <v>1295</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C317" s="0" t="s">
+      <c r="C317" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="D317" s="0" t="s">
+      <c r="D317" s="1" t="s">
         <v>1293</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C318" s="0" t="s">
+      <c r="C318" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="D318" s="0" t="s">
+      <c r="D318" s="1" t="s">
         <v>1289</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C319" s="0" t="s">
+      <c r="C319" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="D319" s="0" t="s">
+      <c r="D319" s="1" t="s">
         <v>1284</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C320" s="0" t="s">
+      <c r="C320" s="1" t="s">
         <v>1463</v>
       </c>
-      <c r="D320" s="0" t="s">
+      <c r="D320" s="1" t="s">
         <v>1273</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C321" s="0" t="s">
+      <c r="C321" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="D321" s="0" t="s">
+      <c r="D321" s="1" t="s">
         <v>1271</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C322" s="0" t="s">
+      <c r="C322" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="D322" s="0" t="s">
+      <c r="D322" s="1" t="s">
         <v>1265</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C323" s="0" t="s">
+      <c r="C323" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="D323" s="0" t="s">
+      <c r="D323" s="1" t="s">
         <v>1263</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C324" s="0" t="s">
+      <c r="C324" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="D324" s="0" t="s">
+      <c r="D324" s="1" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C325" s="0" t="s">
+      <c r="C325" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="D325" s="0" t="s">
+      <c r="D325" s="1" t="s">
         <v>1248</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C326" s="0" t="s">
+      <c r="C326" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="D326" s="0" t="s">
+      <c r="D326" s="1" t="s">
         <v>1246</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C327" s="0" t="s">
+      <c r="C327" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="D327" s="0" t="s">
+      <c r="D327" s="1" t="s">
         <v>1241</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C328" s="0" t="s">
+      <c r="C328" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="D328" s="0" t="s">
+      <c r="D328" s="1" t="s">
         <v>1238</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C329" s="0" t="s">
+      <c r="C329" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="D329" s="0" t="s">
+      <c r="D329" s="1" t="s">
         <v>1232</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C330" s="0" t="s">
+      <c r="C330" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="D330" s="0" t="s">
+      <c r="D330" s="1" t="s">
         <v>1229</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C331" s="0" t="s">
+      <c r="C331" s="1" t="s">
         <v>1469</v>
       </c>
-      <c r="D331" s="0" t="s">
+      <c r="D331" s="1" t="s">
         <v>1226</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C332" s="0" t="s">
+      <c r="C332" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="D332" s="0" t="s">
+      <c r="D332" s="1" t="s">
         <v>1217</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C333" s="0" t="s">
+      <c r="C333" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="D333" s="0" t="s">
+      <c r="D333" s="1" t="s">
         <v>1214</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C334" s="0" t="s">
+      <c r="C334" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="D334" s="0" t="s">
+      <c r="D334" s="1" t="s">
         <v>1211</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C335" s="0" t="s">
+      <c r="C335" s="1" t="s">
         <v>1471</v>
       </c>
-      <c r="D335" s="0" t="s">
+      <c r="D335" s="1" t="s">
         <v>1208</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C336" s="0" t="s">
+      <c r="C336" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="D336" s="0" t="s">
+      <c r="D336" s="1" t="s">
         <v>1199</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C337" s="0" t="s">
+      <c r="C337" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="D337" s="0" t="s">
+      <c r="D337" s="1" t="s">
         <v>1196</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C338" s="0" t="s">
+      <c r="C338" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="D338" s="0" t="s">
+      <c r="D338" s="1" t="s">
         <v>1193</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C339" s="0" t="s">
+      <c r="C339" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="D339" s="0" t="s">
+      <c r="D339" s="1" t="s">
         <v>1185</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C340" s="0" t="s">
+      <c r="C340" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="D340" s="0" t="s">
+      <c r="D340" s="1" t="s">
         <v>1180</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C341" s="0" t="s">
+      <c r="C341" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="D341" s="0" t="s">
+      <c r="D341" s="1" t="s">
         <v>1177</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C342" s="0" t="s">
+      <c r="C342" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="D342" s="0" t="s">
+      <c r="D342" s="1" t="s">
         <v>1174</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C343" s="0" t="s">
+      <c r="C343" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="D343" s="0" t="s">
+      <c r="D343" s="1" t="s">
         <v>1171</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C344" s="0" t="s">
+      <c r="C344" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="D344" s="0" t="s">
+      <c r="D344" s="1" t="s">
         <v>1166</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C345" s="0" t="s">
+      <c r="C345" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="D345" s="0" t="s">
+      <c r="D345" s="1" t="s">
         <v>1163</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C346" s="0" t="s">
+      <c r="C346" s="1" t="s">
         <v>1477</v>
       </c>
-      <c r="D346" s="0" t="s">
+      <c r="D346" s="1" t="s">
         <v>1160</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C347" s="0" t="s">
+      <c r="C347" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="D347" s="0" t="s">
+      <c r="D347" s="1" t="s">
         <v>1157</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C348" s="0" t="s">
+      <c r="C348" s="1" t="s">
         <v>1372</v>
       </c>
-      <c r="D348" s="0" t="s">
+      <c r="D348" s="1" t="s">
         <v>1154</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C349" s="0" t="s">
+      <c r="C349" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="D349" s="0" t="s">
+      <c r="D349" s="1" t="s">
         <v>1144</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C350" s="0" t="s">
+      <c r="C350" s="1" t="s">
         <v>1368</v>
       </c>
-      <c r="D350" s="0" t="s">
+      <c r="D350" s="1" t="s">
         <v>1142</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C351" s="0" t="s">
+      <c r="C351" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="D351" s="0" t="s">
+      <c r="D351" s="1" t="s">
         <v>1136</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C352" s="0" t="s">
+      <c r="C352" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="D352" s="0" t="s">
+      <c r="D352" s="1" t="s">
         <v>1130</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C353" s="0" t="s">
+      <c r="C353" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="D353" s="0" t="s">
+      <c r="D353" s="1" t="s">
         <v>1127</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C354" s="0" t="s">
+      <c r="C354" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="D354" s="0" t="s">
+      <c r="D354" s="1" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C355" s="0" t="s">
+      <c r="C355" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="D355" s="0" t="s">
+      <c r="D355" s="1" t="s">
         <v>1123</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C356" s="0" t="s">
+      <c r="C356" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="D356" s="0" t="s">
+      <c r="D356" s="1" t="s">
         <v>1113</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C357" s="0" t="s">
+      <c r="C357" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="D357" s="0" t="s">
+      <c r="D357" s="1" t="s">
         <v>1111</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C358" s="0" t="s">
+      <c r="C358" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="D358" s="0" t="s">
+      <c r="D358" s="1" t="s">
         <v>1104</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C359" s="0" t="s">
+      <c r="C359" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="D359" s="0" t="s">
+      <c r="D359" s="1" t="s">
         <v>1095</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C360" s="0" t="s">
+      <c r="C360" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="D360" s="0" t="s">
+      <c r="D360" s="1" t="s">
         <v>1085</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C361" s="0" t="s">
+      <c r="C361" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="D361" s="0" t="s">
+      <c r="D361" s="1" t="s">
         <v>1079</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C362" s="0" t="s">
+      <c r="C362" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="D362" s="0" t="s">
+      <c r="D362" s="1" t="s">
         <v>1077</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C363" s="0" t="s">
+      <c r="C363" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="D363" s="0" t="s">
+      <c r="D363" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C364" s="0" t="s">
+      <c r="C364" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="D364" s="0" t="s">
+      <c r="D364" s="1" t="s">
         <v>1072</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C365" s="0" t="s">
+      <c r="C365" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="D365" s="0" t="s">
+      <c r="D365" s="1" t="s">
         <v>1070</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C366" s="0" t="s">
+      <c r="C366" s="1" t="s">
         <v>1481</v>
       </c>
-      <c r="D366" s="0" t="s">
+      <c r="D366" s="1" t="s">
         <v>1068</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C367" s="0" t="s">
+      <c r="C367" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="D367" s="0" t="s">
+      <c r="D367" s="1" t="s">
         <v>1059</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C368" s="0" t="s">
+      <c r="C368" s="1" t="s">
         <v>1483</v>
       </c>
-      <c r="D368" s="0" t="s">
+      <c r="D368" s="1" t="s">
         <v>1048</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C369" s="0" t="s">
+      <c r="C369" s="1" t="s">
         <v>1484</v>
       </c>
-      <c r="D369" s="0" t="s">
+      <c r="D369" s="1" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C370" s="0" t="s">
+      <c r="C370" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="D370" s="0" t="s">
+      <c r="D370" s="1" t="s">
         <v>1040</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C371" s="0" t="s">
+      <c r="C371" s="1" t="s">
         <v>1486</v>
       </c>
-      <c r="D371" s="0" t="s">
+      <c r="D371" s="1" t="s">
         <v>1034</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C372" s="0" t="s">
+      <c r="C372" s="1" t="s">
         <v>1487</v>
       </c>
-      <c r="D372" s="0" t="s">
+      <c r="D372" s="1" t="s">
         <v>1025</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C373" s="0" t="s">
+      <c r="C373" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="D373" s="0" t="s">
+      <c r="D373" s="1" t="s">
         <v>1022</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C374" s="0" t="s">
+      <c r="C374" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="D374" s="0" t="s">
+      <c r="D374" s="1" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C375" s="0" t="s">
+      <c r="C375" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="D375" s="0" t="s">
+      <c r="D375" s="1" t="s">
         <v>1015</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C376" s="0" t="s">
+      <c r="C376" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="D376" s="0" t="s">
+      <c r="D376" s="1" t="s">
         <v>1005</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C377" s="0" t="s">
+      <c r="C377" s="1" t="s">
         <v>1489</v>
       </c>
-      <c r="D377" s="0" t="s">
+      <c r="D377" s="1" t="s">
         <v>1002</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C378" s="0" t="s">
+      <c r="C378" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="D378" s="0" t="s">
+      <c r="D378" s="1" t="s">
         <v>996</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C379" s="0" t="s">
+      <c r="C379" s="1" t="s">
         <v>1490</v>
       </c>
-      <c r="D379" s="0" t="s">
+      <c r="D379" s="1" t="s">
         <v>991</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C380" s="0" t="s">
+      <c r="C380" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="D380" s="0" t="s">
+      <c r="D380" s="1" t="s">
         <v>989</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C381" s="0" t="s">
+      <c r="C381" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="D381" s="0" t="s">
+      <c r="D381" s="1" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C382" s="0" t="s">
+      <c r="C382" s="1" t="s">
         <v>1492</v>
       </c>
-      <c r="D382" s="0" t="s">
+      <c r="D382" s="1" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C383" s="0" t="s">
+      <c r="C383" s="1" t="s">
         <v>1493</v>
       </c>
-      <c r="D383" s="0" t="s">
+      <c r="D383" s="1" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C384" s="0" t="s">
+      <c r="C384" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="D384" s="0" t="s">
+      <c r="D384" s="1" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C385" s="0" t="s">
+      <c r="C385" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="D385" s="0" t="s">
+      <c r="D385" s="1" t="s">
         <v>968</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C386" s="0" t="s">
+      <c r="C386" s="1" t="s">
         <v>1495</v>
       </c>
-      <c r="D386" s="0" t="s">
+      <c r="D386" s="1" t="s">
         <v>966</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C387" s="0" t="s">
+      <c r="C387" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="D387" s="0" t="s">
+      <c r="D387" s="1" t="s">
         <v>963</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C388" s="0" t="s">
+      <c r="C388" s="1" t="s">
         <v>1328</v>
       </c>
-      <c r="D388" s="0" t="s">
+      <c r="D388" s="1" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C389" s="0" t="s">
+      <c r="C389" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="D389" s="0" t="s">
+      <c r="D389" s="1" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C390" s="0" t="s">
+      <c r="C390" s="1" t="s">
         <v>1496</v>
       </c>
-      <c r="D390" s="0" t="s">
+      <c r="D390" s="1" t="s">
         <v>955</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C391" s="0" t="s">
+      <c r="C391" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="D391" s="0" t="s">
+      <c r="D391" s="1" t="s">
         <v>947</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C392" s="0" t="s">
+      <c r="C392" s="1" t="s">
         <v>1498</v>
       </c>
-      <c r="D392" s="0" t="s">
+      <c r="D392" s="1" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C393" s="0" t="s">
+      <c r="C393" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="D393" s="0" t="s">
+      <c r="D393" s="1" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C394" s="0" t="s">
+      <c r="C394" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="D394" s="0" t="s">
+      <c r="D394" s="1" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C395" s="0" t="s">
+      <c r="C395" s="1" t="s">
         <v>1499</v>
       </c>
-      <c r="D395" s="0" t="s">
+      <c r="D395" s="1" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C396" s="0" t="s">
+      <c r="C396" s="1" t="s">
         <v>1500</v>
       </c>
-      <c r="D396" s="0" t="s">
+      <c r="D396" s="1" t="s">
         <v>908</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C397" s="0" t="s">
+      <c r="C397" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="D397" s="0" t="s">
+      <c r="D397" s="1" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C398" s="0" t="s">
+      <c r="C398" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="D398" s="0" t="s">
+      <c r="D398" s="1" t="s">
         <v>892</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C399" s="0" t="s">
+      <c r="C399" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="D399" s="0" t="s">
+      <c r="D399" s="1" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C400" s="0" t="s">
+      <c r="C400" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="D400" s="0" t="s">
+      <c r="D400" s="1" t="s">
         <v>852</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C401" s="0" t="s">
+      <c r="C401" s="1" t="s">
         <v>1502</v>
       </c>
-      <c r="D401" s="0" t="s">
+      <c r="D401" s="1" t="s">
         <v>849</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C402" s="0" t="s">
+      <c r="C402" s="1" t="s">
         <v>1503</v>
       </c>
-      <c r="D402" s="0" t="s">
+      <c r="D402" s="1" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C403" s="0" t="s">
+      <c r="C403" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="D403" s="0" t="s">
+      <c r="D403" s="1" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C404" s="0" t="s">
+      <c r="C404" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="D404" s="0" t="s">
+      <c r="D404" s="1" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C405" s="0" t="s">
+      <c r="C405" s="1" t="s">
         <v>1505</v>
       </c>
-      <c r="D405" s="0" t="s">
+      <c r="D405" s="1" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C406" s="0" t="s">
+      <c r="C406" s="1" t="s">
         <v>1506</v>
       </c>
-      <c r="D406" s="0" t="s">
+      <c r="D406" s="1" t="s">
         <v>805</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C407" s="0" t="s">
+      <c r="C407" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="D407" s="0" t="s">
+      <c r="D407" s="1" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C408" s="0" t="s">
+      <c r="C408" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="D408" s="0" t="s">
+      <c r="D408" s="1" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C409" s="0" t="s">
+      <c r="C409" s="1" t="s">
         <v>1508</v>
       </c>
-      <c r="D409" s="0" t="s">
+      <c r="D409" s="1" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C410" s="0" t="s">
+      <c r="C410" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="D410" s="0" t="s">
+      <c r="D410" s="1" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C411" s="0" t="s">
+      <c r="C411" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="D411" s="0" t="s">
+      <c r="D411" s="1" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C412" s="0" t="s">
+      <c r="C412" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="D412" s="0" t="s">
+      <c r="D412" s="1" t="s">
         <v>754</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C413" s="0" t="s">
+      <c r="C413" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="D413" s="0" t="s">
+      <c r="D413" s="1" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C414" s="0" t="s">
+      <c r="C414" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="D414" s="0" t="s">
+      <c r="D414" s="1" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C415" s="0" t="s">
+      <c r="C415" s="1" t="s">
         <v>1510</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C416" s="0" t="s">
+      <c r="C416" s="1" t="s">
         <v>1302</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C417" s="0" t="s">
+      <c r="C417" s="1" t="s">
         <v>1300</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C418" s="0" t="s">
+      <c r="C418" s="1" t="s">
         <v>1298</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C419" s="0" t="s">
+      <c r="C419" s="1" t="s">
         <v>1296</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C420" s="0" t="s">
+      <c r="C420" s="1" t="s">
         <v>1511</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C421" s="0" t="s">
+      <c r="C421" s="1" t="s">
         <v>1294</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C422" s="0" t="s">
+      <c r="C422" s="1" t="s">
         <v>1292</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C423" s="0" t="s">
+      <c r="C423" s="1" t="s">
         <v>1512</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C424" s="0" t="s">
+      <c r="C424" s="1" t="s">
         <v>1290</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C425" s="0" t="s">
+      <c r="C425" s="1" t="s">
         <v>1288</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C426" s="0" t="s">
+      <c r="C426" s="1" t="s">
         <v>1513</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C427" s="0" t="s">
+      <c r="C427" s="1" t="s">
         <v>1285</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C428" s="0" t="s">
+      <c r="C428" s="1" t="s">
         <v>1283</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C429" s="0" t="s">
+      <c r="C429" s="1" t="s">
         <v>1514</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C430" s="0" t="s">
+      <c r="C430" s="1" t="s">
         <v>1281</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C431" s="0" t="s">
+      <c r="C431" s="1" t="s">
         <v>1515</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C432" s="0" t="s">
+      <c r="C432" s="1" t="s">
         <v>1279</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C433" s="0" t="s">
+      <c r="C433" s="1" t="s">
         <v>1516</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C434" s="0" t="s">
+      <c r="C434" s="1" t="s">
         <v>1517</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C435" s="0" t="s">
+      <c r="C435" s="1" t="s">
         <v>1518</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C436" s="0" t="s">
+      <c r="C436" s="1" t="s">
         <v>1519</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C437" s="0" t="s">
+      <c r="C437" s="1" t="s">
         <v>1520</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C438" s="0" t="s">
+      <c r="C438" s="1" t="s">
         <v>1276</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C439" s="0" t="s">
+      <c r="C439" s="1" t="s">
         <v>1274</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C440" s="0" t="s">
+      <c r="C440" s="1" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C441" s="0" t="s">
+      <c r="C441" s="1" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C442" s="0" t="s">
+      <c r="C442" s="1" t="s">
         <v>1521</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C443" s="0" t="s">
+      <c r="C443" s="1" t="s">
         <v>1522</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C444" s="0" t="s">
+      <c r="C444" s="1" t="s">
         <v>1523</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C445" s="0" t="s">
+      <c r="C445" s="1" t="s">
         <v>1268</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C446" s="0" t="s">
+      <c r="C446" s="1" t="s">
         <v>1266</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C447" s="0" t="s">
+      <c r="C447" s="1" t="s">
         <v>1264</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C448" s="0" t="s">
+      <c r="C448" s="1" t="s">
         <v>1524</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C449" s="0" t="s">
+      <c r="C449" s="1" t="s">
         <v>1525</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C450" s="0" t="s">
+      <c r="C450" s="1" t="s">
         <v>1526</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C451" s="0" t="s">
+      <c r="C451" s="1" t="s">
         <v>1261</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C452" s="0" t="s">
+      <c r="C452" s="1" t="s">
         <v>1258</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C453" s="0" t="s">
+      <c r="C453" s="1" t="s">
         <v>1527</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C454" s="0" t="s">
+      <c r="C454" s="1" t="s">
         <v>1528</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C455" s="0" t="s">
+      <c r="C455" s="1" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C456" s="0" t="s">
+      <c r="C456" s="1" t="s">
         <v>1252</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C457" s="0" t="s">
+      <c r="C457" s="1" t="s">
         <v>1529</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C458" s="0" t="s">
+      <c r="C458" s="1" t="s">
         <v>1249</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C459" s="0" t="s">
+      <c r="C459" s="1" t="s">
         <v>1530</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C460" s="0" t="s">
+      <c r="C460" s="1" t="s">
         <v>1247</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C461" s="0" t="s">
+      <c r="C461" s="1" t="s">
         <v>1245</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C462" s="0" t="s">
+      <c r="C462" s="1" t="s">
         <v>1242</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C463" s="0" t="s">
+      <c r="C463" s="1" t="s">
         <v>1531</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C464" s="0" t="s">
+      <c r="C464" s="1" t="s">
         <v>1532</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C465" s="0" t="s">
+      <c r="C465" s="1" t="s">
         <v>1239</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C466" s="0" t="s">
+      <c r="C466" s="1" t="s">
         <v>1533</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C467" s="0" t="s">
+      <c r="C467" s="1" t="s">
         <v>1534</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C468" s="0" t="s">
+      <c r="C468" s="1" t="s">
         <v>1535</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C469" s="0" t="s">
+      <c r="C469" s="1" t="s">
         <v>1536</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C470" s="0" t="s">
+      <c r="C470" s="1" t="s">
         <v>1236</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C471" s="0" t="s">
+      <c r="C471" s="1" t="s">
         <v>1537</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C472" s="0" t="s">
+      <c r="C472" s="1" t="s">
         <v>1233</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C473" s="0" t="s">
+      <c r="C473" s="1" t="s">
         <v>1538</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C474" s="0" t="s">
+      <c r="C474" s="1" t="s">
         <v>1230</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C475" s="0" t="s">
+      <c r="C475" s="1" t="s">
         <v>1539</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C476" s="0" t="s">
+      <c r="C476" s="1" t="s">
         <v>1540</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C477" s="0" t="s">
+      <c r="C477" s="1" t="s">
         <v>1541</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C478" s="0" t="s">
+      <c r="C478" s="1" t="s">
         <v>1227</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C479" s="0" t="s">
+      <c r="C479" s="1" t="s">
         <v>1542</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C480" s="0" t="s">
+      <c r="C480" s="1" t="s">
         <v>1224</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C481" s="0" t="s">
+      <c r="C481" s="1" t="s">
         <v>1543</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C482" s="0" t="s">
+      <c r="C482" s="1" t="s">
         <v>1221</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C483" s="0" t="s">
+      <c r="C483" s="1" t="s">
         <v>1218</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C484" s="0" t="s">
+      <c r="C484" s="1" t="s">
         <v>1544</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C485" s="0" t="s">
+      <c r="C485" s="1" t="s">
         <v>1215</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C486" s="0" t="s">
+      <c r="C486" s="1" t="s">
         <v>1212</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C487" s="0" t="s">
+      <c r="C487" s="1" t="s">
         <v>1545</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C488" s="0" t="s">
+      <c r="C488" s="1" t="s">
         <v>1209</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C489" s="0" t="s">
+      <c r="C489" s="1" t="s">
         <v>1206</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C490" s="0" t="s">
+      <c r="C490" s="1" t="s">
         <v>1203</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C491" s="0" t="s">
+      <c r="C491" s="1" t="s">
         <v>1546</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C492" s="0" t="s">
+      <c r="C492" s="1" t="s">
         <v>1547</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C493" s="0" t="s">
+      <c r="C493" s="1" t="s">
         <v>1200</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C494" s="0" t="s">
+      <c r="C494" s="1" t="s">
         <v>1197</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C495" s="0" t="s">
+      <c r="C495" s="1" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C496" s="0" t="s">
+      <c r="C496" s="1" t="s">
         <v>1192</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C497" s="0" t="s">
+      <c r="C497" s="1" t="s">
         <v>1189</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C498" s="0" t="s">
+      <c r="C498" s="1" t="s">
         <v>1548</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C499" s="0" t="s">
+      <c r="C499" s="1" t="s">
         <v>1186</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C500" s="0" t="s">
+      <c r="C500" s="1" t="s">
         <v>1183</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C501" s="0" t="s">
+      <c r="C501" s="1" t="s">
         <v>1181</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C502" s="0" t="s">
+      <c r="C502" s="1" t="s">
         <v>1178</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C503" s="0" t="s">
+      <c r="C503" s="1" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C504" s="0" t="s">
+      <c r="C504" s="1" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C505" s="0" t="s">
+      <c r="C505" s="1" t="s">
         <v>1550</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C506" s="0" t="s">
+      <c r="C506" s="1" t="s">
         <v>1172</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C507" s="0" t="s">
+      <c r="C507" s="1" t="s">
         <v>1170</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C508" s="0" t="s">
+      <c r="C508" s="1" t="s">
         <v>1167</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C509" s="0" t="s">
+      <c r="C509" s="1" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C510" s="0" t="s">
+      <c r="C510" s="1" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C511" s="0" t="s">
+      <c r="C511" s="1" t="s">
         <v>1158</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C512" s="0" t="s">
+      <c r="C512" s="1" t="s">
         <v>1551</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C513" s="0" t="s">
+      <c r="C513" s="1" t="s">
         <v>1552</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C514" s="0" t="s">
+      <c r="C514" s="1" t="s">
         <v>1155</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C515" s="0" t="s">
+      <c r="C515" s="1" t="s">
         <v>1152</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C516" s="0" t="s">
+      <c r="C516" s="1" t="s">
         <v>1149</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C517" s="0" t="s">
+      <c r="C517" s="1" t="s">
         <v>1147</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C518" s="0" t="s">
+      <c r="C518" s="1" t="s">
         <v>1145</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C519" s="0" t="s">
+      <c r="C519" s="1" t="s">
         <v>1143</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C520" s="0" t="s">
+      <c r="C520" s="1" t="s">
         <v>1141</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C521" s="0" t="s">
+      <c r="C521" s="1" t="s">
         <v>1139</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C522" s="0" t="s">
+      <c r="C522" s="1" t="s">
         <v>1137</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C523" s="0" t="s">
+      <c r="C523" s="1" t="s">
         <v>1135</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C524" s="0" t="s">
+      <c r="C524" s="1" t="s">
         <v>1553</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C525" s="0" t="s">
+      <c r="C525" s="1" t="s">
         <v>1554</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C526" s="0" t="s">
+      <c r="C526" s="1" t="s">
         <v>1133</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C527" s="0" t="s">
+      <c r="C527" s="1" t="s">
         <v>1555</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C528" s="0" t="s">
+      <c r="C528" s="1" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C529" s="0" t="s">
+      <c r="C529" s="1" t="s">
         <v>1556</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C530" s="0" t="s">
+      <c r="C530" s="1" t="s">
         <v>1557</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C531" s="0" t="s">
+      <c r="C531" s="1" t="s">
         <v>1128</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C532" s="0" t="s">
+      <c r="C532" s="1" t="s">
         <v>1126</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C533" s="0" t="s">
+      <c r="C533" s="1" t="s">
         <v>1558</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C534" s="0" t="s">
+      <c r="C534" s="1" t="s">
         <v>1124</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C535" s="0" t="s">
+      <c r="C535" s="1" t="s">
         <v>1122</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C536" s="0" t="s">
+      <c r="C536" s="1" t="s">
         <v>1119</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C537" s="0" t="s">
+      <c r="C537" s="1" t="s">
         <v>1559</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C538" s="0" t="s">
+      <c r="C538" s="1" t="s">
         <v>1117</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C539" s="0" t="s">
+      <c r="C539" s="1" t="s">
         <v>1114</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C540" s="0" t="s">
+      <c r="C540" s="1" t="s">
         <v>1112</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C541" s="0" t="s">
+      <c r="C541" s="1" t="s">
         <v>1560</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C542" s="0" t="s">
+      <c r="C542" s="1" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C543" s="0" t="s">
+      <c r="C543" s="1" t="s">
         <v>1107</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C544" s="0" t="s">
+      <c r="C544" s="1" t="s">
         <v>1561</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C545" s="0" t="s">
+      <c r="C545" s="1" t="s">
         <v>1562</v>
       </c>
     </row>
     <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C546" s="0" t="s">
+      <c r="C546" s="1" t="s">
         <v>1105</v>
       </c>
     </row>
     <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C547" s="0" t="s">
+      <c r="C547" s="1" t="s">
         <v>1102</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C548" s="0" t="s">
+      <c r="C548" s="1" t="s">
         <v>1099</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C549" s="0" t="s">
+      <c r="C549" s="1" t="s">
         <v>1096</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C550" s="0" t="s">
+      <c r="C550" s="1" t="s">
         <v>1094</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C551" s="0" t="s">
+      <c r="C551" s="1" t="s">
         <v>1092</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C552" s="0" t="s">
+      <c r="C552" s="1" t="s">
         <v>1089</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C553" s="0" t="s">
+      <c r="C553" s="1" t="s">
         <v>1563</v>
       </c>
     </row>
     <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C554" s="0" t="s">
+      <c r="C554" s="1" t="s">
         <v>1086</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C555" s="0" t="s">
+      <c r="C555" s="1" t="s">
         <v>1083</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C556" s="0" t="s">
+      <c r="C556" s="1" t="s">
         <v>1564</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C557" s="0" t="s">
+      <c r="C557" s="1" t="s">
         <v>1080</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C558" s="0" t="s">
+      <c r="C558" s="1" t="s">
         <v>1078</v>
       </c>
     </row>
     <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C559" s="0" t="s">
+      <c r="C559" s="1" t="s">
         <v>1076</v>
       </c>
     </row>
     <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C560" s="0" t="s">
+      <c r="C560" s="1" t="s">
         <v>1073</v>
       </c>
     </row>
     <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C561" s="0" t="s">
+      <c r="C561" s="1" t="s">
         <v>1071</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C562" s="0" t="s">
+      <c r="C562" s="1" t="s">
         <v>1069</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C563" s="0" t="s">
+      <c r="C563" s="1" t="s">
         <v>1565</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C564" s="0" t="s">
+      <c r="C564" s="1" t="s">
         <v>1066</v>
       </c>
     </row>
     <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C565" s="0" t="s">
+      <c r="C565" s="1" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C566" s="0" t="s">
+      <c r="C566" s="1" t="s">
         <v>1060</v>
       </c>
     </row>
     <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C567" s="0" t="s">
+      <c r="C567" s="1" t="s">
         <v>1566</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C568" s="0" t="s">
+      <c r="C568" s="1" t="s">
         <v>1058</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C569" s="0" t="s">
+      <c r="C569" s="1" t="s">
         <v>1567</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C570" s="0" t="s">
+      <c r="C570" s="1" t="s">
         <v>1568</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C571" s="0" t="s">
+      <c r="C571" s="1" t="s">
         <v>1055</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C572" s="0" t="s">
+      <c r="C572" s="1" t="s">
         <v>1052</v>
       </c>
     </row>
     <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C573" s="0" t="s">
+      <c r="C573" s="1" t="s">
         <v>1049</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C574" s="0" t="s">
+      <c r="C574" s="1" t="s">
         <v>1569</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C575" s="0" t="s">
+      <c r="C575" s="1" t="s">
         <v>1570</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C576" s="0" t="s">
+      <c r="C576" s="1" t="s">
         <v>1047</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C577" s="0" t="s">
+      <c r="C577" s="1" t="s">
         <v>1571</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C578" s="0" t="s">
+      <c r="C578" s="1" t="s">
         <v>1044</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C579" s="0" t="s">
+      <c r="C579" s="1" t="s">
         <v>1041</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C580" s="0" t="s">
+      <c r="C580" s="1" t="s">
         <v>1038</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C581" s="0" t="s">
+      <c r="C581" s="1" t="s">
         <v>1572</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C582" s="0" t="s">
+      <c r="C582" s="1" t="s">
         <v>1035</v>
       </c>
     </row>
     <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C583" s="0" t="s">
+      <c r="C583" s="1" t="s">
         <v>1573</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C584" s="0" t="s">
+      <c r="C584" s="1" t="s">
         <v>1032</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C585" s="0" t="s">
+      <c r="C585" s="1" t="s">
         <v>1029</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C586" s="0" t="s">
+      <c r="C586" s="1" t="s">
         <v>1574</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C587" s="0" t="s">
+      <c r="C587" s="1" t="s">
         <v>1026</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C588" s="0" t="s">
+      <c r="C588" s="1" t="s">
         <v>1023</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C589" s="0" t="s">
+      <c r="C589" s="1" t="s">
         <v>1020</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C590" s="0" t="s">
+      <c r="C590" s="1" t="s">
         <v>1018</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C591" s="0" t="s">
+      <c r="C591" s="1" t="s">
         <v>1575</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C592" s="0" t="s">
+      <c r="C592" s="1" t="s">
         <v>1016</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C593" s="0" t="s">
+      <c r="C593" s="1" t="s">
         <v>1014</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C594" s="0" t="s">
+      <c r="C594" s="1" t="s">
         <v>1576</v>
       </c>
     </row>
     <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C595" s="0" t="s">
+      <c r="C595" s="1" t="s">
         <v>1011</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C596" s="0" t="s">
+      <c r="C596" s="1" t="s">
         <v>1577</v>
       </c>
     </row>
     <row r="597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C597" s="0" t="s">
+      <c r="C597" s="1" t="s">
         <v>1009</v>
       </c>
     </row>
     <row r="598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C598" s="0" t="s">
+      <c r="C598" s="1" t="s">
         <v>1578</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C599" s="0" t="s">
+      <c r="C599" s="1" t="s">
         <v>1579</v>
       </c>
     </row>
     <row r="600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C600" s="0" t="s">
+      <c r="C600" s="1" t="s">
         <v>1006</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C601" s="0" t="s">
+      <c r="C601" s="1" t="s">
         <v>1580</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C602" s="0" t="s">
+      <c r="C602" s="1" t="s">
         <v>1003</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C603" s="0" t="s">
+      <c r="C603" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C604" s="0" t="s">
+      <c r="C604" s="1" t="s">
         <v>997</v>
       </c>
     </row>
     <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C605" s="0" t="s">
+      <c r="C605" s="1" t="s">
         <v>994</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C606" s="0" t="s">
+      <c r="C606" s="1" t="s">
         <v>992</v>
       </c>
     </row>
     <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C607" s="0" t="s">
+      <c r="C607" s="1" t="s">
         <v>1581</v>
       </c>
     </row>
     <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C608" s="0" t="s">
+      <c r="C608" s="1" t="s">
         <v>1582</v>
       </c>
     </row>
     <row r="609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C609" s="0" t="s">
+      <c r="C609" s="1" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C610" s="0" t="s">
+      <c r="C610" s="1" t="s">
         <v>987</v>
       </c>
     </row>
     <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C611" s="0" t="s">
+      <c r="C611" s="1" t="s">
         <v>984</v>
       </c>
     </row>
     <row r="612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C612" s="0" t="s">
+      <c r="C612" s="1" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C613" s="0" t="s">
+      <c r="C613" s="1" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C614" s="0" t="s">
+      <c r="C614" s="1" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C615" s="0" t="s">
+      <c r="C615" s="1" t="s">
         <v>1583</v>
       </c>
     </row>
     <row r="616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C616" s="0" t="s">
+      <c r="C616" s="1" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C617" s="0" t="s">
+      <c r="C617" s="1" t="s">
         <v>969</v>
       </c>
     </row>
     <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C618" s="0" t="s">
+      <c r="C618" s="1" t="s">
         <v>967</v>
       </c>
     </row>
     <row r="619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C619" s="0" t="s">
+      <c r="C619" s="1" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C620" s="0" t="s">
+      <c r="C620" s="1" t="s">
         <v>1584</v>
       </c>
     </row>
     <row r="621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C621" s="0" t="s">
+      <c r="C621" s="1" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C622" s="0" t="s">
+      <c r="C622" s="1" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C623" s="0" t="s">
+      <c r="C623" s="1" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C624" s="0" t="s">
+      <c r="C624" s="1" t="s">
         <v>953</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C625" s="0" t="s">
+      <c r="C625" s="1" t="s">
         <v>948</v>
       </c>
     </row>
     <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C626" s="0" t="s">
+      <c r="C626" s="1" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C627" s="0" t="s">
+      <c r="C627" s="1" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C628" s="0" t="s">
+      <c r="C628" s="1" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C629" s="0" t="s">
+      <c r="C629" s="1" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C630" s="0" t="s">
+      <c r="C630" s="1" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C631" s="0" t="s">
+      <c r="C631" s="1" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C632" s="0" t="s">
+      <c r="C632" s="1" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C633" s="0" t="s">
+      <c r="C633" s="1" t="s">
         <v>918</v>
       </c>
     </row>
     <row r="634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C634" s="0" t="s">
+      <c r="C634" s="1" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C635" s="0" t="s">
+      <c r="C635" s="1" t="s">
         <v>909</v>
       </c>
     </row>
     <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C636" s="0" t="s">
+      <c r="C636" s="1" t="s">
         <v>1585</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C637" s="0" t="s">
+      <c r="C637" s="1" t="s">
         <v>1586</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C638" s="0" t="s">
+      <c r="C638" s="1" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C639" s="0" t="s">
+      <c r="C639" s="1" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C640" s="0" t="s">
+      <c r="C640" s="1" t="s">
         <v>1587</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C641" s="0" t="s">
+      <c r="C641" s="1" t="s">
         <v>1588</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C642" s="0" t="s">
+      <c r="C642" s="1" t="s">
         <v>897</v>
       </c>
     </row>
     <row r="643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C643" s="0" t="s">
+      <c r="C643" s="1" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C644" s="0" t="s">
+      <c r="C644" s="1" t="s">
         <v>1589</v>
       </c>
     </row>
     <row r="645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C645" s="0" t="s">
+      <c r="C645" s="1" t="s">
         <v>1590</v>
       </c>
     </row>
     <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C646" s="0" t="s">
+      <c r="C646" s="1" t="s">
         <v>891</v>
       </c>
     </row>
     <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C647" s="0" t="s">
+      <c r="C647" s="1" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C648" s="0" t="s">
+      <c r="C648" s="1" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C649" s="0" t="s">
+      <c r="C649" s="1" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C650" s="0" t="s">
+      <c r="C650" s="1" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C651" s="0" t="s">
+      <c r="C651" s="1" t="s">
         <v>1591</v>
       </c>
     </row>
     <row r="652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C652" s="0" t="s">
+      <c r="C652" s="1" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C653" s="0" t="s">
+      <c r="C653" s="1" t="s">
         <v>867</v>
       </c>
     </row>
     <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C654" s="0" t="s">
+      <c r="C654" s="1" t="s">
         <v>1592</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C655" s="0" t="s">
+      <c r="C655" s="1" t="s">
         <v>862</v>
       </c>
     </row>
     <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C656" s="0" t="s">
+      <c r="C656" s="1" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C657" s="0" t="s">
+      <c r="C657" s="1" t="s">
         <v>853</v>
       </c>
     </row>
     <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C658" s="0" t="s">
+      <c r="C658" s="1" t="s">
         <v>850</v>
       </c>
     </row>
     <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C659" s="0" t="s">
+      <c r="C659" s="1" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C660" s="0" t="s">
+      <c r="C660" s="1" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C661" s="0" t="s">
+      <c r="C661" s="1" t="s">
         <v>1593</v>
       </c>
     </row>
     <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C662" s="0" t="s">
+      <c r="C662" s="1" t="s">
         <v>1594</v>
       </c>
     </row>
     <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C663" s="0" t="s">
+      <c r="C663" s="1" t="s">
         <v>838</v>
       </c>
     </row>
     <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C664" s="0" t="s">
+      <c r="C664" s="1" t="s">
         <v>1595</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C665" s="0" t="s">
+      <c r="C665" s="1" t="s">
         <v>834</v>
       </c>
     </row>
     <row r="666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C666" s="0" t="s">
+      <c r="C666" s="1" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C667" s="0" t="s">
+      <c r="C667" s="1" t="s">
         <v>1596</v>
       </c>
     </row>
     <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C668" s="0" t="s">
+      <c r="C668" s="1" t="s">
         <v>825</v>
       </c>
     </row>
     <row r="669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C669" s="0" t="s">
+      <c r="C669" s="1" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C670" s="0" t="s">
+      <c r="C670" s="1" t="s">
         <v>1597</v>
       </c>
     </row>
     <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C671" s="0" t="s">
+      <c r="C671" s="1" t="s">
         <v>1598</v>
       </c>
     </row>
     <row r="672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C672" s="0" t="s">
+      <c r="C672" s="1" t="s">
         <v>1599</v>
       </c>
     </row>
     <row r="673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C673" s="0" t="s">
+      <c r="C673" s="1" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C674" s="0" t="s">
+      <c r="C674" s="1" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C675" s="0" t="s">
+      <c r="C675" s="1" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C676" s="0" t="s">
+      <c r="C676" s="1" t="s">
         <v>1600</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C677" s="0" t="s">
+      <c r="C677" s="1" t="s">
         <v>1601</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C678" s="0" t="s">
+      <c r="C678" s="1" t="s">
         <v>808</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C679" s="0" t="s">
+      <c r="C679" s="1" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C680" s="0" t="s">
+      <c r="C680" s="1" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C681" s="0" t="s">
+      <c r="C681" s="1" t="s">
         <v>798</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C682" s="0" t="s">
+      <c r="C682" s="1" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C683" s="0" t="s">
+      <c r="C683" s="1" t="s">
         <v>1602</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C684" s="0" t="s">
+      <c r="C684" s="1" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C685" s="0" t="s">
+      <c r="C685" s="1" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C686" s="0" t="s">
+      <c r="C686" s="1" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C687" s="0" t="s">
+      <c r="C687" s="1" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C688" s="0" t="s">
+      <c r="C688" s="1" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C689" s="0" t="s">
+      <c r="C689" s="1" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C690" s="0" t="s">
+      <c r="C690" s="1" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C691" s="0" t="s">
+      <c r="C691" s="1" t="s">
         <v>1603</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C692" s="0" t="s">
+      <c r="C692" s="1" t="s">
         <v>1604</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C693" s="0" t="s">
+      <c r="C693" s="1" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C694" s="0" t="s">
+      <c r="C694" s="1" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C695" s="0" t="s">
+      <c r="C695" s="1" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C696" s="0" t="s">
+      <c r="C696" s="1" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C697" s="0" t="s">
+      <c r="C697" s="1" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C698" s="0" t="s">
+      <c r="C698" s="1" t="s">
         <v>1605</v>
       </c>
     </row>
     <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C699" s="0" t="s">
+      <c r="C699" s="1" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C700" s="0" t="s">
+      <c r="C700" s="1" t="s">
         <v>1606</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C701" s="0" t="s">
+      <c r="C701" s="1" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C702" s="0" t="s">
+      <c r="C702" s="1" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C703" s="0" t="s">
+      <c r="C703" s="1" t="s">
         <v>1607</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C704" s="0" t="s">
+      <c r="C704" s="1" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C705" s="0" t="s">
+      <c r="C705" s="1" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C706" s="0" t="s">
+      <c r="C706" s="1" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C707" s="0" t="s">
+      <c r="C707" s="1" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C708" s="0" t="s">
+      <c r="C708" s="1" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C709" s="0" t="s">
+      <c r="C709" s="1" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C710" s="0" t="s">
+      <c r="C710" s="1" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C711" s="0" t="s">
+      <c r="C711" s="1" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C712" s="0" t="s">
+      <c r="C712" s="1" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C713" s="0" t="s">
+      <c r="C713" s="1" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C714" s="0" t="s">
+      <c r="C714" s="1" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C715" s="0" t="s">
+      <c r="C715" s="1" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C716" s="0" t="s">
+      <c r="C716" s="1" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C717" s="0" t="s">
+      <c r="C717" s="1" t="s">
         <v>656</v>
       </c>
     </row>
     <row r="718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C718" s="0" t="s">
+      <c r="C718" s="1" t="s">
         <v>646</v>
       </c>
     </row>
@@ -29726,7 +29726,7 @@
       <c r="E2" s="1" t="s">
         <v>1612</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>1613</v>
       </c>
       <c r="G2" s="1" t="n">
@@ -32237,19 +32237,19 @@
         <v>1976</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>569</v>
+        <v>1977</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>9606</v>
@@ -32257,26 +32257,26 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>629</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>630</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1984</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32284,7 +32284,7 @@
         <v>1985</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1024</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32292,7 +32292,7 @@
         <v>1986</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1045</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32300,7 +32300,7 @@
         <v>1987</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1067</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32308,31 +32308,46 @@
         <v>1988</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>775</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>1989</v>
       </c>
+      <c r="B10" s="7" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>1990</v>
       </c>
+      <c r="B11" s="7" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>1991</v>
       </c>
+      <c r="B12" s="7" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1992</v>
+        <v>1977</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>1993</v>
       </c>
     </row>
@@ -32340,136 +32355,217 @@
       <c r="A15" s="1" t="s">
         <v>1994</v>
       </c>
+      <c r="B15" s="7" t="s">
+        <v>1995</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1995</v>
+        <v>1996</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1996</v>
+        <v>1997</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>559</v>
       </c>
+      <c r="B18" s="7" t="s">
+        <v>1998</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>567</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>568</v>
       </c>
+      <c r="B20" s="7" t="s">
+        <v>1999</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>569</v>
       </c>
+      <c r="B21" s="7" t="s">
+        <v>2000</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>571</v>
       </c>
+      <c r="B22" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>575</v>
       </c>
+      <c r="B23" s="7" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>576</v>
       </c>
+      <c r="B24" s="7" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>577</v>
       </c>
+      <c r="B25" s="7" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>579</v>
       </c>
+      <c r="B26" s="7" t="s">
+        <v>2001</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>580</v>
       </c>
+      <c r="B27" s="7" t="s">
+        <v>2002</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>581</v>
       </c>
+      <c r="B28" s="7" t="s">
+        <v>2003</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>583</v>
       </c>
+      <c r="B29" s="7" t="s">
+        <v>1024</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>584</v>
       </c>
+      <c r="B30" s="7" t="s">
+        <v>1027</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>585</v>
       </c>
+      <c r="B31" s="7" t="s">
+        <v>1045</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>586</v>
       </c>
+      <c r="B32" s="7" t="s">
+        <v>1061</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>587</v>
       </c>
+      <c r="B33" s="7" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>1997</v>
+        <v>2004</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>1067</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>590</v>
       </c>
+      <c r="B35" s="7" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>591</v>
       </c>
+      <c r="B36" s="7" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>592</v>
       </c>
+      <c r="B37" s="7" t="s">
+        <v>750</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>594</v>
       </c>
+      <c r="B38" s="7" t="s">
+        <v>2005</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>595</v>
       </c>
+      <c r="B39" s="7" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>596</v>
       </c>
+      <c r="B40" s="7" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>597</v>
       </c>
+      <c r="B41" s="7" t="s">
+        <v>1187</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
@@ -32593,67 +32689,67 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>1998</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>1999</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>2000</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>2001</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32698,7 +32794,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>2011</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32713,7 +32809,7 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>2012</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32733,27 +32829,27 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>2013</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>2014</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>2015</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>2016</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32768,17 +32864,17 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32793,12 +32889,12 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32813,17 +32909,17 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32833,12 +32929,12 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32848,22 +32944,22 @@
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32933,17 +33029,17 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>2032</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>2033</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>1984</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32988,7 +33084,7 @@
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32998,17 +33094,17 @@
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33083,7 +33179,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33108,7 +33204,7 @@
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>2039</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33746,7 +33842,7 @@
       <c r="G2" s="1" t="s">
         <v>2140</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>2141</v>
       </c>
       <c r="I2" s="1" t="n">
@@ -38657,7 +38753,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>3021</v>
